--- a/du_lieu_tram.xlsx
+++ b/du_lieu_tram.xlsx
@@ -12652,7 +12652,11 @@
       <c r="G359" t="n">
         <v>105.7261</v>
       </c>
-      <c r="H359" t="inlineStr"/>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12686,7 +12690,11 @@
       <c r="G360" t="n">
         <v>105.7261</v>
       </c>
-      <c r="H360" t="inlineStr"/>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">

--- a/du_lieu_tram.xlsx
+++ b/du_lieu_tram.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="862">
   <si>
     <t>ma_tram</t>
   </si>
@@ -2103,6 +2103,516 @@
   </si>
   <si>
     <t>TL295, Tân Hưng, Lạng Giang, Bắc Giang</t>
+  </si>
+  <si>
+    <t>BSS-254441000314</t>
+  </si>
+  <si>
+    <t>B.TQU10019</t>
+  </si>
+  <si>
+    <t>TDP Trầm Ân Thắng quân Yên Sơn Tuyên Quang</t>
+  </si>
+  <si>
+    <t>Xã Yên Sơn</t>
+  </si>
+  <si>
+    <t>Tuyên Quang</t>
+  </si>
+  <si>
+    <t>BSS-254641000080</t>
+  </si>
+  <si>
+    <t>B.TQU00027</t>
+  </si>
+  <si>
+    <t>Quốc lộ 37, Xã Thái Bình</t>
+  </si>
+  <si>
+    <t>BSS-254641000177</t>
+  </si>
+  <si>
+    <t>B.TQU00044</t>
+  </si>
+  <si>
+    <t>Xã Sơn Nam</t>
+  </si>
+  <si>
+    <t>Xã Sơn Dương</t>
+  </si>
+  <si>
+    <t>BSS-254641001221</t>
+  </si>
+  <si>
+    <t>B.TQU10025</t>
+  </si>
+  <si>
+    <t>TDP Tân Hà 4, P. Minh Xuân, Tỉnh Tuyên Quang</t>
+  </si>
+  <si>
+    <t>Phường Minh Xuân</t>
+  </si>
+  <si>
+    <t>BSS-254741000549</t>
+  </si>
+  <si>
+    <t>B.TQU10180</t>
+  </si>
+  <si>
+    <t>Tổ dân phố Cơ quan, Xã Sơn Dương, Tỉnh Tuyên Quang, Việt Nam</t>
+  </si>
+  <si>
+    <t>Phường Hà Giang 2</t>
+  </si>
+  <si>
+    <t>BSS-254741001149</t>
+  </si>
+  <si>
+    <t>B.TQU10254</t>
+  </si>
+  <si>
+    <t>Tổ 2 khu xuân hoà.xã tân quang tỉnh tuyên quang</t>
+  </si>
+  <si>
+    <t>Xã Ngọc Đường</t>
+  </si>
+  <si>
+    <t>BSS-254841000304</t>
+  </si>
+  <si>
+    <t>B.TQU00028</t>
+  </si>
+  <si>
+    <t>Thôn Trục Trì, Xã Yên Nguyên</t>
+  </si>
+  <si>
+    <t>Xã Chiêm Hóa</t>
+  </si>
+  <si>
+    <t>BSS-254841000382</t>
+  </si>
+  <si>
+    <t>B.TQU00143</t>
+  </si>
+  <si>
+    <t>Tỉnh Tuyên Quang</t>
+  </si>
+  <si>
+    <t>BSS-254841000401</t>
+  </si>
+  <si>
+    <t>B.TQU00030</t>
+  </si>
+  <si>
+    <t>Thôn Nà Ngà, Xã Ngọc Hội</t>
+  </si>
+  <si>
+    <t>BSS-254841000496</t>
+  </si>
+  <si>
+    <t>B.TQU00029</t>
+  </si>
+  <si>
+    <t>Thôn Pắc Nghiêng, Xã Kiến Thiết</t>
+  </si>
+  <si>
+    <t>BSS-254841000294</t>
+  </si>
+  <si>
+    <t>B.TQU00147</t>
+  </si>
+  <si>
+    <t>BSS-254841000398</t>
+  </si>
+  <si>
+    <t>B.TQU00149</t>
+  </si>
+  <si>
+    <t>BSS-254841000480</t>
+  </si>
+  <si>
+    <t>B.TQU00150</t>
+  </si>
+  <si>
+    <t>BSS-254841000601</t>
+  </si>
+  <si>
+    <t>B.TQU00144</t>
+  </si>
+  <si>
+    <t>BSS-254741000913</t>
+  </si>
+  <si>
+    <t>B.TQU00146</t>
+  </si>
+  <si>
+    <t>BSS-254841000400</t>
+  </si>
+  <si>
+    <t>B.TQU00142</t>
+  </si>
+  <si>
+    <t>BSS-254841000484</t>
+  </si>
+  <si>
+    <t>B.TQU00141</t>
+  </si>
+  <si>
+    <t>BSS-254741001048</t>
+  </si>
+  <si>
+    <t>B.TQU10002</t>
+  </si>
+  <si>
+    <t>Số 144, đường Trần Hưng Đạo, tổ 8, Phường Hà Giang 2, Tỉnh Tuyên Quang, Việt Nam</t>
+  </si>
+  <si>
+    <t>BSS-254741000947</t>
+  </si>
+  <si>
+    <t>B.TQU00035</t>
+  </si>
+  <si>
+    <t>Đường tỉnh 186, Xã Hào Phú</t>
+  </si>
+  <si>
+    <t>BSS-254841000477</t>
+  </si>
+  <si>
+    <t>B.TQU00036</t>
+  </si>
+  <si>
+    <t>Huyện Yên Sơn</t>
+  </si>
+  <si>
+    <t>BSS-254841000282</t>
+  </si>
+  <si>
+    <t>B.TQU00033</t>
+  </si>
+  <si>
+    <t>Thôn Đồng Chùa 1, Xã Bình Xa</t>
+  </si>
+  <si>
+    <t>Xã Hàm Yên</t>
+  </si>
+  <si>
+    <t>BSS-254841000512</t>
+  </si>
+  <si>
+    <t>B.TQU00034</t>
+  </si>
+  <si>
+    <t>Thôn Phú Lương, Xã CẤp Tiến</t>
+  </si>
+  <si>
+    <t>BSS-254841000016</t>
+  </si>
+  <si>
+    <t>B.TQU00038</t>
+  </si>
+  <si>
+    <t>Phường Tân Hà</t>
+  </si>
+  <si>
+    <t>BSS-254841000563</t>
+  </si>
+  <si>
+    <t>B.TQU00040</t>
+  </si>
+  <si>
+    <t>Thôn Cầu Quất, Xã Tú Thịnh</t>
+  </si>
+  <si>
+    <t>BSS-254741001038</t>
+  </si>
+  <si>
+    <t>B.TQU00042</t>
+  </si>
+  <si>
+    <t>Chợ Văn Phú, Xã Văn Phú</t>
+  </si>
+  <si>
+    <t>BSS-254841000288</t>
+  </si>
+  <si>
+    <t>B.TQU00031</t>
+  </si>
+  <si>
+    <t>Tổ 7, Phường Mỹ Lâm</t>
+  </si>
+  <si>
+    <t>Phường Mỹ Lâm</t>
+  </si>
+  <si>
+    <t>BSS-254941000934</t>
+  </si>
+  <si>
+    <t>B.TQU00052</t>
+  </si>
+  <si>
+    <t>Thôn Phú An, Xã Thái Long</t>
+  </si>
+  <si>
+    <t>Phường Bình Thuận</t>
+  </si>
+  <si>
+    <t>BSS-254841001305</t>
+  </si>
+  <si>
+    <t>B.TQU10024</t>
+  </si>
+  <si>
+    <t>Đường Hải Dương, Thai Long Commune, Bình Thuận Ward, Tuyên Quang</t>
+  </si>
+  <si>
+    <t>BSS-254941000675</t>
+  </si>
+  <si>
+    <t>B.TQU10005</t>
+  </si>
+  <si>
+    <t>Số nhà 64-66, Xã Quản Bạ, Tỉnh Tuyên Quang, Việt Nam</t>
+  </si>
+  <si>
+    <t>Xã Quản Bạ</t>
+  </si>
+  <si>
+    <t>BSS-254941000431</t>
+  </si>
+  <si>
+    <t>B.TQU10004</t>
+  </si>
+  <si>
+    <t>Tổ 2, Xã Yên Minh, Tỉnh Tuyên Quang, Việt Nam</t>
+  </si>
+  <si>
+    <t>Xã Yên Minh</t>
+  </si>
+  <si>
+    <t>BSS-254941000631</t>
+  </si>
+  <si>
+    <t>B.TQU10003</t>
+  </si>
+  <si>
+    <t>Thửa đất số 106, tờ bản đồ số 21, Xóm Thành Tâm, Xã Đồng Văn, Tỉnh Tuyên Quang, Việt Nam</t>
+  </si>
+  <si>
+    <t>Xã Đồng Văn</t>
+  </si>
+  <si>
+    <t>BSS-254941000077</t>
+  </si>
+  <si>
+    <t>BSS-254941000632</t>
+  </si>
+  <si>
+    <t>BSS-254941000601</t>
+  </si>
+  <si>
+    <t>B.TQU10179</t>
+  </si>
+  <si>
+    <t>Đường Quốc Lộ 2, tổ dân phố Tân An, Xã Hàm Yên, Tỉnh Tuyên Quang, Việt Nam</t>
+  </si>
+  <si>
+    <t>BSS-254941001913</t>
+  </si>
+  <si>
+    <t>B.TQU10181</t>
+  </si>
+  <si>
+    <t>CHXD Thanh Hương 1- TDP Minh Hải, Phường Thuận An, TP Huế</t>
+  </si>
+  <si>
+    <t>BSS-254941001460</t>
+  </si>
+  <si>
+    <t>B.TQU00011</t>
+  </si>
+  <si>
+    <t>Hầm B1, Vincom Plaza Tuyên Quang, số 260, đường Quang Trung</t>
+  </si>
+  <si>
+    <t>BSS-254941001874</t>
+  </si>
+  <si>
+    <t>BSS-254941001191</t>
+  </si>
+  <si>
+    <t>B.TQU00096</t>
+  </si>
+  <si>
+    <t>Thoôn 4, xã Việt Quang</t>
+  </si>
+  <si>
+    <t>BSS-255041001459</t>
+  </si>
+  <si>
+    <t>B.TQU00145</t>
+  </si>
+  <si>
+    <t>Thôn Quyết Thắng, Xã Sơn Thuỷ</t>
+  </si>
+  <si>
+    <t>BSS-254941002042</t>
+  </si>
+  <si>
+    <t>B.TQU00148</t>
+  </si>
+  <si>
+    <t>thôn Vĩnh Thịnh</t>
+  </si>
+  <si>
+    <t>BSS-254841001205</t>
+  </si>
+  <si>
+    <t>B.TQU10045</t>
+  </si>
+  <si>
+    <t>BSS-254941000763</t>
+  </si>
+  <si>
+    <t>BSS-255041000135</t>
+  </si>
+  <si>
+    <t>BSS-254941000317</t>
+  </si>
+  <si>
+    <t>B.TQU00026</t>
+  </si>
+  <si>
+    <t>Phúc ứng</t>
+  </si>
+  <si>
+    <t>BSS-254841001301</t>
+  </si>
+  <si>
+    <t>B.TQU10205</t>
+  </si>
+  <si>
+    <t>R675+RR9, Lê Lợi, P. Tân Quang, Tuyên Quang, Việt Nam</t>
+  </si>
+  <si>
+    <t>Xã Tân Quang</t>
+  </si>
+  <si>
+    <t>BSS-255041001732</t>
+  </si>
+  <si>
+    <t>BSS-254841001353</t>
+  </si>
+  <si>
+    <t>B.TQU00010</t>
+  </si>
+  <si>
+    <t>Quốc lộ 2, thôn Hòa Bình, xã Đội Bình</t>
+  </si>
+  <si>
+    <t>BSS-255341000614</t>
+  </si>
+  <si>
+    <t>B.TQU10237</t>
+  </si>
+  <si>
+    <t>Số 115 đường Trần Phú, tổ 15, phường Hà Giang 2 , tỉnh Tuyên Quang.</t>
+  </si>
+  <si>
+    <t>BSS-255241000219</t>
+  </si>
+  <si>
+    <t>B.TQU10239</t>
+  </si>
+  <si>
+    <t>số 225a , đường Lý Thường Kiệt, tổ 3 phường Hà Giang 2 , tỉnh Tuyên Quang.</t>
+  </si>
+  <si>
+    <t>BSS-255341000568</t>
+  </si>
+  <si>
+    <t>B.TQU10249</t>
+  </si>
+  <si>
+    <t>Km42 Hàm Yên, Tuyên Quang</t>
+  </si>
+  <si>
+    <t>BSS-255141001562</t>
+  </si>
+  <si>
+    <t>B.TQU10029</t>
+  </si>
+  <si>
+    <t>Thôn Tân Phúc, xã Sơn Dương, tỉnh Tuyên Quang</t>
+  </si>
+  <si>
+    <t>BSS-255341000141</t>
+  </si>
+  <si>
+    <t>B.TQU10251</t>
+  </si>
+  <si>
+    <t>Số Nhà 283, Tổ Dân Phố Số 6, phường, Tuyên Quang, Việt Nam</t>
+  </si>
+  <si>
+    <t>BSS-255341000621</t>
+  </si>
+  <si>
+    <t>B.TQU10238</t>
+  </si>
+  <si>
+    <t>số 293 đường Trần Phú , tổ 5 , phường Hà Giang 2 , tỉnh Tuyên Quang</t>
+  </si>
+  <si>
+    <t>BSS-260141000486</t>
+  </si>
+  <si>
+    <t>BSS-255241001740</t>
+  </si>
+  <si>
+    <t>B.TQU10027</t>
+  </si>
+  <si>
+    <t>TỔ 5, ĐƯỜNG VÕ CHÍ CÔNG, PHƯỜNG AN TƯỜNG, TP TUYÊN QUANG,TUYÊN QUANG</t>
+  </si>
+  <si>
+    <t>Phường An Tường</t>
+  </si>
+  <si>
+    <t>BSS-255341000081</t>
+  </si>
+  <si>
+    <t>B.TQU10282</t>
+  </si>
+  <si>
+    <t>Pả Vi, Mèo Vạc, Hà Giang</t>
+  </si>
+  <si>
+    <t>BSS-255141002224</t>
+  </si>
+  <si>
+    <t>B.TQU10031</t>
+  </si>
+  <si>
+    <t>X3MV+GCC Hàm Yên, Tuyên Quang, Việt Nam</t>
+  </si>
+  <si>
+    <t>BSS-255041000111</t>
+  </si>
+  <si>
+    <t>B.TQU10250</t>
+  </si>
+  <si>
+    <t>Tổ dân phố Liên Thịnh, phường An Tường, Tuyên Quang</t>
+  </si>
+  <si>
+    <t>BSS-255241000100</t>
+  </si>
+  <si>
+    <t>B.TQU10216</t>
+  </si>
+  <si>
+    <t>Km 12 đường đi tq hà nội Tổ 10 phường bình thuận Tuyên Quang</t>
   </si>
 </sst>
 </file>
@@ -2857,7 +3367,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2945,6 +3455,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3293,7 +3813,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I243"/>
+  <dimension ref="A1:I302"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -8871,6 +9391,1363 @@
         <v>106.301483</v>
       </c>
     </row>
+    <row r="244" ht="96.6" spans="1:7">
+      <c r="A244" s="39" t="s">
+        <v>692</v>
+      </c>
+      <c r="B244" s="40" t="s">
+        <v>693</v>
+      </c>
+      <c r="C244" s="41" t="s">
+        <v>694</v>
+      </c>
+      <c r="D244" s="40" t="s">
+        <v>695</v>
+      </c>
+      <c r="E244" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F244" s="40">
+        <v>21.876932</v>
+      </c>
+      <c r="G244" s="40">
+        <v>105.13732</v>
+      </c>
+    </row>
+    <row r="245" ht="55.2" spans="1:7">
+      <c r="A245" s="39" t="s">
+        <v>697</v>
+      </c>
+      <c r="B245" s="40" t="s">
+        <v>698</v>
+      </c>
+      <c r="C245" s="41" t="s">
+        <v>699</v>
+      </c>
+      <c r="D245" s="40" t="s">
+        <v>695</v>
+      </c>
+      <c r="E245" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F245" s="40">
+        <v>21.780275</v>
+      </c>
+      <c r="G245" s="40">
+        <v>105.293159</v>
+      </c>
+    </row>
+    <row r="246" ht="27.6" spans="1:7">
+      <c r="A246" s="39" t="s">
+        <v>700</v>
+      </c>
+      <c r="B246" s="40" t="s">
+        <v>701</v>
+      </c>
+      <c r="C246" s="41" t="s">
+        <v>702</v>
+      </c>
+      <c r="D246" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="E246" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F246" s="40">
+        <v>21.520733</v>
+      </c>
+      <c r="G246" s="40">
+        <v>105.485558</v>
+      </c>
+    </row>
+    <row r="247" ht="96.6" spans="1:7">
+      <c r="A247" s="39" t="s">
+        <v>704</v>
+      </c>
+      <c r="B247" s="40" t="s">
+        <v>705</v>
+      </c>
+      <c r="C247" s="41" t="s">
+        <v>706</v>
+      </c>
+      <c r="D247" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="E247" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F247" s="40">
+        <v>21.837469</v>
+      </c>
+      <c r="G247" s="40">
+        <v>105.19622</v>
+      </c>
+    </row>
+    <row r="248" ht="124.2" spans="1:7">
+      <c r="A248" s="39" t="s">
+        <v>708</v>
+      </c>
+      <c r="B248" s="40" t="s">
+        <v>709</v>
+      </c>
+      <c r="C248" s="41" t="s">
+        <v>710</v>
+      </c>
+      <c r="D248" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E248" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F248" s="40">
+        <v>21.696782</v>
+      </c>
+      <c r="G248" s="40">
+        <v>105.39147</v>
+      </c>
+    </row>
+    <row r="249" ht="110.4" spans="1:7">
+      <c r="A249" s="39" t="s">
+        <v>712</v>
+      </c>
+      <c r="B249" s="40" t="s">
+        <v>713</v>
+      </c>
+      <c r="C249" s="41" t="s">
+        <v>714</v>
+      </c>
+      <c r="D249" s="40" t="s">
+        <v>715</v>
+      </c>
+      <c r="E249" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F249" s="40">
+        <v>22.496029</v>
+      </c>
+      <c r="G249" s="40">
+        <v>104.873677</v>
+      </c>
+    </row>
+    <row r="250" ht="55.2" spans="1:7">
+      <c r="A250" s="39" t="s">
+        <v>716</v>
+      </c>
+      <c r="B250" s="40" t="s">
+        <v>717</v>
+      </c>
+      <c r="C250" s="41" t="s">
+        <v>718</v>
+      </c>
+      <c r="D250" s="40" t="s">
+        <v>719</v>
+      </c>
+      <c r="E250" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F250" s="40">
+        <v>22.071905</v>
+      </c>
+      <c r="G250" s="40">
+        <v>105.174988</v>
+      </c>
+    </row>
+    <row r="251" ht="41.4" spans="1:7">
+      <c r="A251" s="39" t="s">
+        <v>720</v>
+      </c>
+      <c r="B251" s="40" t="s">
+        <v>721</v>
+      </c>
+      <c r="C251" s="41" t="s">
+        <v>722</v>
+      </c>
+      <c r="D251" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E251" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F251" s="40">
+        <v>1</v>
+      </c>
+      <c r="G251" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" ht="41.4" spans="1:7">
+      <c r="A252" s="39" t="s">
+        <v>723</v>
+      </c>
+      <c r="B252" s="40" t="s">
+        <v>724</v>
+      </c>
+      <c r="C252" s="41" t="s">
+        <v>725</v>
+      </c>
+      <c r="D252" s="40" t="s">
+        <v>719</v>
+      </c>
+      <c r="E252" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F252" s="40">
+        <v>22.148243</v>
+      </c>
+      <c r="G252" s="40">
+        <v>105.283913</v>
+      </c>
+    </row>
+    <row r="253" ht="69" spans="1:7">
+      <c r="A253" s="39" t="s">
+        <v>726</v>
+      </c>
+      <c r="B253" s="40" t="s">
+        <v>727</v>
+      </c>
+      <c r="C253" s="41" t="s">
+        <v>728</v>
+      </c>
+      <c r="D253" s="40" t="s">
+        <v>695</v>
+      </c>
+      <c r="E253" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F253" s="40">
+        <v>21.9918</v>
+      </c>
+      <c r="G253" s="40">
+        <v>105.312599</v>
+      </c>
+    </row>
+    <row r="254" ht="41.4" spans="1:7">
+      <c r="A254" s="39" t="s">
+        <v>729</v>
+      </c>
+      <c r="B254" s="40" t="s">
+        <v>730</v>
+      </c>
+      <c r="C254" s="41" t="s">
+        <v>722</v>
+      </c>
+      <c r="D254" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E254" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F254" s="40">
+        <v>1</v>
+      </c>
+      <c r="G254" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" ht="41.4" spans="1:7">
+      <c r="A255" s="39" t="s">
+        <v>731</v>
+      </c>
+      <c r="B255" s="40" t="s">
+        <v>732</v>
+      </c>
+      <c r="C255" s="41" t="s">
+        <v>722</v>
+      </c>
+      <c r="D255" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E255" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F255" s="40">
+        <v>1</v>
+      </c>
+      <c r="G255" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" ht="41.4" spans="1:7">
+      <c r="A256" s="39" t="s">
+        <v>733</v>
+      </c>
+      <c r="B256" s="40" t="s">
+        <v>734</v>
+      </c>
+      <c r="C256" s="41" t="s">
+        <v>722</v>
+      </c>
+      <c r="D256" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E256" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F256" s="40">
+        <v>1</v>
+      </c>
+      <c r="G256" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" ht="41.4" spans="1:7">
+      <c r="A257" s="39" t="s">
+        <v>735</v>
+      </c>
+      <c r="B257" s="40" t="s">
+        <v>736</v>
+      </c>
+      <c r="C257" s="41" t="s">
+        <v>722</v>
+      </c>
+      <c r="D257" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E257" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F257" s="40">
+        <v>1</v>
+      </c>
+      <c r="G257" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" ht="41.4" spans="1:7">
+      <c r="A258" s="39" t="s">
+        <v>737</v>
+      </c>
+      <c r="B258" s="40" t="s">
+        <v>738</v>
+      </c>
+      <c r="C258" s="41" t="s">
+        <v>722</v>
+      </c>
+      <c r="D258" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E258" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F258" s="40">
+        <v>1</v>
+      </c>
+      <c r="G258" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" ht="41.4" spans="1:7">
+      <c r="A259" s="39" t="s">
+        <v>739</v>
+      </c>
+      <c r="B259" s="40" t="s">
+        <v>740</v>
+      </c>
+      <c r="C259" s="41" t="s">
+        <v>722</v>
+      </c>
+      <c r="D259" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E259" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F259" s="40">
+        <v>1</v>
+      </c>
+      <c r="G259" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" ht="41.4" spans="1:7">
+      <c r="A260" s="39" t="s">
+        <v>741</v>
+      </c>
+      <c r="B260" s="40" t="s">
+        <v>742</v>
+      </c>
+      <c r="C260" s="41" t="s">
+        <v>722</v>
+      </c>
+      <c r="D260" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E260" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F260" s="40">
+        <v>1</v>
+      </c>
+      <c r="G260" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" ht="179.4" spans="1:7">
+      <c r="A261" s="39" t="s">
+        <v>743</v>
+      </c>
+      <c r="B261" s="40" t="s">
+        <v>744</v>
+      </c>
+      <c r="C261" s="41" t="s">
+        <v>745</v>
+      </c>
+      <c r="D261" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E261" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F261" s="40">
+        <v>22.830748</v>
+      </c>
+      <c r="G261" s="40">
+        <v>104.98534</v>
+      </c>
+    </row>
+    <row r="262" ht="55.2" spans="1:7">
+      <c r="A262" s="39" t="s">
+        <v>746</v>
+      </c>
+      <c r="B262" s="40" t="s">
+        <v>747</v>
+      </c>
+      <c r="C262" s="41" t="s">
+        <v>748</v>
+      </c>
+      <c r="D262" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="E262" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F262" s="40">
+        <v>21.548981</v>
+      </c>
+      <c r="G262" s="40">
+        <v>105.31749</v>
+      </c>
+    </row>
+    <row r="263" ht="27.6" spans="1:7">
+      <c r="A263" s="39" t="s">
+        <v>749</v>
+      </c>
+      <c r="B263" s="40" t="s">
+        <v>750</v>
+      </c>
+      <c r="C263" s="41" t="s">
+        <v>751</v>
+      </c>
+      <c r="D263" s="40" t="s">
+        <v>695</v>
+      </c>
+      <c r="E263" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F263" s="40">
+        <v>21.7812</v>
+      </c>
+      <c r="G263" s="40">
+        <v>105.185402</v>
+      </c>
+    </row>
+    <row r="264" ht="69" spans="1:7">
+      <c r="A264" s="39" t="s">
+        <v>752</v>
+      </c>
+      <c r="B264" s="40" t="s">
+        <v>753</v>
+      </c>
+      <c r="C264" s="41" t="s">
+        <v>754</v>
+      </c>
+      <c r="D264" s="40" t="s">
+        <v>755</v>
+      </c>
+      <c r="E264" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F264" s="40">
+        <v>22.052073</v>
+      </c>
+      <c r="G264" s="40">
+        <v>105.116814</v>
+      </c>
+    </row>
+    <row r="265" ht="69" spans="1:7">
+      <c r="A265" s="39" t="s">
+        <v>756</v>
+      </c>
+      <c r="B265" s="40" t="s">
+        <v>757</v>
+      </c>
+      <c r="C265" s="41" t="s">
+        <v>758</v>
+      </c>
+      <c r="D265" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="E265" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F265" s="40">
+        <v>21.707808</v>
+      </c>
+      <c r="G265" s="40">
+        <v>105.263786</v>
+      </c>
+    </row>
+    <row r="266" ht="27.6" spans="1:7">
+      <c r="A266" s="39" t="s">
+        <v>759</v>
+      </c>
+      <c r="B266" s="40" t="s">
+        <v>760</v>
+      </c>
+      <c r="C266" s="41" t="s">
+        <v>761</v>
+      </c>
+      <c r="D266" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="E266" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F266" s="40">
+        <v>21.840565</v>
+      </c>
+      <c r="G266" s="40">
+        <v>105.19619</v>
+      </c>
+    </row>
+    <row r="267" ht="55.2" spans="1:7">
+      <c r="A267" s="39" t="s">
+        <v>762</v>
+      </c>
+      <c r="B267" s="40" t="s">
+        <v>763</v>
+      </c>
+      <c r="C267" s="41" t="s">
+        <v>764</v>
+      </c>
+      <c r="D267" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="E267" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F267" s="40">
+        <v>21.720547</v>
+      </c>
+      <c r="G267" s="40">
+        <v>105.405602</v>
+      </c>
+    </row>
+    <row r="268" ht="41.4" spans="1:7">
+      <c r="A268" s="39" t="s">
+        <v>765</v>
+      </c>
+      <c r="B268" s="40" t="s">
+        <v>766</v>
+      </c>
+      <c r="C268" s="41" t="s">
+        <v>767</v>
+      </c>
+      <c r="D268" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="E268" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F268" s="40">
+        <v>21.594042</v>
+      </c>
+      <c r="G268" s="40">
+        <v>105.292412</v>
+      </c>
+    </row>
+    <row r="269" ht="41.4" spans="1:7">
+      <c r="A269" s="39" t="s">
+        <v>768</v>
+      </c>
+      <c r="B269" s="40" t="s">
+        <v>769</v>
+      </c>
+      <c r="C269" s="41" t="s">
+        <v>770</v>
+      </c>
+      <c r="D269" s="40" t="s">
+        <v>771</v>
+      </c>
+      <c r="E269" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F269" s="40">
+        <v>21.759022</v>
+      </c>
+      <c r="G269" s="40">
+        <v>105.105736</v>
+      </c>
+    </row>
+    <row r="270" ht="55.2" spans="1:7">
+      <c r="A270" s="39" t="s">
+        <v>772</v>
+      </c>
+      <c r="B270" s="40" t="s">
+        <v>773</v>
+      </c>
+      <c r="C270" s="41" t="s">
+        <v>774</v>
+      </c>
+      <c r="D270" s="40" t="s">
+        <v>775</v>
+      </c>
+      <c r="E270" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F270" s="40">
+        <v>21.741411</v>
+      </c>
+      <c r="G270" s="40">
+        <v>105.231201</v>
+      </c>
+    </row>
+    <row r="271" ht="151.8" spans="1:7">
+      <c r="A271" s="39" t="s">
+        <v>776</v>
+      </c>
+      <c r="B271" s="40" t="s">
+        <v>777</v>
+      </c>
+      <c r="C271" s="41" t="s">
+        <v>778</v>
+      </c>
+      <c r="D271" s="40" t="s">
+        <v>775</v>
+      </c>
+      <c r="E271" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F271" s="40">
+        <v>21.733482</v>
+      </c>
+      <c r="G271" s="40">
+        <v>105.23231</v>
+      </c>
+    </row>
+    <row r="272" ht="96.6" spans="1:7">
+      <c r="A272" s="39" t="s">
+        <v>779</v>
+      </c>
+      <c r="B272" s="40" t="s">
+        <v>780</v>
+      </c>
+      <c r="C272" s="41" t="s">
+        <v>781</v>
+      </c>
+      <c r="D272" s="40" t="s">
+        <v>782</v>
+      </c>
+      <c r="E272" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F272" s="40">
+        <v>23.064776</v>
+      </c>
+      <c r="G272" s="40">
+        <v>104.99103</v>
+      </c>
+    </row>
+    <row r="273" ht="96.6" spans="1:7">
+      <c r="A273" s="39" t="s">
+        <v>783</v>
+      </c>
+      <c r="B273" s="40" t="s">
+        <v>784</v>
+      </c>
+      <c r="C273" s="41" t="s">
+        <v>785</v>
+      </c>
+      <c r="D273" s="40" t="s">
+        <v>786</v>
+      </c>
+      <c r="E273" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F273" s="40">
+        <v>23.119403</v>
+      </c>
+      <c r="G273" s="40">
+        <v>105.13737</v>
+      </c>
+    </row>
+    <row r="274" ht="179.4" spans="1:7">
+      <c r="A274" s="39" t="s">
+        <v>787</v>
+      </c>
+      <c r="B274" s="40" t="s">
+        <v>788</v>
+      </c>
+      <c r="C274" s="41" t="s">
+        <v>789</v>
+      </c>
+      <c r="D274" s="40" t="s">
+        <v>790</v>
+      </c>
+      <c r="E274" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F274" s="40">
+        <v>23.277016</v>
+      </c>
+      <c r="G274" s="40">
+        <v>105.364295</v>
+      </c>
+    </row>
+    <row r="275" ht="96.6" spans="1:7">
+      <c r="A275" s="39" t="s">
+        <v>791</v>
+      </c>
+      <c r="B275" s="40" t="s">
+        <v>784</v>
+      </c>
+      <c r="C275" s="41" t="s">
+        <v>785</v>
+      </c>
+      <c r="D275" s="40" t="s">
+        <v>786</v>
+      </c>
+      <c r="E275" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F275" s="40">
+        <v>23.119403</v>
+      </c>
+      <c r="G275" s="40">
+        <v>105.13737</v>
+      </c>
+    </row>
+    <row r="276" ht="179.4" spans="1:7">
+      <c r="A276" s="39" t="s">
+        <v>792</v>
+      </c>
+      <c r="B276" s="40" t="s">
+        <v>788</v>
+      </c>
+      <c r="C276" s="41" t="s">
+        <v>789</v>
+      </c>
+      <c r="D276" s="40" t="s">
+        <v>790</v>
+      </c>
+      <c r="E276" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F276" s="40">
+        <v>23.277016</v>
+      </c>
+      <c r="G276" s="40">
+        <v>105.364295</v>
+      </c>
+    </row>
+    <row r="277" ht="151.8" spans="1:7">
+      <c r="A277" s="39" t="s">
+        <v>793</v>
+      </c>
+      <c r="B277" s="40" t="s">
+        <v>794</v>
+      </c>
+      <c r="C277" s="41" t="s">
+        <v>795</v>
+      </c>
+      <c r="D277" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E277" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F277" s="40">
+        <v>22.058082</v>
+      </c>
+      <c r="G277" s="40">
+        <v>105.0329</v>
+      </c>
+    </row>
+    <row r="278" ht="138" spans="1:7">
+      <c r="A278" s="39" t="s">
+        <v>796</v>
+      </c>
+      <c r="B278" s="40" t="s">
+        <v>797</v>
+      </c>
+      <c r="C278" s="41" t="s">
+        <v>798</v>
+      </c>
+      <c r="D278" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E278" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F278" s="40">
+        <v>21.817961</v>
+      </c>
+      <c r="G278" s="40">
+        <v>105.20759</v>
+      </c>
+    </row>
+    <row r="279" ht="124.2" spans="1:7">
+      <c r="A279" s="39" t="s">
+        <v>799</v>
+      </c>
+      <c r="B279" s="40" t="s">
+        <v>800</v>
+      </c>
+      <c r="C279" s="41" t="s">
+        <v>801</v>
+      </c>
+      <c r="D279" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="E279" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F279" s="40">
+        <v>20.988386</v>
+      </c>
+      <c r="G279" s="40">
+        <v>105.941887</v>
+      </c>
+    </row>
+    <row r="280" ht="124.2" spans="1:7">
+      <c r="A280" s="39" t="s">
+        <v>802</v>
+      </c>
+      <c r="B280" s="40" t="s">
+        <v>800</v>
+      </c>
+      <c r="C280" s="41" t="s">
+        <v>801</v>
+      </c>
+      <c r="D280" s="40" t="s">
+        <v>707</v>
+      </c>
+      <c r="E280" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F280" s="40">
+        <v>20.988386</v>
+      </c>
+      <c r="G280" s="40">
+        <v>105.941887</v>
+      </c>
+    </row>
+    <row r="281" ht="41.4" spans="1:7">
+      <c r="A281" s="39" t="s">
+        <v>803</v>
+      </c>
+      <c r="B281" s="40" t="s">
+        <v>804</v>
+      </c>
+      <c r="C281" s="41" t="s">
+        <v>805</v>
+      </c>
+      <c r="D281" s="40" t="s">
+        <v>755</v>
+      </c>
+      <c r="E281" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F281" s="40">
+        <v>22.41474</v>
+      </c>
+      <c r="G281" s="40">
+        <v>104.808823</v>
+      </c>
+    </row>
+    <row r="282" ht="69" spans="1:7">
+      <c r="A282" s="39" t="s">
+        <v>806</v>
+      </c>
+      <c r="B282" s="40" t="s">
+        <v>807</v>
+      </c>
+      <c r="C282" s="41" t="s">
+        <v>808</v>
+      </c>
+      <c r="D282" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E282" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F282" s="40">
+        <v>21.555861</v>
+      </c>
+      <c r="G282" s="40">
+        <v>105.461086</v>
+      </c>
+    </row>
+    <row r="283" ht="41.4" spans="1:7">
+      <c r="A283" s="39" t="s">
+        <v>809</v>
+      </c>
+      <c r="B283" s="40" t="s">
+        <v>810</v>
+      </c>
+      <c r="C283" s="41" t="s">
+        <v>811</v>
+      </c>
+      <c r="D283" s="40" t="s">
+        <v>719</v>
+      </c>
+      <c r="E283" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F283" s="40">
+        <v>22.14478</v>
+      </c>
+      <c r="G283" s="40">
+        <v>105.25837</v>
+      </c>
+    </row>
+    <row r="284" ht="41.4" spans="1:7">
+      <c r="A284" s="39" t="s">
+        <v>812</v>
+      </c>
+      <c r="B284" s="40" t="s">
+        <v>813</v>
+      </c>
+      <c r="C284" s="41" t="s">
+        <v>722</v>
+      </c>
+      <c r="D284" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E284" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F284" s="40">
+        <v>1</v>
+      </c>
+      <c r="G284" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" ht="151.8" spans="1:7">
+      <c r="A285" s="39" t="s">
+        <v>814</v>
+      </c>
+      <c r="B285" s="40" t="s">
+        <v>794</v>
+      </c>
+      <c r="C285" s="41" t="s">
+        <v>795</v>
+      </c>
+      <c r="D285" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E285" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F285" s="40">
+        <v>22.058082</v>
+      </c>
+      <c r="G285" s="40">
+        <v>105.0329</v>
+      </c>
+    </row>
+    <row r="286" ht="138" spans="1:7">
+      <c r="A286" s="39" t="s">
+        <v>815</v>
+      </c>
+      <c r="B286" s="40" t="s">
+        <v>797</v>
+      </c>
+      <c r="C286" s="41" t="s">
+        <v>798</v>
+      </c>
+      <c r="D286" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E286" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F286" s="40">
+        <v>21.817961</v>
+      </c>
+      <c r="G286" s="40">
+        <v>105.20759</v>
+      </c>
+    </row>
+    <row r="287" ht="27.6" spans="1:7">
+      <c r="A287" s="39" t="s">
+        <v>816</v>
+      </c>
+      <c r="B287" s="40" t="s">
+        <v>817</v>
+      </c>
+      <c r="C287" s="41" t="s">
+        <v>818</v>
+      </c>
+      <c r="D287" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="E287" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F287" s="40">
+        <v>21.6422</v>
+      </c>
+      <c r="G287" s="40">
+        <v>105.382797</v>
+      </c>
+    </row>
+    <row r="288" ht="110.4" spans="1:7">
+      <c r="A288" s="39" t="s">
+        <v>819</v>
+      </c>
+      <c r="B288" s="40" t="s">
+        <v>820</v>
+      </c>
+      <c r="C288" s="41" t="s">
+        <v>821</v>
+      </c>
+      <c r="D288" s="40" t="s">
+        <v>822</v>
+      </c>
+      <c r="E288" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F288" s="40">
+        <v>21.814473</v>
+      </c>
+      <c r="G288" s="40">
+        <v>105.209279</v>
+      </c>
+    </row>
+    <row r="289" ht="55.2" spans="1:7">
+      <c r="A289" s="39" t="s">
+        <v>823</v>
+      </c>
+      <c r="B289" s="40" t="s">
+        <v>773</v>
+      </c>
+      <c r="C289" s="41" t="s">
+        <v>774</v>
+      </c>
+      <c r="D289" s="40" t="s">
+        <v>775</v>
+      </c>
+      <c r="E289" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F289" s="40">
+        <v>21.741411</v>
+      </c>
+      <c r="G289" s="40">
+        <v>105.231201</v>
+      </c>
+    </row>
+    <row r="290" ht="69" spans="1:7">
+      <c r="A290" s="39" t="s">
+        <v>824</v>
+      </c>
+      <c r="B290" s="40" t="s">
+        <v>825</v>
+      </c>
+      <c r="C290" s="41" t="s">
+        <v>826</v>
+      </c>
+      <c r="D290" s="40" t="s">
+        <v>695</v>
+      </c>
+      <c r="E290" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F290" s="40">
+        <v>21.672562</v>
+      </c>
+      <c r="G290" s="40">
+        <v>105.210373</v>
+      </c>
+    </row>
+    <row r="291" ht="151.8" spans="1:7">
+      <c r="A291" s="42" t="s">
+        <v>827</v>
+      </c>
+      <c r="B291" s="40" t="s">
+        <v>828</v>
+      </c>
+      <c r="C291" s="41" t="s">
+        <v>829</v>
+      </c>
+      <c r="D291" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E291" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F291" s="40">
+        <v>22.82121</v>
+      </c>
+      <c r="G291" s="40">
+        <v>104.9874</v>
+      </c>
+    </row>
+    <row r="292" ht="151.8" spans="1:7">
+      <c r="A292" s="42" t="s">
+        <v>830</v>
+      </c>
+      <c r="B292" s="40" t="s">
+        <v>831</v>
+      </c>
+      <c r="C292" s="41" t="s">
+        <v>832</v>
+      </c>
+      <c r="D292" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E292" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F292" s="40">
+        <v>22.84116</v>
+      </c>
+      <c r="G292" s="40">
+        <v>105.0001</v>
+      </c>
+    </row>
+    <row r="293" ht="69" spans="1:7">
+      <c r="A293" s="42" t="s">
+        <v>833</v>
+      </c>
+      <c r="B293" s="40" t="s">
+        <v>834</v>
+      </c>
+      <c r="C293" s="41" t="s">
+        <v>835</v>
+      </c>
+      <c r="D293" s="40" t="s">
+        <v>755</v>
+      </c>
+      <c r="E293" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F293" s="40">
+        <v>22.072248</v>
+      </c>
+      <c r="G293" s="40">
+        <v>105.03269</v>
+      </c>
+    </row>
+    <row r="294" ht="110.4" spans="1:7">
+      <c r="A294" s="42" t="s">
+        <v>836</v>
+      </c>
+      <c r="B294" s="40" t="s">
+        <v>837</v>
+      </c>
+      <c r="C294" s="41" t="s">
+        <v>838</v>
+      </c>
+      <c r="D294" s="40" t="s">
+        <v>703</v>
+      </c>
+      <c r="E294" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F294" s="40">
+        <v>21.701799</v>
+      </c>
+      <c r="G294" s="40">
+        <v>105.369263</v>
+      </c>
+    </row>
+    <row r="295" ht="110.4" spans="1:7">
+      <c r="A295" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="B295" s="40" t="s">
+        <v>840</v>
+      </c>
+      <c r="C295" s="41" t="s">
+        <v>841</v>
+      </c>
+      <c r="D295" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E295" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F295" s="40">
+        <v>21.792997</v>
+      </c>
+      <c r="G295" s="40">
+        <v>105.218974</v>
+      </c>
+    </row>
+    <row r="296" ht="151.8" spans="1:7">
+      <c r="A296" s="42" t="s">
+        <v>842</v>
+      </c>
+      <c r="B296" s="40" t="s">
+        <v>843</v>
+      </c>
+      <c r="C296" s="41" t="s">
+        <v>844</v>
+      </c>
+      <c r="D296" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E296" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F296" s="40">
+        <v>22.82818</v>
+      </c>
+      <c r="G296" s="40">
+        <v>104.9876</v>
+      </c>
+    </row>
+    <row r="297" ht="124.2" spans="1:7">
+      <c r="A297" s="42" t="s">
+        <v>845</v>
+      </c>
+      <c r="B297" s="40" t="s">
+        <v>709</v>
+      </c>
+      <c r="C297" s="41" t="s">
+        <v>710</v>
+      </c>
+      <c r="D297" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E297" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F297" s="40">
+        <v>21.696782</v>
+      </c>
+      <c r="G297" s="40">
+        <v>105.39147</v>
+      </c>
+    </row>
+    <row r="298" ht="165.6" spans="1:7">
+      <c r="A298" s="42" t="s">
+        <v>846</v>
+      </c>
+      <c r="B298" s="40" t="s">
+        <v>847</v>
+      </c>
+      <c r="C298" s="41" t="s">
+        <v>848</v>
+      </c>
+      <c r="D298" s="40" t="s">
+        <v>849</v>
+      </c>
+      <c r="E298" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F298" s="40">
+        <v>21.795111</v>
+      </c>
+      <c r="G298" s="40">
+        <v>105.21508</v>
+      </c>
+    </row>
+    <row r="299" ht="55.2" spans="1:7">
+      <c r="A299" s="42" t="s">
+        <v>850</v>
+      </c>
+      <c r="B299" s="40" t="s">
+        <v>851</v>
+      </c>
+      <c r="C299" s="41" t="s">
+        <v>852</v>
+      </c>
+      <c r="D299" s="40" t="s">
+        <v>715</v>
+      </c>
+      <c r="E299" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F299" s="40">
+        <v>23.182599</v>
+      </c>
+      <c r="G299" s="40">
+        <v>105.412022</v>
+      </c>
+    </row>
+    <row r="300" ht="82.8" spans="1:7">
+      <c r="A300" s="42" t="s">
+        <v>853</v>
+      </c>
+      <c r="B300" s="40" t="s">
+        <v>854</v>
+      </c>
+      <c r="C300" s="41" t="s">
+        <v>855</v>
+      </c>
+      <c r="D300" s="40" t="s">
+        <v>715</v>
+      </c>
+      <c r="E300" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F300" s="40">
+        <v>21.983817</v>
+      </c>
+      <c r="G300" s="40">
+        <v>105.09352</v>
+      </c>
+    </row>
+    <row r="301" ht="110.4" spans="1:7">
+      <c r="A301" s="42" t="s">
+        <v>856</v>
+      </c>
+      <c r="B301" s="40" t="s">
+        <v>857</v>
+      </c>
+      <c r="C301" s="41" t="s">
+        <v>858</v>
+      </c>
+      <c r="D301" s="40" t="s">
+        <v>715</v>
+      </c>
+      <c r="E301" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F301" s="40">
+        <v>21.771169</v>
+      </c>
+      <c r="G301" s="40">
+        <v>105.21401</v>
+      </c>
+    </row>
+    <row r="302" ht="124.2" spans="1:7">
+      <c r="A302" s="42" t="s">
+        <v>859</v>
+      </c>
+      <c r="B302" s="40" t="s">
+        <v>860</v>
+      </c>
+      <c r="C302" s="41" t="s">
+        <v>861</v>
+      </c>
+      <c r="D302" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E302" s="40" t="s">
+        <v>696</v>
+      </c>
+      <c r="F302" s="40">
+        <v>21.7221</v>
+      </c>
+      <c r="G302" s="40">
+        <v>105.2309</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/du_lieu_tram.xlsx
+++ b/du_lieu_tram.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="1179">
   <si>
     <t>ma_tram</t>
   </si>
@@ -2613,6 +2613,957 @@
   </si>
   <si>
     <t>Km 12 đường đi tq hà nội Tổ 10 phường bình thuận Tuyên Quang</t>
+  </si>
+  <si>
+    <t>BSS-254641000186</t>
+  </si>
+  <si>
+    <t>B.HNA00014</t>
+  </si>
+  <si>
+    <t>Thôn Hồng Sơn</t>
+  </si>
+  <si>
+    <t>Phường Kim Bảng</t>
+  </si>
+  <si>
+    <t>Ninh Bình</t>
+  </si>
+  <si>
+    <t>BSS-254641000221</t>
+  </si>
+  <si>
+    <t>B.HNA00011</t>
+  </si>
+  <si>
+    <t>Quốc lộ 21A, xã Liêm Phong</t>
+  </si>
+  <si>
+    <t>Xã Thanh Liêm</t>
+  </si>
+  <si>
+    <t>BSS-254641000134</t>
+  </si>
+  <si>
+    <t>B.HNA00017</t>
+  </si>
+  <si>
+    <t>Xã Thanh Nguyên</t>
+  </si>
+  <si>
+    <t>BSS-254641000145</t>
+  </si>
+  <si>
+    <t>B.HNA00041</t>
+  </si>
+  <si>
+    <t>Đường tránh Đồng Văn - Phủ Lý, Xã Thi Sơn</t>
+  </si>
+  <si>
+    <t>BSS-254641000210</t>
+  </si>
+  <si>
+    <t>B.HNA00006</t>
+  </si>
+  <si>
+    <t>Khu công nghiệp Đồng Văn 1</t>
+  </si>
+  <si>
+    <t>Phường Duy Tiên</t>
+  </si>
+  <si>
+    <t>BSS-254641000339</t>
+  </si>
+  <si>
+    <t>B.HNA00005</t>
+  </si>
+  <si>
+    <t>Đường Trần Hưng Đạo, thị trấn Vĩnh Trụ</t>
+  </si>
+  <si>
+    <t>Xã Lý Nhân</t>
+  </si>
+  <si>
+    <t>BSS-254741000175</t>
+  </si>
+  <si>
+    <t>B.HNA00036</t>
+  </si>
+  <si>
+    <t>Đường QL1A, Thanh Hải</t>
+  </si>
+  <si>
+    <t>BSS-254941000725</t>
+  </si>
+  <si>
+    <t>B.HNA00076</t>
+  </si>
+  <si>
+    <t>Cổng KDT Hanopack, Nhật Tựu, Kim Bảng, Hà Nam</t>
+  </si>
+  <si>
+    <t>BSS-254941001535</t>
+  </si>
+  <si>
+    <t>B.HNA00040</t>
+  </si>
+  <si>
+    <t>Thôn Nhật Tựu, Xã Nhật Tựu</t>
+  </si>
+  <si>
+    <t>BSS-255041001269</t>
+  </si>
+  <si>
+    <t>B.HNA00015</t>
+  </si>
+  <si>
+    <t>Xã Đồn Xá</t>
+  </si>
+  <si>
+    <t>Xã Bình Lục</t>
+  </si>
+  <si>
+    <t>BSS-255041001550</t>
+  </si>
+  <si>
+    <t>B.HNA00047</t>
+  </si>
+  <si>
+    <t>Phù Lưu 2, Xã Nguyễn Uý, Kim Bảng, Hà Nam</t>
+  </si>
+  <si>
+    <t>BSS-254941000138</t>
+  </si>
+  <si>
+    <t>B.HNA00003</t>
+  </si>
+  <si>
+    <t>Cửa hàng xăng dầu Tân Mai ngã 4 đường tránh thành phố Phủ Lý và quốc lộ 21A, đường N2, xã Liêm Tiết</t>
+  </si>
+  <si>
+    <t>Phường Liêm Tuyền</t>
+  </si>
+  <si>
+    <t>BSS-254441000372</t>
+  </si>
+  <si>
+    <t>B.HBI00041</t>
+  </si>
+  <si>
+    <t>Quốc lộ 6, Thị trấn Lương Sơn</t>
+  </si>
+  <si>
+    <t>Xã Lương Sơn</t>
+  </si>
+  <si>
+    <t>Phú Thọ</t>
+  </si>
+  <si>
+    <t>BSS-254641000950</t>
+  </si>
+  <si>
+    <t>B.HBI10043</t>
+  </si>
+  <si>
+    <t>Đường An Dương Vương, Phường Phương Lâm</t>
+  </si>
+  <si>
+    <t>Phường Hòa Bình</t>
+  </si>
+  <si>
+    <t>BSS-254641000255</t>
+  </si>
+  <si>
+    <t>B.HBI10042</t>
+  </si>
+  <si>
+    <t>Trung Minh, Phường Hòa Bình</t>
+  </si>
+  <si>
+    <t>BSS-254841000265</t>
+  </si>
+  <si>
+    <t>B.HBI00037</t>
+  </si>
+  <si>
+    <t>Huyện Lạc Thủy</t>
+  </si>
+  <si>
+    <t>Xã Lạc Thủy</t>
+  </si>
+  <si>
+    <t>BSS-254941001246</t>
+  </si>
+  <si>
+    <t>B.HBI00038</t>
+  </si>
+  <si>
+    <t>Xóm Khăm, xã Bình Sơn</t>
+  </si>
+  <si>
+    <t>Xã Kim Bôi</t>
+  </si>
+  <si>
+    <t>BSS-254941001443</t>
+  </si>
+  <si>
+    <t>B.HBI00026</t>
+  </si>
+  <si>
+    <t>Xóm Sèo, Xã Cao Sơn</t>
+  </si>
+  <si>
+    <t>Xã Đà Bắc</t>
+  </si>
+  <si>
+    <t>BSS-254941001266</t>
+  </si>
+  <si>
+    <t>B.HBI00029</t>
+  </si>
+  <si>
+    <t>Đường tỉnh 12B, Xã Mi Hòa</t>
+  </si>
+  <si>
+    <t>BSS-254941001253</t>
+  </si>
+  <si>
+    <t>B.HBI00008</t>
+  </si>
+  <si>
+    <t>Yên Quang</t>
+  </si>
+  <si>
+    <t>BSS-254941001467</t>
+  </si>
+  <si>
+    <t>B.HBI00032</t>
+  </si>
+  <si>
+    <t>Xóm Lục Đồi, Thị trấn Bo</t>
+  </si>
+  <si>
+    <t>BSS-254941001243</t>
+  </si>
+  <si>
+    <t>B.HBI00033</t>
+  </si>
+  <si>
+    <t>Xóm Đỉnh Cun, Xã Thu Phong</t>
+  </si>
+  <si>
+    <t>Xã Cao Phong</t>
+  </si>
+  <si>
+    <t>BSS-254941001472</t>
+  </si>
+  <si>
+    <t>B.HBI00031</t>
+  </si>
+  <si>
+    <t>Xóm Đậu, Xã Tòng Đậu</t>
+  </si>
+  <si>
+    <t>Xã Mai Châu</t>
+  </si>
+  <si>
+    <t>BSS-254941001901</t>
+  </si>
+  <si>
+    <t>B.HBI00013</t>
+  </si>
+  <si>
+    <t>Số 332, đường Cù Chính Lan, Phường Đồng Tiến</t>
+  </si>
+  <si>
+    <t>BSS-254941000721</t>
+  </si>
+  <si>
+    <t>B.HBI00015</t>
+  </si>
+  <si>
+    <t>332 Cù Chính Lan, phường Đồng Tiến</t>
+  </si>
+  <si>
+    <t>BSS-254941000683</t>
+  </si>
+  <si>
+    <t>B.HBI00016</t>
+  </si>
+  <si>
+    <t>Hầm B1 Vincom Plaza Hòa Bình, số 332, đường Cù Chính Lan</t>
+  </si>
+  <si>
+    <t>BSS-254941001518</t>
+  </si>
+  <si>
+    <t>BSS-254941001440</t>
+  </si>
+  <si>
+    <t>BSS-254941001130</t>
+  </si>
+  <si>
+    <t>B.HBI00005</t>
+  </si>
+  <si>
+    <t>Bãi đỗ xe mặt đất, Vincom Plaza Hòa Bình, số 332, đường Cù Chính Lan, phường Đồng Tên</t>
+  </si>
+  <si>
+    <t>BSS-255041000493</t>
+  </si>
+  <si>
+    <t>B.HBI00002</t>
+  </si>
+  <si>
+    <t>Thôn 2, xã Bảo Hiệu</t>
+  </si>
+  <si>
+    <t>Xã Yên Thủy</t>
+  </si>
+  <si>
+    <t>BSS-255041001076</t>
+  </si>
+  <si>
+    <t>B.HBI00017</t>
+  </si>
+  <si>
+    <t>Thôn Đồng Bảng, Xã Đông Tân</t>
+  </si>
+  <si>
+    <t>BSS-254941000342</t>
+  </si>
+  <si>
+    <t>B.HBI00014</t>
+  </si>
+  <si>
+    <t>Quốc lộ 12B, xóm Thượng, xã Lạc Thịnh</t>
+  </si>
+  <si>
+    <t>SN255041001589</t>
+  </si>
+  <si>
+    <t>B.HBI00069</t>
+  </si>
+  <si>
+    <t>Phường Quỳnh Lâm</t>
+  </si>
+  <si>
+    <t>SN255041001633</t>
+  </si>
+  <si>
+    <t>B.HBI00003</t>
+  </si>
+  <si>
+    <t>Cửa hàng xăng dầu Tân Lạc, thị trấn Mường Khiến</t>
+  </si>
+  <si>
+    <t>Xã Tân Lạc</t>
+  </si>
+  <si>
+    <t>BSS-254441000021</t>
+  </si>
+  <si>
+    <t>B.VPH00146</t>
+  </si>
+  <si>
+    <t>Thôn Quan Nội, Xã Tam Quan</t>
+  </si>
+  <si>
+    <t>Xã Tam Đảo</t>
+  </si>
+  <si>
+    <t>BSS-254641000143</t>
+  </si>
+  <si>
+    <t>B.VPH10037</t>
+  </si>
+  <si>
+    <t>Quốc lộ 2B, Kim Long</t>
+  </si>
+  <si>
+    <t>Phường Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>BSS-254641000141</t>
+  </si>
+  <si>
+    <t>B.VPH10027</t>
+  </si>
+  <si>
+    <t>BSS-254741000565</t>
+  </si>
+  <si>
+    <t>B.VPH00051</t>
+  </si>
+  <si>
+    <t>Số 1D, Đường Kim Ngọc, Phường Tích Sơn</t>
+  </si>
+  <si>
+    <t>Phường Vĩnh Yên</t>
+  </si>
+  <si>
+    <t>BSS-254841000467</t>
+  </si>
+  <si>
+    <t>B.VPH00045</t>
+  </si>
+  <si>
+    <t>Phường Hội hợp</t>
+  </si>
+  <si>
+    <t>BSS-254841000472</t>
+  </si>
+  <si>
+    <t>B.VPH00053</t>
+  </si>
+  <si>
+    <t>Huyện Vĩnh Tường</t>
+  </si>
+  <si>
+    <t>BSS-254841000466</t>
+  </si>
+  <si>
+    <t>B.VPH00043</t>
+  </si>
+  <si>
+    <t>Thôn Đông Cao, xã Ngọc Thanh</t>
+  </si>
+  <si>
+    <t>Phường Phúc Yên</t>
+  </si>
+  <si>
+    <t>BSS-254841000459</t>
+  </si>
+  <si>
+    <t>B.VPH00047</t>
+  </si>
+  <si>
+    <t>Thôn Đồng Vang, Kim Dương, Tam Dương, Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>Xã Tam Dương</t>
+  </si>
+  <si>
+    <t>BSS-254741001018</t>
+  </si>
+  <si>
+    <t>B.VPH00044</t>
+  </si>
+  <si>
+    <t>Thôn Yên Thịnh, Xã Bình Dương</t>
+  </si>
+  <si>
+    <t>Xã Vĩnh Tường</t>
+  </si>
+  <si>
+    <t>BSS-254841000494</t>
+  </si>
+  <si>
+    <t>B.VPH00050</t>
+  </si>
+  <si>
+    <t>Thôn Thượng, Xã Thượng Trưng</t>
+  </si>
+  <si>
+    <t>BSS-254841000370</t>
+  </si>
+  <si>
+    <t>B.VPH00052</t>
+  </si>
+  <si>
+    <t>Thôn suối, Xã Cao Phong</t>
+  </si>
+  <si>
+    <t>Xã Sông Lô</t>
+  </si>
+  <si>
+    <t>BSS-254841000502</t>
+  </si>
+  <si>
+    <t>B.VPH00023</t>
+  </si>
+  <si>
+    <t>Cửa hàng xăng dầu Petrolimex Hà Anh, đường 2B, thị trấn Hợp Châu, Tam Đảo, Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>BSS-254941001133</t>
+  </si>
+  <si>
+    <t>B.VPH00041</t>
+  </si>
+  <si>
+    <t>Quốc lộ 2A, Thị trấn Hương Canh, Bình Xuyên, Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>Xã Bình Xuyên</t>
+  </si>
+  <si>
+    <t>BSS-254941000221</t>
+  </si>
+  <si>
+    <t>B.VPH00040</t>
+  </si>
+  <si>
+    <t>Đường Nguyễn Văn Cừ, Phường Khai Quang, Vĩnh Yên, Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>BSS-254941001482</t>
+  </si>
+  <si>
+    <t>B.VPH10026</t>
+  </si>
+  <si>
+    <t>Số 408 Mê Linh, Phường Khai Quang, Thành phố Vĩnh Yên, Tỉnh Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>BSS-254941001292</t>
+  </si>
+  <si>
+    <t>B.VPH00048</t>
+  </si>
+  <si>
+    <t>Số 31, Đường Hoàng Quốc Việt, Phường Trưng Trắc</t>
+  </si>
+  <si>
+    <t>BSS-254941001377</t>
+  </si>
+  <si>
+    <t>B.VPH00149</t>
+  </si>
+  <si>
+    <t>thành phố Vĩnh Yên,  tỉnh Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>BSS-254941001948</t>
+  </si>
+  <si>
+    <t>B.VPH00026</t>
+  </si>
+  <si>
+    <t>Số 408. đường Mê Linh, phường Khai Quang</t>
+  </si>
+  <si>
+    <t>BSS-255041001444</t>
+  </si>
+  <si>
+    <t>B.VPH00038</t>
+  </si>
+  <si>
+    <t>Thôn Nhân Mỹ, Xã Thanh Vân</t>
+  </si>
+  <si>
+    <t>BSS-255041001237</t>
+  </si>
+  <si>
+    <t>B.VPH00056</t>
+  </si>
+  <si>
+    <t>Phường Hùng Vương</t>
+  </si>
+  <si>
+    <t>BSS-255041002558</t>
+  </si>
+  <si>
+    <t>B.VPH00060</t>
+  </si>
+  <si>
+    <t>Đường tỉnh 310, Xã Thiện Kế</t>
+  </si>
+  <si>
+    <t>BSS-254841001062</t>
+  </si>
+  <si>
+    <t>B.VPH00058</t>
+  </si>
+  <si>
+    <t>Tiếng Anh xã Ngọc Thanh, huyện Phúc Yên, tỉnh Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>BSS-255141001087</t>
+  </si>
+  <si>
+    <t>B.VPH00063</t>
+  </si>
+  <si>
+    <t>Thị trấn Đại Đình</t>
+  </si>
+  <si>
+    <t>BSS-254441000047</t>
+  </si>
+  <si>
+    <t>B.PTH10428</t>
+  </si>
+  <si>
+    <t>289, National Highway 2, Hung Vuong Ward, Phúc Yên Ward, Phú</t>
+  </si>
+  <si>
+    <t>BSS-254441000040</t>
+  </si>
+  <si>
+    <t>B.PTH10429</t>
+  </si>
+  <si>
+    <t>Đường 304 Phạm Công Bình, Phú Thọ</t>
+  </si>
+  <si>
+    <t>Xã Tam Hồng</t>
+  </si>
+  <si>
+    <t>BSS-254441000701</t>
+  </si>
+  <si>
+    <t>B.PTH10155</t>
+  </si>
+  <si>
+    <t>2a, National Highway 2, Dao Duc Town, Xuân Lãng Commune, Phú Thọ</t>
+  </si>
+  <si>
+    <t>Xã Xuân Lãng</t>
+  </si>
+  <si>
+    <t>BSS-254741000515</t>
+  </si>
+  <si>
+    <t>B.PTH10438</t>
+  </si>
+  <si>
+    <t>Vietnam, Phú Thọ Province · Vĩnh Yên Ward · Hoi Hop Ward</t>
+  </si>
+  <si>
+    <t>BSS-254741000304</t>
+  </si>
+  <si>
+    <t>B.PTH10632</t>
+  </si>
+  <si>
+    <t>Thôn Xuân Chiểu</t>
+  </si>
+  <si>
+    <t>BSS-254741001168</t>
+  </si>
+  <si>
+    <t>B.PTH10625</t>
+  </si>
+  <si>
+    <t>Thôn Đồng Giếng Đạo Trù</t>
+  </si>
+  <si>
+    <t>BSS-254741001163</t>
+  </si>
+  <si>
+    <t>B.PTH10628</t>
+  </si>
+  <si>
+    <t>Thôn Hạ Ích Đồng Ích</t>
+  </si>
+  <si>
+    <t>BSS-254841000103</t>
+  </si>
+  <si>
+    <t>B.PTH10004</t>
+  </si>
+  <si>
+    <t>Số nhà 42, Khu 3, Xã Cao Phong, Tỉnh Phú Thọ, Việt Nam</t>
+  </si>
+  <si>
+    <t>BSS-254741001087</t>
+  </si>
+  <si>
+    <t>BSS-254841000315</t>
+  </si>
+  <si>
+    <t>B.PTH10026</t>
+  </si>
+  <si>
+    <t>Đường Quốc lộ 2C, Phố Me, Xã Tam Dương, Tỉnh Phú Thọ, Việt Nam</t>
+  </si>
+  <si>
+    <t>BSS-254741001024</t>
+  </si>
+  <si>
+    <t>B.PTH10025</t>
+  </si>
+  <si>
+    <t>Số 26 đường Trần Hưng Đạo, Phường Phúc Yên, Tỉnh Phú Thọ, Việt Nam</t>
+  </si>
+  <si>
+    <t>BSS-254841000566</t>
+  </si>
+  <si>
+    <t>B.PTH10023</t>
+  </si>
+  <si>
+    <t>Số 136, Đường Trường Chinh, Phường Xuân Hòa, Tỉnh Phú Thọ, Việt Nam</t>
+  </si>
+  <si>
+    <t>Phường Xuân Hòa</t>
+  </si>
+  <si>
+    <t>BSS-254941000709</t>
+  </si>
+  <si>
+    <t>B.PTH10007</t>
+  </si>
+  <si>
+    <t>Số 79, Quốc lộ 32, Phố Ba Mỏ, Xã Thanh Sơn, Tỉnh Phú Thọ, Việt Nam</t>
+  </si>
+  <si>
+    <t>Xã Thanh Sơn</t>
+  </si>
+  <si>
+    <t>BSS-254841000562</t>
+  </si>
+  <si>
+    <t>BSS-254941001124</t>
+  </si>
+  <si>
+    <t>B.PTH10621</t>
+  </si>
+  <si>
+    <t>Thôn Vĩnh Ninh Đạo Trù Tam Đảo</t>
+  </si>
+  <si>
+    <t>BSS-254941000612</t>
+  </si>
+  <si>
+    <t>B.PTH10630</t>
+  </si>
+  <si>
+    <t>Thôn Duy Bình Vĩnh Ninh</t>
+  </si>
+  <si>
+    <t>BSS-254941001481</t>
+  </si>
+  <si>
+    <t>B.PTH10623</t>
+  </si>
+  <si>
+    <t>Thôn Đồng Quạ Đạo trù</t>
+  </si>
+  <si>
+    <t>BSS-254941000278</t>
+  </si>
+  <si>
+    <t>B.PTH10631</t>
+  </si>
+  <si>
+    <t>Thôn Kim xa Vĩnh Ninh</t>
+  </si>
+  <si>
+    <t>BSS-254941001449</t>
+  </si>
+  <si>
+    <t>B.PTH10633</t>
+  </si>
+  <si>
+    <t>Ngọc Mỹ Lập Thạch</t>
+  </si>
+  <si>
+    <t>BSS-254941001305</t>
+  </si>
+  <si>
+    <t>B.PTH00081</t>
+  </si>
+  <si>
+    <t>Khu Minh Đức, Xã Minh Hòa</t>
+  </si>
+  <si>
+    <t>Xã Yên Lập</t>
+  </si>
+  <si>
+    <t>BSS-255041001429</t>
+  </si>
+  <si>
+    <t>B.PTH00082</t>
+  </si>
+  <si>
+    <t>Xã Tinh Nhuệ</t>
+  </si>
+  <si>
+    <t>BSS-254941001242</t>
+  </si>
+  <si>
+    <t>B.PTH00061</t>
+  </si>
+  <si>
+    <t>Khu Minh Khai, Xã Cự Đồng</t>
+  </si>
+  <si>
+    <t>BSS-255041001417</t>
+  </si>
+  <si>
+    <t>B.PTH00069</t>
+  </si>
+  <si>
+    <t>Xã Tuy Lộc</t>
+  </si>
+  <si>
+    <t>BSS-254941001260</t>
+  </si>
+  <si>
+    <t>B.PTH00057</t>
+  </si>
+  <si>
+    <t>Đường 32C, Xã Minh Côi</t>
+  </si>
+  <si>
+    <t>Xã Văn Lang</t>
+  </si>
+  <si>
+    <t>BSS-254941001250</t>
+  </si>
+  <si>
+    <t>B.PTH00083</t>
+  </si>
+  <si>
+    <t>Xã Xuân Đài</t>
+  </si>
+  <si>
+    <t>BSS-254941001272</t>
+  </si>
+  <si>
+    <t>B.PTH00076</t>
+  </si>
+  <si>
+    <t>Xã Tân Phú</t>
+  </si>
+  <si>
+    <t>Xã Tân Sơn</t>
+  </si>
+  <si>
+    <t>BSS-255041000043</t>
+  </si>
+  <si>
+    <t>B.PTH10624</t>
+  </si>
+  <si>
+    <t>BSS-255041001813</t>
+  </si>
+  <si>
+    <t>B.PTH00194</t>
+  </si>
+  <si>
+    <t>Đường tỉnh 306, Lap Thach Town, Lập Thạch Commune, Phú Thọ</t>
+  </si>
+  <si>
+    <t>BSS-255041001838</t>
+  </si>
+  <si>
+    <t>B.PTH00159</t>
+  </si>
+  <si>
+    <t>Xóm bần 1, Phường Võ Miếu, Quận Thanh Sơn, Tỉnh Phú Thọ</t>
+  </si>
+  <si>
+    <t>BSS-255041001058</t>
+  </si>
+  <si>
+    <t>B.PTH00089</t>
+  </si>
+  <si>
+    <t>Phố Ba Mỏ, thị trấn Thanh Sơn</t>
+  </si>
+  <si>
+    <t>BSS-254941000326</t>
+  </si>
+  <si>
+    <t>B.PTH00054</t>
+  </si>
+  <si>
+    <t>Khu Tân Tiến, Thị trấn Thanh Sơn</t>
+  </si>
+  <si>
+    <t>BSS-255041001107</t>
+  </si>
+  <si>
+    <t>B.PTH10342</t>
+  </si>
+  <si>
+    <t>Vietnam, Phú Thọ Province · Vĩnh Thành Commune · Viet Xuan Commune</t>
+  </si>
+  <si>
+    <t>Xã Vĩnh Thành</t>
+  </si>
+  <si>
+    <t>BSS-255041001135</t>
+  </si>
+  <si>
+    <t>B.PTH10663</t>
+  </si>
+  <si>
+    <t>Số nhà 313 đường Hùng Vương, Phường Tích Sơn, Thành phố Vĩnh Yên, Tỉnh Vĩnh Phúc(Gần cầu oai bệnh viện 109)</t>
+  </si>
+  <si>
+    <t>BSS-255241001278</t>
+  </si>
+  <si>
+    <t>B.PTH10626</t>
+  </si>
+  <si>
+    <t>Thôn Lục Liễu Đạo Trù</t>
+  </si>
+  <si>
+    <t>BSS-255041002438</t>
+  </si>
+  <si>
+    <t>BSS-255041001075</t>
+  </si>
+  <si>
+    <t>B.PTH10629</t>
+  </si>
+  <si>
+    <t>Thôn Hậu Lộc Vĩnh Ninh</t>
+  </si>
+  <si>
+    <t>BSS-255341000722</t>
+  </si>
+  <si>
+    <t>BSS-255241003215</t>
+  </si>
+  <si>
+    <t>BSS-255241002060</t>
+  </si>
+  <si>
+    <t>B.PTH10425</t>
+  </si>
+  <si>
+    <t>QL2B, Hợp Châu, Tam Đảo, Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>BSS-255341000360</t>
+  </si>
+  <si>
+    <t>B.PTH10622</t>
+  </si>
+  <si>
+    <t>BSS-255341000487</t>
+  </si>
+  <si>
+    <t>B.PTH10664</t>
+  </si>
+  <si>
+    <t>Số nhà 523 Đường Mê Linh,Phường Khai quang, Thành phố Vĩnh Yên, Tỉnh Vĩnh Phúc(Gần nhà thi đấu Vĩnh Yên).</t>
+  </si>
+  <si>
+    <t>BSS-255141002445</t>
+  </si>
+  <si>
+    <t>B.PTH10024</t>
+  </si>
+  <si>
+    <t>Số nhà 499, đường Hùng Vương, Phường Vĩnh Yên, Tỉnh Phú Thọ, Việt Nam</t>
+  </si>
+  <si>
+    <t>BSS-255241001914</t>
+  </si>
+  <si>
+    <t>BSS-260141000003</t>
+  </si>
+  <si>
+    <t>B.PTH10627</t>
+  </si>
+  <si>
+    <t>Thôn Viên Luận Đồng Ích</t>
   </si>
 </sst>
 </file>
@@ -3813,7 +4764,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I302"/>
+  <dimension ref="A1:I403"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -9392,1360 +10343,3683 @@
       </c>
     </row>
     <row r="244" ht="96.6" spans="1:7">
-      <c r="A244" s="39" t="s">
+      <c r="A244" s="29" t="s">
         <v>692</v>
       </c>
-      <c r="B244" s="40" t="s">
+      <c r="B244" s="30" t="s">
         <v>693</v>
       </c>
-      <c r="C244" s="41" t="s">
+      <c r="C244" s="31" t="s">
         <v>694</v>
       </c>
-      <c r="D244" s="40" t="s">
+      <c r="D244" s="30" t="s">
         <v>695</v>
       </c>
-      <c r="E244" s="40" t="s">
+      <c r="E244" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F244" s="40">
+      <c r="F244" s="30">
         <v>21.876932</v>
       </c>
-      <c r="G244" s="40">
+      <c r="G244" s="30">
         <v>105.13732</v>
       </c>
     </row>
     <row r="245" ht="55.2" spans="1:7">
-      <c r="A245" s="39" t="s">
+      <c r="A245" s="29" t="s">
         <v>697</v>
       </c>
-      <c r="B245" s="40" t="s">
+      <c r="B245" s="30" t="s">
         <v>698</v>
       </c>
-      <c r="C245" s="41" t="s">
+      <c r="C245" s="31" t="s">
         <v>699</v>
       </c>
-      <c r="D245" s="40" t="s">
+      <c r="D245" s="30" t="s">
         <v>695</v>
       </c>
-      <c r="E245" s="40" t="s">
+      <c r="E245" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F245" s="40">
+      <c r="F245" s="30">
         <v>21.780275</v>
       </c>
-      <c r="G245" s="40">
+      <c r="G245" s="30">
         <v>105.293159</v>
       </c>
     </row>
     <row r="246" ht="27.6" spans="1:7">
-      <c r="A246" s="39" t="s">
+      <c r="A246" s="29" t="s">
         <v>700</v>
       </c>
-      <c r="B246" s="40" t="s">
+      <c r="B246" s="30" t="s">
         <v>701</v>
       </c>
-      <c r="C246" s="41" t="s">
+      <c r="C246" s="31" t="s">
         <v>702</v>
       </c>
-      <c r="D246" s="40" t="s">
+      <c r="D246" s="30" t="s">
         <v>703</v>
       </c>
-      <c r="E246" s="40" t="s">
+      <c r="E246" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F246" s="40">
+      <c r="F246" s="30">
         <v>21.520733</v>
       </c>
-      <c r="G246" s="40">
+      <c r="G246" s="30">
         <v>105.485558</v>
       </c>
     </row>
     <row r="247" ht="96.6" spans="1:7">
-      <c r="A247" s="39" t="s">
+      <c r="A247" s="29" t="s">
         <v>704</v>
       </c>
-      <c r="B247" s="40" t="s">
+      <c r="B247" s="30" t="s">
         <v>705</v>
       </c>
-      <c r="C247" s="41" t="s">
+      <c r="C247" s="31" t="s">
         <v>706</v>
       </c>
-      <c r="D247" s="40" t="s">
+      <c r="D247" s="30" t="s">
         <v>707</v>
       </c>
-      <c r="E247" s="40" t="s">
+      <c r="E247" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F247" s="40">
+      <c r="F247" s="30">
         <v>21.837469</v>
       </c>
-      <c r="G247" s="40">
+      <c r="G247" s="30">
         <v>105.19622</v>
       </c>
     </row>
     <row r="248" ht="124.2" spans="1:7">
-      <c r="A248" s="39" t="s">
+      <c r="A248" s="29" t="s">
         <v>708</v>
       </c>
-      <c r="B248" s="40" t="s">
+      <c r="B248" s="30" t="s">
         <v>709</v>
       </c>
-      <c r="C248" s="41" t="s">
+      <c r="C248" s="31" t="s">
         <v>710</v>
       </c>
-      <c r="D248" s="40" t="s">
+      <c r="D248" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E248" s="40" t="s">
+      <c r="E248" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F248" s="40">
+      <c r="F248" s="30">
         <v>21.696782</v>
       </c>
-      <c r="G248" s="40">
+      <c r="G248" s="30">
         <v>105.39147</v>
       </c>
     </row>
     <row r="249" ht="110.4" spans="1:7">
-      <c r="A249" s="39" t="s">
+      <c r="A249" s="29" t="s">
         <v>712</v>
       </c>
-      <c r="B249" s="40" t="s">
+      <c r="B249" s="30" t="s">
         <v>713</v>
       </c>
-      <c r="C249" s="41" t="s">
+      <c r="C249" s="31" t="s">
         <v>714</v>
       </c>
-      <c r="D249" s="40" t="s">
+      <c r="D249" s="30" t="s">
         <v>715</v>
       </c>
-      <c r="E249" s="40" t="s">
+      <c r="E249" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F249" s="40">
+      <c r="F249" s="30">
         <v>22.496029</v>
       </c>
-      <c r="G249" s="40">
+      <c r="G249" s="30">
         <v>104.873677</v>
       </c>
     </row>
     <row r="250" ht="55.2" spans="1:7">
-      <c r="A250" s="39" t="s">
+      <c r="A250" s="29" t="s">
         <v>716</v>
       </c>
-      <c r="B250" s="40" t="s">
+      <c r="B250" s="30" t="s">
         <v>717</v>
       </c>
-      <c r="C250" s="41" t="s">
+      <c r="C250" s="31" t="s">
         <v>718</v>
       </c>
-      <c r="D250" s="40" t="s">
+      <c r="D250" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="E250" s="40" t="s">
+      <c r="E250" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F250" s="40">
+      <c r="F250" s="30">
         <v>22.071905</v>
       </c>
-      <c r="G250" s="40">
+      <c r="G250" s="30">
         <v>105.174988</v>
       </c>
     </row>
     <row r="251" ht="41.4" spans="1:7">
-      <c r="A251" s="39" t="s">
+      <c r="A251" s="29" t="s">
         <v>720</v>
       </c>
-      <c r="B251" s="40" t="s">
+      <c r="B251" s="30" t="s">
         <v>721</v>
       </c>
-      <c r="C251" s="41" t="s">
+      <c r="C251" s="31" t="s">
         <v>722</v>
       </c>
-      <c r="D251" s="40" t="s">
+      <c r="D251" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E251" s="40" t="s">
+      <c r="E251" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F251" s="40">
+      <c r="F251" s="30">
         <v>1</v>
       </c>
-      <c r="G251" s="40">
+      <c r="G251" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="252" ht="41.4" spans="1:7">
-      <c r="A252" s="39" t="s">
+      <c r="A252" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="B252" s="40" t="s">
+      <c r="B252" s="30" t="s">
         <v>724</v>
       </c>
-      <c r="C252" s="41" t="s">
+      <c r="C252" s="31" t="s">
         <v>725</v>
       </c>
-      <c r="D252" s="40" t="s">
+      <c r="D252" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="E252" s="40" t="s">
+      <c r="E252" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F252" s="40">
+      <c r="F252" s="30">
         <v>22.148243</v>
       </c>
-      <c r="G252" s="40">
+      <c r="G252" s="30">
         <v>105.283913</v>
       </c>
     </row>
     <row r="253" ht="69" spans="1:7">
-      <c r="A253" s="39" t="s">
+      <c r="A253" s="29" t="s">
         <v>726</v>
       </c>
-      <c r="B253" s="40" t="s">
+      <c r="B253" s="30" t="s">
         <v>727</v>
       </c>
-      <c r="C253" s="41" t="s">
+      <c r="C253" s="31" t="s">
         <v>728</v>
       </c>
-      <c r="D253" s="40" t="s">
+      <c r="D253" s="30" t="s">
         <v>695</v>
       </c>
-      <c r="E253" s="40" t="s">
+      <c r="E253" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F253" s="40">
+      <c r="F253" s="30">
         <v>21.9918</v>
       </c>
-      <c r="G253" s="40">
+      <c r="G253" s="30">
         <v>105.312599</v>
       </c>
     </row>
     <row r="254" ht="41.4" spans="1:7">
-      <c r="A254" s="39" t="s">
+      <c r="A254" s="29" t="s">
         <v>729</v>
       </c>
-      <c r="B254" s="40" t="s">
+      <c r="B254" s="30" t="s">
         <v>730</v>
       </c>
-      <c r="C254" s="41" t="s">
+      <c r="C254" s="31" t="s">
         <v>722</v>
       </c>
-      <c r="D254" s="40" t="s">
+      <c r="D254" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E254" s="40" t="s">
+      <c r="E254" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F254" s="40">
+      <c r="F254" s="30">
         <v>1</v>
       </c>
-      <c r="G254" s="40">
+      <c r="G254" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="255" ht="41.4" spans="1:7">
-      <c r="A255" s="39" t="s">
+      <c r="A255" s="29" t="s">
         <v>731</v>
       </c>
-      <c r="B255" s="40" t="s">
+      <c r="B255" s="30" t="s">
         <v>732</v>
       </c>
-      <c r="C255" s="41" t="s">
+      <c r="C255" s="31" t="s">
         <v>722</v>
       </c>
-      <c r="D255" s="40" t="s">
+      <c r="D255" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E255" s="40" t="s">
+      <c r="E255" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F255" s="40">
+      <c r="F255" s="30">
         <v>1</v>
       </c>
-      <c r="G255" s="40">
+      <c r="G255" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="256" ht="41.4" spans="1:7">
-      <c r="A256" s="39" t="s">
+      <c r="A256" s="29" t="s">
         <v>733</v>
       </c>
-      <c r="B256" s="40" t="s">
+      <c r="B256" s="30" t="s">
         <v>734</v>
       </c>
-      <c r="C256" s="41" t="s">
+      <c r="C256" s="31" t="s">
         <v>722</v>
       </c>
-      <c r="D256" s="40" t="s">
+      <c r="D256" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E256" s="40" t="s">
+      <c r="E256" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F256" s="40">
+      <c r="F256" s="30">
         <v>1</v>
       </c>
-      <c r="G256" s="40">
+      <c r="G256" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="257" ht="41.4" spans="1:7">
-      <c r="A257" s="39" t="s">
+      <c r="A257" s="29" t="s">
         <v>735</v>
       </c>
-      <c r="B257" s="40" t="s">
+      <c r="B257" s="30" t="s">
         <v>736</v>
       </c>
-      <c r="C257" s="41" t="s">
+      <c r="C257" s="31" t="s">
         <v>722</v>
       </c>
-      <c r="D257" s="40" t="s">
+      <c r="D257" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E257" s="40" t="s">
+      <c r="E257" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F257" s="40">
+      <c r="F257" s="30">
         <v>1</v>
       </c>
-      <c r="G257" s="40">
+      <c r="G257" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="258" ht="41.4" spans="1:7">
-      <c r="A258" s="39" t="s">
+      <c r="A258" s="29" t="s">
         <v>737</v>
       </c>
-      <c r="B258" s="40" t="s">
+      <c r="B258" s="30" t="s">
         <v>738</v>
       </c>
-      <c r="C258" s="41" t="s">
+      <c r="C258" s="31" t="s">
         <v>722</v>
       </c>
-      <c r="D258" s="40" t="s">
+      <c r="D258" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E258" s="40" t="s">
+      <c r="E258" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F258" s="40">
+      <c r="F258" s="30">
         <v>1</v>
       </c>
-      <c r="G258" s="40">
+      <c r="G258" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="259" ht="41.4" spans="1:7">
-      <c r="A259" s="39" t="s">
+      <c r="A259" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="B259" s="40" t="s">
+      <c r="B259" s="30" t="s">
         <v>740</v>
       </c>
-      <c r="C259" s="41" t="s">
+      <c r="C259" s="31" t="s">
         <v>722</v>
       </c>
-      <c r="D259" s="40" t="s">
+      <c r="D259" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E259" s="40" t="s">
+      <c r="E259" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F259" s="40">
+      <c r="F259" s="30">
         <v>1</v>
       </c>
-      <c r="G259" s="40">
+      <c r="G259" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="260" ht="41.4" spans="1:7">
-      <c r="A260" s="39" t="s">
+      <c r="A260" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="B260" s="40" t="s">
+      <c r="B260" s="30" t="s">
         <v>742</v>
       </c>
-      <c r="C260" s="41" t="s">
+      <c r="C260" s="31" t="s">
         <v>722</v>
       </c>
-      <c r="D260" s="40" t="s">
+      <c r="D260" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E260" s="40" t="s">
+      <c r="E260" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F260" s="40">
+      <c r="F260" s="30">
         <v>1</v>
       </c>
-      <c r="G260" s="40">
+      <c r="G260" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="261" ht="179.4" spans="1:7">
-      <c r="A261" s="39" t="s">
+      <c r="A261" s="29" t="s">
         <v>743</v>
       </c>
-      <c r="B261" s="40" t="s">
+      <c r="B261" s="30" t="s">
         <v>744</v>
       </c>
-      <c r="C261" s="41" t="s">
+      <c r="C261" s="31" t="s">
         <v>745</v>
       </c>
-      <c r="D261" s="40" t="s">
+      <c r="D261" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E261" s="40" t="s">
+      <c r="E261" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F261" s="40">
+      <c r="F261" s="30">
         <v>22.830748</v>
       </c>
-      <c r="G261" s="40">
+      <c r="G261" s="30">
         <v>104.98534</v>
       </c>
     </row>
     <row r="262" ht="55.2" spans="1:7">
-      <c r="A262" s="39" t="s">
+      <c r="A262" s="29" t="s">
         <v>746</v>
       </c>
-      <c r="B262" s="40" t="s">
+      <c r="B262" s="30" t="s">
         <v>747</v>
       </c>
-      <c r="C262" s="41" t="s">
+      <c r="C262" s="31" t="s">
         <v>748</v>
       </c>
-      <c r="D262" s="40" t="s">
+      <c r="D262" s="30" t="s">
         <v>703</v>
       </c>
-      <c r="E262" s="40" t="s">
+      <c r="E262" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F262" s="40">
+      <c r="F262" s="30">
         <v>21.548981</v>
       </c>
-      <c r="G262" s="40">
+      <c r="G262" s="30">
         <v>105.31749</v>
       </c>
     </row>
     <row r="263" ht="27.6" spans="1:7">
-      <c r="A263" s="39" t="s">
+      <c r="A263" s="29" t="s">
         <v>749</v>
       </c>
-      <c r="B263" s="40" t="s">
+      <c r="B263" s="30" t="s">
         <v>750</v>
       </c>
-      <c r="C263" s="41" t="s">
+      <c r="C263" s="31" t="s">
         <v>751</v>
       </c>
-      <c r="D263" s="40" t="s">
+      <c r="D263" s="30" t="s">
         <v>695</v>
       </c>
-      <c r="E263" s="40" t="s">
+      <c r="E263" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F263" s="40">
+      <c r="F263" s="30">
         <v>21.7812</v>
       </c>
-      <c r="G263" s="40">
+      <c r="G263" s="30">
         <v>105.185402</v>
       </c>
     </row>
     <row r="264" ht="69" spans="1:7">
-      <c r="A264" s="39" t="s">
+      <c r="A264" s="29" t="s">
         <v>752</v>
       </c>
-      <c r="B264" s="40" t="s">
+      <c r="B264" s="30" t="s">
         <v>753</v>
       </c>
-      <c r="C264" s="41" t="s">
+      <c r="C264" s="31" t="s">
         <v>754</v>
       </c>
-      <c r="D264" s="40" t="s">
+      <c r="D264" s="30" t="s">
         <v>755</v>
       </c>
-      <c r="E264" s="40" t="s">
+      <c r="E264" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F264" s="40">
+      <c r="F264" s="30">
         <v>22.052073</v>
       </c>
-      <c r="G264" s="40">
+      <c r="G264" s="30">
         <v>105.116814</v>
       </c>
     </row>
     <row r="265" ht="69" spans="1:7">
-      <c r="A265" s="39" t="s">
+      <c r="A265" s="29" t="s">
         <v>756</v>
       </c>
-      <c r="B265" s="40" t="s">
+      <c r="B265" s="30" t="s">
         <v>757</v>
       </c>
-      <c r="C265" s="41" t="s">
+      <c r="C265" s="31" t="s">
         <v>758</v>
       </c>
-      <c r="D265" s="40" t="s">
+      <c r="D265" s="30" t="s">
         <v>703</v>
       </c>
-      <c r="E265" s="40" t="s">
+      <c r="E265" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F265" s="40">
+      <c r="F265" s="30">
         <v>21.707808</v>
       </c>
-      <c r="G265" s="40">
+      <c r="G265" s="30">
         <v>105.263786</v>
       </c>
     </row>
     <row r="266" ht="27.6" spans="1:7">
-      <c r="A266" s="39" t="s">
+      <c r="A266" s="29" t="s">
         <v>759</v>
       </c>
-      <c r="B266" s="40" t="s">
+      <c r="B266" s="30" t="s">
         <v>760</v>
       </c>
-      <c r="C266" s="41" t="s">
+      <c r="C266" s="31" t="s">
         <v>761</v>
       </c>
-      <c r="D266" s="40" t="s">
+      <c r="D266" s="30" t="s">
         <v>707</v>
       </c>
-      <c r="E266" s="40" t="s">
+      <c r="E266" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F266" s="40">
+      <c r="F266" s="30">
         <v>21.840565</v>
       </c>
-      <c r="G266" s="40">
+      <c r="G266" s="30">
         <v>105.19619</v>
       </c>
     </row>
     <row r="267" ht="55.2" spans="1:7">
-      <c r="A267" s="39" t="s">
+      <c r="A267" s="29" t="s">
         <v>762</v>
       </c>
-      <c r="B267" s="40" t="s">
+      <c r="B267" s="30" t="s">
         <v>763</v>
       </c>
-      <c r="C267" s="41" t="s">
+      <c r="C267" s="31" t="s">
         <v>764</v>
       </c>
-      <c r="D267" s="40" t="s">
+      <c r="D267" s="30" t="s">
         <v>703</v>
       </c>
-      <c r="E267" s="40" t="s">
+      <c r="E267" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F267" s="40">
+      <c r="F267" s="30">
         <v>21.720547</v>
       </c>
-      <c r="G267" s="40">
+      <c r="G267" s="30">
         <v>105.405602</v>
       </c>
     </row>
     <row r="268" ht="41.4" spans="1:7">
-      <c r="A268" s="39" t="s">
+      <c r="A268" s="29" t="s">
         <v>765</v>
       </c>
-      <c r="B268" s="40" t="s">
+      <c r="B268" s="30" t="s">
         <v>766</v>
       </c>
-      <c r="C268" s="41" t="s">
+      <c r="C268" s="31" t="s">
         <v>767</v>
       </c>
-      <c r="D268" s="40" t="s">
+      <c r="D268" s="30" t="s">
         <v>703</v>
       </c>
-      <c r="E268" s="40" t="s">
+      <c r="E268" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F268" s="40">
+      <c r="F268" s="30">
         <v>21.594042</v>
       </c>
-      <c r="G268" s="40">
+      <c r="G268" s="30">
         <v>105.292412</v>
       </c>
     </row>
     <row r="269" ht="41.4" spans="1:7">
-      <c r="A269" s="39" t="s">
+      <c r="A269" s="29" t="s">
         <v>768</v>
       </c>
-      <c r="B269" s="40" t="s">
+      <c r="B269" s="30" t="s">
         <v>769</v>
       </c>
-      <c r="C269" s="41" t="s">
+      <c r="C269" s="31" t="s">
         <v>770</v>
       </c>
-      <c r="D269" s="40" t="s">
+      <c r="D269" s="30" t="s">
         <v>771</v>
       </c>
-      <c r="E269" s="40" t="s">
+      <c r="E269" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F269" s="40">
+      <c r="F269" s="30">
         <v>21.759022</v>
       </c>
-      <c r="G269" s="40">
+      <c r="G269" s="30">
         <v>105.105736</v>
       </c>
     </row>
     <row r="270" ht="55.2" spans="1:7">
-      <c r="A270" s="39" t="s">
+      <c r="A270" s="29" t="s">
         <v>772</v>
       </c>
-      <c r="B270" s="40" t="s">
+      <c r="B270" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="C270" s="41" t="s">
+      <c r="C270" s="31" t="s">
         <v>774</v>
       </c>
-      <c r="D270" s="40" t="s">
+      <c r="D270" s="30" t="s">
         <v>775</v>
       </c>
-      <c r="E270" s="40" t="s">
+      <c r="E270" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F270" s="40">
+      <c r="F270" s="30">
         <v>21.741411</v>
       </c>
-      <c r="G270" s="40">
+      <c r="G270" s="30">
         <v>105.231201</v>
       </c>
     </row>
     <row r="271" ht="151.8" spans="1:7">
-      <c r="A271" s="39" t="s">
+      <c r="A271" s="29" t="s">
         <v>776</v>
       </c>
-      <c r="B271" s="40" t="s">
+      <c r="B271" s="30" t="s">
         <v>777</v>
       </c>
-      <c r="C271" s="41" t="s">
+      <c r="C271" s="31" t="s">
         <v>778</v>
       </c>
-      <c r="D271" s="40" t="s">
+      <c r="D271" s="30" t="s">
         <v>775</v>
       </c>
-      <c r="E271" s="40" t="s">
+      <c r="E271" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F271" s="40">
+      <c r="F271" s="30">
         <v>21.733482</v>
       </c>
-      <c r="G271" s="40">
+      <c r="G271" s="30">
         <v>105.23231</v>
       </c>
     </row>
     <row r="272" ht="96.6" spans="1:7">
-      <c r="A272" s="39" t="s">
+      <c r="A272" s="29" t="s">
         <v>779</v>
       </c>
-      <c r="B272" s="40" t="s">
+      <c r="B272" s="30" t="s">
         <v>780</v>
       </c>
-      <c r="C272" s="41" t="s">
+      <c r="C272" s="31" t="s">
         <v>781</v>
       </c>
-      <c r="D272" s="40" t="s">
+      <c r="D272" s="30" t="s">
         <v>782</v>
       </c>
-      <c r="E272" s="40" t="s">
+      <c r="E272" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F272" s="40">
+      <c r="F272" s="30">
         <v>23.064776</v>
       </c>
-      <c r="G272" s="40">
+      <c r="G272" s="30">
         <v>104.99103</v>
       </c>
     </row>
     <row r="273" ht="96.6" spans="1:7">
-      <c r="A273" s="39" t="s">
+      <c r="A273" s="29" t="s">
         <v>783</v>
       </c>
-      <c r="B273" s="40" t="s">
+      <c r="B273" s="30" t="s">
         <v>784</v>
       </c>
-      <c r="C273" s="41" t="s">
+      <c r="C273" s="31" t="s">
         <v>785</v>
       </c>
-      <c r="D273" s="40" t="s">
+      <c r="D273" s="30" t="s">
         <v>786</v>
       </c>
-      <c r="E273" s="40" t="s">
+      <c r="E273" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F273" s="40">
+      <c r="F273" s="30">
         <v>23.119403</v>
       </c>
-      <c r="G273" s="40">
+      <c r="G273" s="30">
         <v>105.13737</v>
       </c>
     </row>
     <row r="274" ht="179.4" spans="1:7">
-      <c r="A274" s="39" t="s">
+      <c r="A274" s="29" t="s">
         <v>787</v>
       </c>
-      <c r="B274" s="40" t="s">
+      <c r="B274" s="30" t="s">
         <v>788</v>
       </c>
-      <c r="C274" s="41" t="s">
+      <c r="C274" s="31" t="s">
         <v>789</v>
       </c>
-      <c r="D274" s="40" t="s">
+      <c r="D274" s="30" t="s">
         <v>790</v>
       </c>
-      <c r="E274" s="40" t="s">
+      <c r="E274" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F274" s="40">
+      <c r="F274" s="30">
         <v>23.277016</v>
       </c>
-      <c r="G274" s="40">
+      <c r="G274" s="30">
         <v>105.364295</v>
       </c>
     </row>
     <row r="275" ht="96.6" spans="1:7">
-      <c r="A275" s="39" t="s">
+      <c r="A275" s="29" t="s">
         <v>791</v>
       </c>
-      <c r="B275" s="40" t="s">
+      <c r="B275" s="30" t="s">
         <v>784</v>
       </c>
-      <c r="C275" s="41" t="s">
+      <c r="C275" s="31" t="s">
         <v>785</v>
       </c>
-      <c r="D275" s="40" t="s">
+      <c r="D275" s="30" t="s">
         <v>786</v>
       </c>
-      <c r="E275" s="40" t="s">
+      <c r="E275" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F275" s="40">
+      <c r="F275" s="30">
         <v>23.119403</v>
       </c>
-      <c r="G275" s="40">
+      <c r="G275" s="30">
         <v>105.13737</v>
       </c>
     </row>
     <row r="276" ht="179.4" spans="1:7">
-      <c r="A276" s="39" t="s">
+      <c r="A276" s="29" t="s">
         <v>792</v>
       </c>
-      <c r="B276" s="40" t="s">
+      <c r="B276" s="30" t="s">
         <v>788</v>
       </c>
-      <c r="C276" s="41" t="s">
+      <c r="C276" s="31" t="s">
         <v>789</v>
       </c>
-      <c r="D276" s="40" t="s">
+      <c r="D276" s="30" t="s">
         <v>790</v>
       </c>
-      <c r="E276" s="40" t="s">
+      <c r="E276" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F276" s="40">
+      <c r="F276" s="30">
         <v>23.277016</v>
       </c>
-      <c r="G276" s="40">
+      <c r="G276" s="30">
         <v>105.364295</v>
       </c>
     </row>
     <row r="277" ht="151.8" spans="1:7">
-      <c r="A277" s="39" t="s">
+      <c r="A277" s="29" t="s">
         <v>793</v>
       </c>
-      <c r="B277" s="40" t="s">
+      <c r="B277" s="30" t="s">
         <v>794</v>
       </c>
-      <c r="C277" s="41" t="s">
+      <c r="C277" s="31" t="s">
         <v>795</v>
       </c>
-      <c r="D277" s="40" t="s">
+      <c r="D277" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E277" s="40" t="s">
+      <c r="E277" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F277" s="40">
+      <c r="F277" s="30">
         <v>22.058082</v>
       </c>
-      <c r="G277" s="40">
+      <c r="G277" s="30">
         <v>105.0329</v>
       </c>
     </row>
     <row r="278" ht="138" spans="1:7">
-      <c r="A278" s="39" t="s">
+      <c r="A278" s="29" t="s">
         <v>796</v>
       </c>
-      <c r="B278" s="40" t="s">
+      <c r="B278" s="30" t="s">
         <v>797</v>
       </c>
-      <c r="C278" s="41" t="s">
+      <c r="C278" s="31" t="s">
         <v>798</v>
       </c>
-      <c r="D278" s="40" t="s">
+      <c r="D278" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E278" s="40" t="s">
+      <c r="E278" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F278" s="40">
+      <c r="F278" s="30">
         <v>21.817961</v>
       </c>
-      <c r="G278" s="40">
+      <c r="G278" s="30">
         <v>105.20759</v>
       </c>
     </row>
     <row r="279" ht="124.2" spans="1:7">
-      <c r="A279" s="39" t="s">
+      <c r="A279" s="29" t="s">
         <v>799</v>
       </c>
-      <c r="B279" s="40" t="s">
+      <c r="B279" s="30" t="s">
         <v>800</v>
       </c>
-      <c r="C279" s="41" t="s">
+      <c r="C279" s="31" t="s">
         <v>801</v>
       </c>
-      <c r="D279" s="40" t="s">
+      <c r="D279" s="30" t="s">
         <v>707</v>
       </c>
-      <c r="E279" s="40" t="s">
+      <c r="E279" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F279" s="40">
+      <c r="F279" s="30">
         <v>20.988386</v>
       </c>
-      <c r="G279" s="40">
+      <c r="G279" s="30">
         <v>105.941887</v>
       </c>
     </row>
     <row r="280" ht="124.2" spans="1:7">
-      <c r="A280" s="39" t="s">
+      <c r="A280" s="29" t="s">
         <v>802</v>
       </c>
-      <c r="B280" s="40" t="s">
+      <c r="B280" s="30" t="s">
         <v>800</v>
       </c>
-      <c r="C280" s="41" t="s">
+      <c r="C280" s="31" t="s">
         <v>801</v>
       </c>
-      <c r="D280" s="40" t="s">
+      <c r="D280" s="30" t="s">
         <v>707</v>
       </c>
-      <c r="E280" s="40" t="s">
+      <c r="E280" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F280" s="40">
+      <c r="F280" s="30">
         <v>20.988386</v>
       </c>
-      <c r="G280" s="40">
+      <c r="G280" s="30">
         <v>105.941887</v>
       </c>
     </row>
     <row r="281" ht="41.4" spans="1:7">
-      <c r="A281" s="39" t="s">
+      <c r="A281" s="29" t="s">
         <v>803</v>
       </c>
-      <c r="B281" s="40" t="s">
+      <c r="B281" s="30" t="s">
         <v>804</v>
       </c>
-      <c r="C281" s="41" t="s">
+      <c r="C281" s="31" t="s">
         <v>805</v>
       </c>
-      <c r="D281" s="40" t="s">
+      <c r="D281" s="30" t="s">
         <v>755</v>
       </c>
-      <c r="E281" s="40" t="s">
+      <c r="E281" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F281" s="40">
+      <c r="F281" s="30">
         <v>22.41474</v>
       </c>
-      <c r="G281" s="40">
+      <c r="G281" s="30">
         <v>104.808823</v>
       </c>
     </row>
     <row r="282" ht="69" spans="1:7">
-      <c r="A282" s="39" t="s">
+      <c r="A282" s="29" t="s">
         <v>806</v>
       </c>
-      <c r="B282" s="40" t="s">
+      <c r="B282" s="30" t="s">
         <v>807</v>
       </c>
-      <c r="C282" s="41" t="s">
+      <c r="C282" s="31" t="s">
         <v>808</v>
       </c>
-      <c r="D282" s="40" t="s">
+      <c r="D282" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E282" s="40" t="s">
+      <c r="E282" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F282" s="40">
+      <c r="F282" s="30">
         <v>21.555861</v>
       </c>
-      <c r="G282" s="40">
+      <c r="G282" s="30">
         <v>105.461086</v>
       </c>
     </row>
     <row r="283" ht="41.4" spans="1:7">
-      <c r="A283" s="39" t="s">
+      <c r="A283" s="29" t="s">
         <v>809</v>
       </c>
-      <c r="B283" s="40" t="s">
+      <c r="B283" s="30" t="s">
         <v>810</v>
       </c>
-      <c r="C283" s="41" t="s">
+      <c r="C283" s="31" t="s">
         <v>811</v>
       </c>
-      <c r="D283" s="40" t="s">
+      <c r="D283" s="30" t="s">
         <v>719</v>
       </c>
-      <c r="E283" s="40" t="s">
+      <c r="E283" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F283" s="40">
+      <c r="F283" s="30">
         <v>22.14478</v>
       </c>
-      <c r="G283" s="40">
+      <c r="G283" s="30">
         <v>105.25837</v>
       </c>
     </row>
     <row r="284" ht="41.4" spans="1:7">
-      <c r="A284" s="39" t="s">
+      <c r="A284" s="29" t="s">
         <v>812</v>
       </c>
-      <c r="B284" s="40" t="s">
+      <c r="B284" s="30" t="s">
         <v>813</v>
       </c>
-      <c r="C284" s="41" t="s">
+      <c r="C284" s="31" t="s">
         <v>722</v>
       </c>
-      <c r="D284" s="40" t="s">
+      <c r="D284" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E284" s="40" t="s">
+      <c r="E284" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F284" s="40">
+      <c r="F284" s="30">
         <v>1</v>
       </c>
-      <c r="G284" s="40">
+      <c r="G284" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="285" ht="151.8" spans="1:7">
-      <c r="A285" s="39" t="s">
+      <c r="A285" s="29" t="s">
         <v>814</v>
       </c>
-      <c r="B285" s="40" t="s">
+      <c r="B285" s="30" t="s">
         <v>794</v>
       </c>
-      <c r="C285" s="41" t="s">
+      <c r="C285" s="31" t="s">
         <v>795</v>
       </c>
-      <c r="D285" s="40" t="s">
+      <c r="D285" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E285" s="40" t="s">
+      <c r="E285" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F285" s="40">
+      <c r="F285" s="30">
         <v>22.058082</v>
       </c>
-      <c r="G285" s="40">
+      <c r="G285" s="30">
         <v>105.0329</v>
       </c>
     </row>
     <row r="286" ht="138" spans="1:7">
-      <c r="A286" s="39" t="s">
+      <c r="A286" s="29" t="s">
         <v>815</v>
       </c>
-      <c r="B286" s="40" t="s">
+      <c r="B286" s="30" t="s">
         <v>797</v>
       </c>
-      <c r="C286" s="41" t="s">
+      <c r="C286" s="31" t="s">
         <v>798</v>
       </c>
-      <c r="D286" s="40" t="s">
+      <c r="D286" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E286" s="40" t="s">
+      <c r="E286" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F286" s="40">
+      <c r="F286" s="30">
         <v>21.817961</v>
       </c>
-      <c r="G286" s="40">
+      <c r="G286" s="30">
         <v>105.20759</v>
       </c>
     </row>
     <row r="287" ht="27.6" spans="1:7">
-      <c r="A287" s="39" t="s">
+      <c r="A287" s="29" t="s">
         <v>816</v>
       </c>
-      <c r="B287" s="40" t="s">
+      <c r="B287" s="30" t="s">
         <v>817</v>
       </c>
-      <c r="C287" s="41" t="s">
+      <c r="C287" s="31" t="s">
         <v>818</v>
       </c>
-      <c r="D287" s="40" t="s">
+      <c r="D287" s="30" t="s">
         <v>703</v>
       </c>
-      <c r="E287" s="40" t="s">
+      <c r="E287" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F287" s="40">
+      <c r="F287" s="30">
         <v>21.6422</v>
       </c>
-      <c r="G287" s="40">
+      <c r="G287" s="30">
         <v>105.382797</v>
       </c>
     </row>
     <row r="288" ht="110.4" spans="1:7">
-      <c r="A288" s="39" t="s">
+      <c r="A288" s="29" t="s">
         <v>819</v>
       </c>
-      <c r="B288" s="40" t="s">
+      <c r="B288" s="30" t="s">
         <v>820</v>
       </c>
-      <c r="C288" s="41" t="s">
+      <c r="C288" s="31" t="s">
         <v>821</v>
       </c>
-      <c r="D288" s="40" t="s">
+      <c r="D288" s="30" t="s">
         <v>822</v>
       </c>
-      <c r="E288" s="40" t="s">
+      <c r="E288" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F288" s="40">
+      <c r="F288" s="30">
         <v>21.814473</v>
       </c>
-      <c r="G288" s="40">
+      <c r="G288" s="30">
         <v>105.209279</v>
       </c>
     </row>
     <row r="289" ht="55.2" spans="1:7">
-      <c r="A289" s="39" t="s">
+      <c r="A289" s="29" t="s">
         <v>823</v>
       </c>
-      <c r="B289" s="40" t="s">
+      <c r="B289" s="30" t="s">
         <v>773</v>
       </c>
-      <c r="C289" s="41" t="s">
+      <c r="C289" s="31" t="s">
         <v>774</v>
       </c>
-      <c r="D289" s="40" t="s">
+      <c r="D289" s="30" t="s">
         <v>775</v>
       </c>
-      <c r="E289" s="40" t="s">
+      <c r="E289" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F289" s="40">
+      <c r="F289" s="30">
         <v>21.741411</v>
       </c>
-      <c r="G289" s="40">
+      <c r="G289" s="30">
         <v>105.231201</v>
       </c>
     </row>
     <row r="290" ht="69" spans="1:7">
-      <c r="A290" s="39" t="s">
+      <c r="A290" s="29" t="s">
         <v>824</v>
       </c>
-      <c r="B290" s="40" t="s">
+      <c r="B290" s="30" t="s">
         <v>825</v>
       </c>
-      <c r="C290" s="41" t="s">
+      <c r="C290" s="31" t="s">
         <v>826</v>
       </c>
-      <c r="D290" s="40" t="s">
+      <c r="D290" s="30" t="s">
         <v>695</v>
       </c>
-      <c r="E290" s="40" t="s">
+      <c r="E290" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F290" s="40">
+      <c r="F290" s="30">
         <v>21.672562</v>
       </c>
-      <c r="G290" s="40">
+      <c r="G290" s="30">
         <v>105.210373</v>
       </c>
     </row>
     <row r="291" ht="151.8" spans="1:7">
-      <c r="A291" s="42" t="s">
+      <c r="A291" s="32" t="s">
         <v>827</v>
       </c>
-      <c r="B291" s="40" t="s">
+      <c r="B291" s="30" t="s">
         <v>828</v>
       </c>
-      <c r="C291" s="41" t="s">
+      <c r="C291" s="31" t="s">
         <v>829</v>
       </c>
-      <c r="D291" s="40" t="s">
+      <c r="D291" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E291" s="40" t="s">
+      <c r="E291" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F291" s="40">
+      <c r="F291" s="30">
         <v>22.82121</v>
       </c>
-      <c r="G291" s="40">
+      <c r="G291" s="30">
         <v>104.9874</v>
       </c>
     </row>
     <row r="292" ht="151.8" spans="1:7">
-      <c r="A292" s="42" t="s">
+      <c r="A292" s="32" t="s">
         <v>830</v>
       </c>
-      <c r="B292" s="40" t="s">
+      <c r="B292" s="30" t="s">
         <v>831</v>
       </c>
-      <c r="C292" s="41" t="s">
+      <c r="C292" s="31" t="s">
         <v>832</v>
       </c>
-      <c r="D292" s="40" t="s">
+      <c r="D292" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E292" s="40" t="s">
+      <c r="E292" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F292" s="40">
+      <c r="F292" s="30">
         <v>22.84116</v>
       </c>
-      <c r="G292" s="40">
+      <c r="G292" s="30">
         <v>105.0001</v>
       </c>
     </row>
     <row r="293" ht="69" spans="1:7">
-      <c r="A293" s="42" t="s">
+      <c r="A293" s="32" t="s">
         <v>833</v>
       </c>
-      <c r="B293" s="40" t="s">
+      <c r="B293" s="30" t="s">
         <v>834</v>
       </c>
-      <c r="C293" s="41" t="s">
+      <c r="C293" s="31" t="s">
         <v>835</v>
       </c>
-      <c r="D293" s="40" t="s">
+      <c r="D293" s="30" t="s">
         <v>755</v>
       </c>
-      <c r="E293" s="40" t="s">
+      <c r="E293" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F293" s="40">
+      <c r="F293" s="30">
         <v>22.072248</v>
       </c>
-      <c r="G293" s="40">
+      <c r="G293" s="30">
         <v>105.03269</v>
       </c>
     </row>
     <row r="294" ht="110.4" spans="1:7">
-      <c r="A294" s="42" t="s">
+      <c r="A294" s="32" t="s">
         <v>836</v>
       </c>
-      <c r="B294" s="40" t="s">
+      <c r="B294" s="30" t="s">
         <v>837</v>
       </c>
-      <c r="C294" s="41" t="s">
+      <c r="C294" s="31" t="s">
         <v>838</v>
       </c>
-      <c r="D294" s="40" t="s">
+      <c r="D294" s="30" t="s">
         <v>703</v>
       </c>
-      <c r="E294" s="40" t="s">
+      <c r="E294" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F294" s="40">
+      <c r="F294" s="30">
         <v>21.701799</v>
       </c>
-      <c r="G294" s="40">
+      <c r="G294" s="30">
         <v>105.369263</v>
       </c>
     </row>
     <row r="295" ht="110.4" spans="1:7">
-      <c r="A295" s="42" t="s">
+      <c r="A295" s="32" t="s">
         <v>839</v>
       </c>
-      <c r="B295" s="40" t="s">
+      <c r="B295" s="30" t="s">
         <v>840</v>
       </c>
-      <c r="C295" s="41" t="s">
+      <c r="C295" s="31" t="s">
         <v>841</v>
       </c>
-      <c r="D295" s="40" t="s">
+      <c r="D295" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E295" s="40" t="s">
+      <c r="E295" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F295" s="40">
+      <c r="F295" s="30">
         <v>21.792997</v>
       </c>
-      <c r="G295" s="40">
+      <c r="G295" s="30">
         <v>105.218974</v>
       </c>
     </row>
     <row r="296" ht="151.8" spans="1:7">
-      <c r="A296" s="42" t="s">
+      <c r="A296" s="32" t="s">
         <v>842</v>
       </c>
-      <c r="B296" s="40" t="s">
+      <c r="B296" s="30" t="s">
         <v>843</v>
       </c>
-      <c r="C296" s="41" t="s">
+      <c r="C296" s="31" t="s">
         <v>844</v>
       </c>
-      <c r="D296" s="40" t="s">
+      <c r="D296" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E296" s="40" t="s">
+      <c r="E296" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F296" s="40">
+      <c r="F296" s="30">
         <v>22.82818</v>
       </c>
-      <c r="G296" s="40">
+      <c r="G296" s="30">
         <v>104.9876</v>
       </c>
     </row>
     <row r="297" ht="124.2" spans="1:7">
-      <c r="A297" s="42" t="s">
+      <c r="A297" s="32" t="s">
         <v>845</v>
       </c>
-      <c r="B297" s="40" t="s">
+      <c r="B297" s="30" t="s">
         <v>709</v>
       </c>
-      <c r="C297" s="41" t="s">
+      <c r="C297" s="31" t="s">
         <v>710</v>
       </c>
-      <c r="D297" s="40" t="s">
+      <c r="D297" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E297" s="40" t="s">
+      <c r="E297" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F297" s="40">
+      <c r="F297" s="30">
         <v>21.696782</v>
       </c>
-      <c r="G297" s="40">
+      <c r="G297" s="30">
         <v>105.39147</v>
       </c>
     </row>
     <row r="298" ht="165.6" spans="1:7">
-      <c r="A298" s="42" t="s">
+      <c r="A298" s="32" t="s">
         <v>846</v>
       </c>
-      <c r="B298" s="40" t="s">
+      <c r="B298" s="30" t="s">
         <v>847</v>
       </c>
-      <c r="C298" s="41" t="s">
+      <c r="C298" s="31" t="s">
         <v>848</v>
       </c>
-      <c r="D298" s="40" t="s">
+      <c r="D298" s="30" t="s">
         <v>849</v>
       </c>
-      <c r="E298" s="40" t="s">
+      <c r="E298" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F298" s="40">
+      <c r="F298" s="30">
         <v>21.795111</v>
       </c>
-      <c r="G298" s="40">
+      <c r="G298" s="30">
         <v>105.21508</v>
       </c>
     </row>
     <row r="299" ht="55.2" spans="1:7">
-      <c r="A299" s="42" t="s">
+      <c r="A299" s="32" t="s">
         <v>850</v>
       </c>
-      <c r="B299" s="40" t="s">
+      <c r="B299" s="30" t="s">
         <v>851</v>
       </c>
-      <c r="C299" s="41" t="s">
+      <c r="C299" s="31" t="s">
         <v>852</v>
       </c>
-      <c r="D299" s="40" t="s">
+      <c r="D299" s="30" t="s">
         <v>715</v>
       </c>
-      <c r="E299" s="40" t="s">
+      <c r="E299" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F299" s="40">
+      <c r="F299" s="30">
         <v>23.182599</v>
       </c>
-      <c r="G299" s="40">
+      <c r="G299" s="30">
         <v>105.412022</v>
       </c>
     </row>
     <row r="300" ht="82.8" spans="1:7">
-      <c r="A300" s="42" t="s">
+      <c r="A300" s="32" t="s">
         <v>853</v>
       </c>
-      <c r="B300" s="40" t="s">
+      <c r="B300" s="30" t="s">
         <v>854</v>
       </c>
-      <c r="C300" s="41" t="s">
+      <c r="C300" s="31" t="s">
         <v>855</v>
       </c>
-      <c r="D300" s="40" t="s">
+      <c r="D300" s="30" t="s">
         <v>715</v>
       </c>
-      <c r="E300" s="40" t="s">
+      <c r="E300" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F300" s="40">
+      <c r="F300" s="30">
         <v>21.983817</v>
       </c>
-      <c r="G300" s="40">
+      <c r="G300" s="30">
         <v>105.09352</v>
       </c>
     </row>
     <row r="301" ht="110.4" spans="1:7">
-      <c r="A301" s="42" t="s">
+      <c r="A301" s="32" t="s">
         <v>856</v>
       </c>
-      <c r="B301" s="40" t="s">
+      <c r="B301" s="30" t="s">
         <v>857</v>
       </c>
-      <c r="C301" s="41" t="s">
+      <c r="C301" s="31" t="s">
         <v>858</v>
       </c>
-      <c r="D301" s="40" t="s">
+      <c r="D301" s="30" t="s">
         <v>715</v>
       </c>
-      <c r="E301" s="40" t="s">
+      <c r="E301" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F301" s="40">
+      <c r="F301" s="30">
         <v>21.771169</v>
       </c>
-      <c r="G301" s="40">
+      <c r="G301" s="30">
         <v>105.21401</v>
       </c>
     </row>
     <row r="302" ht="124.2" spans="1:7">
-      <c r="A302" s="42" t="s">
+      <c r="A302" s="32" t="s">
         <v>859</v>
       </c>
-      <c r="B302" s="40" t="s">
+      <c r="B302" s="30" t="s">
         <v>860</v>
       </c>
-      <c r="C302" s="41" t="s">
+      <c r="C302" s="31" t="s">
         <v>861</v>
       </c>
-      <c r="D302" s="40" t="s">
+      <c r="D302" s="30" t="s">
         <v>711</v>
       </c>
-      <c r="E302" s="40" t="s">
+      <c r="E302" s="30" t="s">
         <v>696</v>
       </c>
-      <c r="F302" s="40">
+      <c r="F302" s="30">
         <v>21.7221</v>
       </c>
-      <c r="G302" s="40">
+      <c r="G302" s="30">
         <v>105.2309</v>
+      </c>
+    </row>
+    <row r="303" ht="41.4" spans="1:7">
+      <c r="A303" s="39" t="s">
+        <v>862</v>
+      </c>
+      <c r="B303" s="40" t="s">
+        <v>863</v>
+      </c>
+      <c r="C303" s="41" t="s">
+        <v>864</v>
+      </c>
+      <c r="D303" s="40" t="s">
+        <v>865</v>
+      </c>
+      <c r="E303" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F303" s="40">
+        <v>20.518473</v>
+      </c>
+      <c r="G303" s="40">
+        <v>105.873314</v>
+      </c>
+    </row>
+    <row r="304" ht="55.2" spans="1:7">
+      <c r="A304" s="39" t="s">
+        <v>867</v>
+      </c>
+      <c r="B304" s="40" t="s">
+        <v>868</v>
+      </c>
+      <c r="C304" s="41" t="s">
+        <v>869</v>
+      </c>
+      <c r="D304" s="40" t="s">
+        <v>870</v>
+      </c>
+      <c r="E304" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F304" s="40">
+        <v>20.522057</v>
+      </c>
+      <c r="G304" s="40">
+        <v>105.978264</v>
+      </c>
+    </row>
+    <row r="305" ht="41.4" spans="1:7">
+      <c r="A305" s="39" t="s">
+        <v>871</v>
+      </c>
+      <c r="B305" s="40" t="s">
+        <v>872</v>
+      </c>
+      <c r="C305" s="41" t="s">
+        <v>873</v>
+      </c>
+      <c r="D305" s="40" t="s">
+        <v>870</v>
+      </c>
+      <c r="E305" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F305" s="40">
+        <v>20.425751</v>
+      </c>
+      <c r="G305" s="40">
+        <v>105.917427</v>
+      </c>
+    </row>
+    <row r="306" ht="96.6" spans="1:7">
+      <c r="A306" s="39" t="s">
+        <v>874</v>
+      </c>
+      <c r="B306" s="40" t="s">
+        <v>875</v>
+      </c>
+      <c r="C306" s="41" t="s">
+        <v>876</v>
+      </c>
+      <c r="D306" s="40" t="s">
+        <v>865</v>
+      </c>
+      <c r="E306" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F306" s="40">
+        <v>20.566553</v>
+      </c>
+      <c r="G306" s="40">
+        <v>105.882828</v>
+      </c>
+    </row>
+    <row r="307" ht="69" spans="1:7">
+      <c r="A307" s="39" t="s">
+        <v>877</v>
+      </c>
+      <c r="B307" s="40" t="s">
+        <v>878</v>
+      </c>
+      <c r="C307" s="41" t="s">
+        <v>879</v>
+      </c>
+      <c r="D307" s="40" t="s">
+        <v>880</v>
+      </c>
+      <c r="E307" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F307" s="40">
+        <v>20.644224</v>
+      </c>
+      <c r="G307" s="40">
+        <v>105.925468</v>
+      </c>
+    </row>
+    <row r="308" ht="82.8" spans="1:7">
+      <c r="A308" s="39" t="s">
+        <v>881</v>
+      </c>
+      <c r="B308" s="40" t="s">
+        <v>882</v>
+      </c>
+      <c r="C308" s="41" t="s">
+        <v>883</v>
+      </c>
+      <c r="D308" s="40" t="s">
+        <v>884</v>
+      </c>
+      <c r="E308" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F308" s="40">
+        <v>20.561029</v>
+      </c>
+      <c r="G308" s="40">
+        <v>106.034019</v>
+      </c>
+    </row>
+    <row r="309" ht="55.2" spans="1:7">
+      <c r="A309" s="39" t="s">
+        <v>885</v>
+      </c>
+      <c r="B309" s="40" t="s">
+        <v>886</v>
+      </c>
+      <c r="C309" s="41" t="s">
+        <v>887</v>
+      </c>
+      <c r="D309" s="40" t="s">
+        <v>870</v>
+      </c>
+      <c r="E309" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F309" s="40">
+        <v>20.38341</v>
+      </c>
+      <c r="G309" s="40">
+        <v>105.919899</v>
+      </c>
+    </row>
+    <row r="310" ht="96.6" spans="1:7">
+      <c r="A310" s="39" t="s">
+        <v>888</v>
+      </c>
+      <c r="B310" s="40" t="s">
+        <v>889</v>
+      </c>
+      <c r="C310" s="41" t="s">
+        <v>890</v>
+      </c>
+      <c r="D310" s="40" t="s">
+        <v>865</v>
+      </c>
+      <c r="E310" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F310" s="40">
+        <v>20.641226</v>
+      </c>
+      <c r="G310" s="40">
+        <v>105.895309</v>
+      </c>
+    </row>
+    <row r="311" ht="69" spans="1:7">
+      <c r="A311" s="39" t="s">
+        <v>891</v>
+      </c>
+      <c r="B311" s="40" t="s">
+        <v>892</v>
+      </c>
+      <c r="C311" s="41" t="s">
+        <v>893</v>
+      </c>
+      <c r="D311" s="40" t="s">
+        <v>865</v>
+      </c>
+      <c r="E311" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F311" s="40">
+        <v>20.638803</v>
+      </c>
+      <c r="G311" s="40">
+        <v>105.898026</v>
+      </c>
+    </row>
+    <row r="312" ht="27.6" spans="1:7">
+      <c r="A312" s="39" t="s">
+        <v>894</v>
+      </c>
+      <c r="B312" s="40" t="s">
+        <v>895</v>
+      </c>
+      <c r="C312" s="41" t="s">
+        <v>896</v>
+      </c>
+      <c r="D312" s="40" t="s">
+        <v>897</v>
+      </c>
+      <c r="E312" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F312" s="40">
+        <v>20.510113</v>
+      </c>
+      <c r="G312" s="40">
+        <v>106.002357</v>
+      </c>
+    </row>
+    <row r="313" ht="82.8" spans="1:7">
+      <c r="A313" s="39" t="s">
+        <v>898</v>
+      </c>
+      <c r="B313" s="40" t="s">
+        <v>899</v>
+      </c>
+      <c r="C313" s="41" t="s">
+        <v>900</v>
+      </c>
+      <c r="D313" s="40" t="s">
+        <v>865</v>
+      </c>
+      <c r="E313" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F313" s="40">
+        <v>20.649221</v>
+      </c>
+      <c r="G313" s="40">
+        <v>105.8414</v>
+      </c>
+    </row>
+    <row r="314" ht="207" spans="1:7">
+      <c r="A314" s="39" t="s">
+        <v>901</v>
+      </c>
+      <c r="B314" s="40" t="s">
+        <v>902</v>
+      </c>
+      <c r="C314" s="41" t="s">
+        <v>903</v>
+      </c>
+      <c r="D314" s="40" t="s">
+        <v>904</v>
+      </c>
+      <c r="E314" s="40" t="s">
+        <v>866</v>
+      </c>
+      <c r="F314" s="40">
+        <v>20.5214</v>
+      </c>
+      <c r="G314" s="40">
+        <v>105.944702</v>
+      </c>
+    </row>
+    <row r="315" ht="69" spans="1:7">
+      <c r="A315" s="39" t="s">
+        <v>905</v>
+      </c>
+      <c r="B315" s="40" t="s">
+        <v>906</v>
+      </c>
+      <c r="C315" s="41" t="s">
+        <v>907</v>
+      </c>
+      <c r="D315" s="40" t="s">
+        <v>908</v>
+      </c>
+      <c r="E315" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F315" s="40">
+        <v>20.876547</v>
+      </c>
+      <c r="G315" s="40">
+        <v>105.54071</v>
+      </c>
+    </row>
+    <row r="316" ht="96.6" spans="1:7">
+      <c r="A316" s="39" t="s">
+        <v>910</v>
+      </c>
+      <c r="B316" s="40" t="s">
+        <v>911</v>
+      </c>
+      <c r="C316" s="41" t="s">
+        <v>912</v>
+      </c>
+      <c r="D316" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E316" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F316" s="40">
+        <v>20.80588</v>
+      </c>
+      <c r="G316" s="40">
+        <v>105.334831</v>
+      </c>
+    </row>
+    <row r="317" ht="69" spans="1:7">
+      <c r="A317" s="39" t="s">
+        <v>914</v>
+      </c>
+      <c r="B317" s="40" t="s">
+        <v>915</v>
+      </c>
+      <c r="C317" s="41" t="s">
+        <v>916</v>
+      </c>
+      <c r="D317" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E317" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F317" s="40">
+        <v>20.870747</v>
+      </c>
+      <c r="G317" s="40">
+        <v>105.34713</v>
+      </c>
+    </row>
+    <row r="318" ht="41.4" spans="1:7">
+      <c r="A318" s="39" t="s">
+        <v>917</v>
+      </c>
+      <c r="B318" s="40" t="s">
+        <v>918</v>
+      </c>
+      <c r="C318" s="41" t="s">
+        <v>919</v>
+      </c>
+      <c r="D318" s="40" t="s">
+        <v>920</v>
+      </c>
+      <c r="E318" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F318" s="40">
+        <v>20.495459</v>
+      </c>
+      <c r="G318" s="40">
+        <v>105.777023</v>
+      </c>
+    </row>
+    <row r="319" ht="55.2" spans="1:7">
+      <c r="A319" s="39" t="s">
+        <v>921</v>
+      </c>
+      <c r="B319" s="40" t="s">
+        <v>922</v>
+      </c>
+      <c r="C319" s="41" t="s">
+        <v>923</v>
+      </c>
+      <c r="D319" s="40" t="s">
+        <v>924</v>
+      </c>
+      <c r="E319" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F319" s="40">
+        <v>20.752348</v>
+      </c>
+      <c r="G319" s="40">
+        <v>105.464645</v>
+      </c>
+    </row>
+    <row r="320" ht="41.4" spans="1:7">
+      <c r="A320" s="39" t="s">
+        <v>925</v>
+      </c>
+      <c r="B320" s="40" t="s">
+        <v>926</v>
+      </c>
+      <c r="C320" s="41" t="s">
+        <v>927</v>
+      </c>
+      <c r="D320" s="40" t="s">
+        <v>928</v>
+      </c>
+      <c r="E320" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F320" s="40">
+        <v>20.864719</v>
+      </c>
+      <c r="G320" s="40">
+        <v>105.176079</v>
+      </c>
+    </row>
+    <row r="321" ht="55.2" spans="1:7">
+      <c r="A321" s="39" t="s">
+        <v>929</v>
+      </c>
+      <c r="B321" s="40" t="s">
+        <v>930</v>
+      </c>
+      <c r="C321" s="41" t="s">
+        <v>931</v>
+      </c>
+      <c r="D321" s="40" t="s">
+        <v>924</v>
+      </c>
+      <c r="E321" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F321" s="40">
+        <v>20.580269</v>
+      </c>
+      <c r="G321" s="40">
+        <v>105.63298</v>
+      </c>
+    </row>
+    <row r="322" ht="27.6" spans="1:7">
+      <c r="A322" s="39" t="s">
+        <v>932</v>
+      </c>
+      <c r="B322" s="40" t="s">
+        <v>933</v>
+      </c>
+      <c r="C322" s="41" t="s">
+        <v>934</v>
+      </c>
+      <c r="D322" s="40" t="s">
+        <v>908</v>
+      </c>
+      <c r="E322" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F322" s="40">
+        <v>20.988249</v>
+      </c>
+      <c r="G322" s="40">
+        <v>105.408897</v>
+      </c>
+    </row>
+    <row r="323" ht="41.4" spans="1:7">
+      <c r="A323" s="39" t="s">
+        <v>935</v>
+      </c>
+      <c r="B323" s="40" t="s">
+        <v>936</v>
+      </c>
+      <c r="C323" s="41" t="s">
+        <v>937</v>
+      </c>
+      <c r="D323" s="40" t="s">
+        <v>924</v>
+      </c>
+      <c r="E323" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F323" s="40">
+        <v>20.659927</v>
+      </c>
+      <c r="G323" s="40">
+        <v>105.535889</v>
+      </c>
+    </row>
+    <row r="324" ht="69" spans="1:7">
+      <c r="A324" s="39" t="s">
+        <v>938</v>
+      </c>
+      <c r="B324" s="40" t="s">
+        <v>939</v>
+      </c>
+      <c r="C324" s="41" t="s">
+        <v>940</v>
+      </c>
+      <c r="D324" s="40" t="s">
+        <v>941</v>
+      </c>
+      <c r="E324" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F324" s="40">
+        <v>20.751209</v>
+      </c>
+      <c r="G324" s="40">
+        <v>105.331757</v>
+      </c>
+    </row>
+    <row r="325" ht="55.2" spans="1:7">
+      <c r="A325" s="39" t="s">
+        <v>942</v>
+      </c>
+      <c r="B325" s="40" t="s">
+        <v>943</v>
+      </c>
+      <c r="C325" s="41" t="s">
+        <v>944</v>
+      </c>
+      <c r="D325" s="40" t="s">
+        <v>945</v>
+      </c>
+      <c r="E325" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F325" s="40">
+        <v>20.704571</v>
+      </c>
+      <c r="G325" s="40">
+        <v>105.071877</v>
+      </c>
+    </row>
+    <row r="326" ht="110.4" spans="1:7">
+      <c r="A326" s="39" t="s">
+        <v>946</v>
+      </c>
+      <c r="B326" s="40" t="s">
+        <v>947</v>
+      </c>
+      <c r="C326" s="41" t="s">
+        <v>948</v>
+      </c>
+      <c r="D326" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E326" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F326" s="40">
+        <v>20.825741</v>
+      </c>
+      <c r="G326" s="40">
+        <v>105.351257</v>
+      </c>
+    </row>
+    <row r="327" ht="82.8" spans="1:7">
+      <c r="A327" s="39" t="s">
+        <v>949</v>
+      </c>
+      <c r="B327" s="40" t="s">
+        <v>950</v>
+      </c>
+      <c r="C327" s="41" t="s">
+        <v>951</v>
+      </c>
+      <c r="D327" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E327" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F327" s="40">
+        <v>20.826073</v>
+      </c>
+      <c r="G327" s="40">
+        <v>105.351044</v>
+      </c>
+    </row>
+    <row r="328" ht="138" spans="1:7">
+      <c r="A328" s="39" t="s">
+        <v>952</v>
+      </c>
+      <c r="B328" s="40" t="s">
+        <v>953</v>
+      </c>
+      <c r="C328" s="41" t="s">
+        <v>954</v>
+      </c>
+      <c r="D328" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E328" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F328" s="40">
+        <v>20.826048</v>
+      </c>
+      <c r="G328" s="40">
+        <v>105.351349</v>
+      </c>
+    </row>
+    <row r="329" ht="110.4" spans="1:7">
+      <c r="A329" s="39" t="s">
+        <v>955</v>
+      </c>
+      <c r="B329" s="40" t="s">
+        <v>947</v>
+      </c>
+      <c r="C329" s="41" t="s">
+        <v>948</v>
+      </c>
+      <c r="D329" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E329" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F329" s="40">
+        <v>20.825741</v>
+      </c>
+      <c r="G329" s="40">
+        <v>105.351257</v>
+      </c>
+    </row>
+    <row r="330" ht="138" spans="1:7">
+      <c r="A330" s="39" t="s">
+        <v>956</v>
+      </c>
+      <c r="B330" s="40" t="s">
+        <v>953</v>
+      </c>
+      <c r="C330" s="41" t="s">
+        <v>954</v>
+      </c>
+      <c r="D330" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E330" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F330" s="40">
+        <v>20.826048</v>
+      </c>
+      <c r="G330" s="40">
+        <v>105.351349</v>
+      </c>
+    </row>
+    <row r="331" ht="193.2" spans="1:7">
+      <c r="A331" s="39" t="s">
+        <v>957</v>
+      </c>
+      <c r="B331" s="40" t="s">
+        <v>958</v>
+      </c>
+      <c r="C331" s="41" t="s">
+        <v>959</v>
+      </c>
+      <c r="D331" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E331" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F331" s="40">
+        <v>20.825741</v>
+      </c>
+      <c r="G331" s="40">
+        <v>105.351257</v>
+      </c>
+    </row>
+    <row r="332" ht="41.4" spans="1:7">
+      <c r="A332" s="39" t="s">
+        <v>960</v>
+      </c>
+      <c r="B332" s="40" t="s">
+        <v>961</v>
+      </c>
+      <c r="C332" s="41" t="s">
+        <v>962</v>
+      </c>
+      <c r="D332" s="40" t="s">
+        <v>963</v>
+      </c>
+      <c r="E332" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F332" s="40">
+        <v>20.432171</v>
+      </c>
+      <c r="G332" s="40">
+        <v>105.625237</v>
+      </c>
+    </row>
+    <row r="333" ht="69" spans="1:7">
+      <c r="A333" s="39" t="s">
+        <v>964</v>
+      </c>
+      <c r="B333" s="40" t="s">
+        <v>965</v>
+      </c>
+      <c r="C333" s="41" t="s">
+        <v>966</v>
+      </c>
+      <c r="D333" s="40" t="s">
+        <v>945</v>
+      </c>
+      <c r="E333" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F333" s="40">
+        <v>20.71911</v>
+      </c>
+      <c r="G333" s="40">
+        <v>104.998421</v>
+      </c>
+    </row>
+    <row r="334" ht="69" spans="1:7">
+      <c r="A334" s="39" t="s">
+        <v>967</v>
+      </c>
+      <c r="B334" s="40" t="s">
+        <v>968</v>
+      </c>
+      <c r="C334" s="41" t="s">
+        <v>969</v>
+      </c>
+      <c r="D334" s="40" t="s">
+        <v>963</v>
+      </c>
+      <c r="E334" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F334" s="40">
+        <v>20.403189</v>
+      </c>
+      <c r="G334" s="40">
+        <v>105.587524</v>
+      </c>
+    </row>
+    <row r="335" ht="41.4" spans="1:7">
+      <c r="A335" s="42" t="s">
+        <v>970</v>
+      </c>
+      <c r="B335" s="40" t="s">
+        <v>971</v>
+      </c>
+      <c r="C335" s="41" t="s">
+        <v>972</v>
+      </c>
+      <c r="D335" s="40" t="s">
+        <v>913</v>
+      </c>
+      <c r="E335" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F335" s="40">
+        <v>20.817225</v>
+      </c>
+      <c r="G335" s="40">
+        <v>105.353378</v>
+      </c>
+    </row>
+    <row r="336" ht="96.6" spans="1:7">
+      <c r="A336" s="42" t="s">
+        <v>973</v>
+      </c>
+      <c r="B336" s="40" t="s">
+        <v>974</v>
+      </c>
+      <c r="C336" s="41" t="s">
+        <v>975</v>
+      </c>
+      <c r="D336" s="40" t="s">
+        <v>976</v>
+      </c>
+      <c r="E336" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F336" s="40">
+        <v>20.619947</v>
+      </c>
+      <c r="G336" s="40">
+        <v>105.27462</v>
+      </c>
+    </row>
+    <row r="337" ht="69" spans="1:7">
+      <c r="A337" s="39" t="s">
+        <v>977</v>
+      </c>
+      <c r="B337" s="40" t="s">
+        <v>978</v>
+      </c>
+      <c r="C337" s="41" t="s">
+        <v>979</v>
+      </c>
+      <c r="D337" s="40" t="s">
+        <v>980</v>
+      </c>
+      <c r="E337" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F337" s="40">
+        <v>21.41444</v>
+      </c>
+      <c r="G337" s="40">
+        <v>105.577614</v>
+      </c>
+    </row>
+    <row r="338" ht="41.4" spans="1:7">
+      <c r="A338" s="39" t="s">
+        <v>981</v>
+      </c>
+      <c r="B338" s="40" t="s">
+        <v>982</v>
+      </c>
+      <c r="C338" s="41" t="s">
+        <v>983</v>
+      </c>
+      <c r="D338" s="40" t="s">
+        <v>984</v>
+      </c>
+      <c r="E338" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F338" s="40">
+        <v>21.368959</v>
+      </c>
+      <c r="G338" s="40">
+        <v>105.606903</v>
+      </c>
+    </row>
+    <row r="339" ht="41.4" spans="1:7">
+      <c r="A339" s="39" t="s">
+        <v>985</v>
+      </c>
+      <c r="B339" s="40" t="s">
+        <v>986</v>
+      </c>
+      <c r="C339" s="41" t="s">
+        <v>984</v>
+      </c>
+      <c r="D339" s="40" t="s">
+        <v>984</v>
+      </c>
+      <c r="E339" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F339" s="40">
+        <v>21.319946</v>
+      </c>
+      <c r="G339" s="40">
+        <v>105.567635</v>
+      </c>
+    </row>
+    <row r="340" ht="96.6" spans="1:7">
+      <c r="A340" s="39" t="s">
+        <v>987</v>
+      </c>
+      <c r="B340" s="40" t="s">
+        <v>988</v>
+      </c>
+      <c r="C340" s="41" t="s">
+        <v>989</v>
+      </c>
+      <c r="D340" s="40" t="s">
+        <v>990</v>
+      </c>
+      <c r="E340" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F340" s="40">
+        <v>21.302912</v>
+      </c>
+      <c r="G340" s="40">
+        <v>105.587822</v>
+      </c>
+    </row>
+    <row r="341" ht="27.6" spans="1:7">
+      <c r="A341" s="39" t="s">
+        <v>991</v>
+      </c>
+      <c r="B341" s="40" t="s">
+        <v>992</v>
+      </c>
+      <c r="C341" s="41" t="s">
+        <v>993</v>
+      </c>
+      <c r="D341" s="40" t="s">
+        <v>990</v>
+      </c>
+      <c r="E341" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F341" s="40">
+        <v>21.306091</v>
+      </c>
+      <c r="G341" s="40">
+        <v>105.555504</v>
+      </c>
+    </row>
+    <row r="342" ht="41.4" spans="1:7">
+      <c r="A342" s="39" t="s">
+        <v>994</v>
+      </c>
+      <c r="B342" s="40" t="s">
+        <v>995</v>
+      </c>
+      <c r="C342" s="41" t="s">
+        <v>996</v>
+      </c>
+      <c r="D342" s="40" t="s">
+        <v>984</v>
+      </c>
+      <c r="E342" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F342" s="40">
+        <v>21.2178</v>
+      </c>
+      <c r="G342" s="40">
+        <v>105.516525</v>
+      </c>
+    </row>
+    <row r="343" ht="69" spans="1:7">
+      <c r="A343" s="39" t="s">
+        <v>997</v>
+      </c>
+      <c r="B343" s="40" t="s">
+        <v>998</v>
+      </c>
+      <c r="C343" s="41" t="s">
+        <v>999</v>
+      </c>
+      <c r="D343" s="40" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E343" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F343" s="40">
+        <v>21.295792</v>
+      </c>
+      <c r="G343" s="40">
+        <v>105.728592</v>
+      </c>
+    </row>
+    <row r="344" ht="124.2" spans="1:7">
+      <c r="A344" s="39" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B344" s="40" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C344" s="41" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D344" s="40" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E344" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F344" s="40">
+        <v>21.385872</v>
+      </c>
+      <c r="G344" s="40">
+        <v>105.596031</v>
+      </c>
+    </row>
+    <row r="345" ht="69" spans="1:7">
+      <c r="A345" s="39" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B345" s="40" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C345" s="41" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D345" s="40" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E345" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F345" s="40">
+        <v>21.239538</v>
+      </c>
+      <c r="G345" s="40">
+        <v>105.53125</v>
+      </c>
+    </row>
+    <row r="346" ht="69" spans="1:7">
+      <c r="A346" s="39" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B346" s="40" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C346" s="41" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D346" s="40" t="s">
+        <v>984</v>
+      </c>
+      <c r="E346" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F346" s="40">
+        <v>21.23712</v>
+      </c>
+      <c r="G346" s="40">
+        <v>105.480354</v>
+      </c>
+    </row>
+    <row r="347" ht="55.2" spans="1:7">
+      <c r="A347" s="39" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B347" s="40" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C347" s="41" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D347" s="40" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E347" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F347" s="40">
+        <v>21.340284</v>
+      </c>
+      <c r="G347" s="40">
+        <v>105.451347</v>
+      </c>
+    </row>
+    <row r="348" ht="193.2" spans="1:7">
+      <c r="A348" s="39" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B348" s="40" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C348" s="41" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D348" s="40" t="s">
+        <v>980</v>
+      </c>
+      <c r="E348" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F348" s="40">
+        <v>21.385885</v>
+      </c>
+      <c r="G348" s="40">
+        <v>105.613708</v>
+      </c>
+    </row>
+    <row r="349" ht="124.2" spans="1:7">
+      <c r="A349" s="39" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B349" s="40" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C349" s="41" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D349" s="40" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E349" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F349" s="40">
+        <v>21.259951</v>
+      </c>
+      <c r="G349" s="40">
+        <v>105.657547</v>
+      </c>
+    </row>
+    <row r="350" ht="138" spans="1:7">
+      <c r="A350" s="39" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B350" s="40" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C350" s="41" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D350" s="40" t="s">
+        <v>990</v>
+      </c>
+      <c r="E350" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F350" s="40">
+        <v>21.316677</v>
+      </c>
+      <c r="G350" s="40">
+        <v>105.631683</v>
+      </c>
+    </row>
+    <row r="351" ht="151.8" spans="1:7">
+      <c r="A351" s="39" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B351" s="40" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C351" s="41" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D351" s="40" t="s">
+        <v>984</v>
+      </c>
+      <c r="E351" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F351" s="40">
+        <v>21.305035</v>
+      </c>
+      <c r="G351" s="40">
+        <v>105.61945</v>
+      </c>
+    </row>
+    <row r="352" ht="110.4" spans="1:7">
+      <c r="A352" s="39" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B352" s="40" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C352" s="41" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D352" s="40" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E352" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F352" s="40">
+        <v>21.235355</v>
+      </c>
+      <c r="G352" s="40">
+        <v>105.701462</v>
+      </c>
+    </row>
+    <row r="353" ht="69" spans="1:7">
+      <c r="A353" s="39" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B353" s="40" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C353" s="41" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D353" s="40" t="s">
+        <v>990</v>
+      </c>
+      <c r="E353" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F353" s="40">
+        <v>21.312298</v>
+      </c>
+      <c r="G353" s="40">
+        <v>105.583374</v>
+      </c>
+    </row>
+    <row r="354" ht="82.8" spans="1:7">
+      <c r="A354" s="39" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B354" s="40" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C354" s="41" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D354" s="40" t="s">
+        <v>990</v>
+      </c>
+      <c r="E354" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F354" s="40">
+        <v>21.304882</v>
+      </c>
+      <c r="G354" s="40">
+        <v>105.619331</v>
+      </c>
+    </row>
+    <row r="355" ht="69" spans="1:7">
+      <c r="A355" s="39" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B355" s="40" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C355" s="41" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D355" s="40" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E355" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F355" s="40">
+        <v>21.331591</v>
+      </c>
+      <c r="G355" s="40">
+        <v>105.564331</v>
+      </c>
+    </row>
+    <row r="356" ht="41.4" spans="1:7">
+      <c r="A356" s="39" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B356" s="40" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C356" s="41" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D356" s="40" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E356" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F356" s="40">
+        <v>21.227743</v>
+      </c>
+      <c r="G356" s="40">
+        <v>105.70356</v>
+      </c>
+    </row>
+    <row r="357" ht="55.2" spans="1:7">
+      <c r="A357" s="39" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B357" s="40" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C357" s="41" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D357" s="40" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E357" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F357" s="40">
+        <v>21.340479</v>
+      </c>
+      <c r="G357" s="40">
+        <v>105.547752</v>
+      </c>
+    </row>
+    <row r="358" ht="124.2" spans="1:7">
+      <c r="A358" s="39" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B358" s="40" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C358" s="41" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D358" s="40" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E358" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F358" s="40">
+        <v>21.338945</v>
+      </c>
+      <c r="G358" s="40">
+        <v>105.722321</v>
+      </c>
+    </row>
+    <row r="359" ht="27.6" spans="1:7">
+      <c r="A359" s="42" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B359" s="40" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C359" s="41" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D359" s="40" t="s">
+        <v>980</v>
+      </c>
+      <c r="E359" s="40" t="s">
+        <v>909</v>
+      </c>
+      <c r="F359" s="40">
+        <v>21.457937</v>
+      </c>
+      <c r="G359" s="40">
+        <v>105.564934</v>
+      </c>
+    </row>
+    <row r="360" ht="138" spans="1:7">
+      <c r="A360" s="36" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B360" s="34" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C360" s="35" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D360" s="34" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E360" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F360" s="34">
+        <v>21.231286</v>
+      </c>
+      <c r="G360" s="34">
+        <v>105.70205</v>
+      </c>
+    </row>
+    <row r="361" ht="82.8" spans="1:7">
+      <c r="A361" s="36" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B361" s="34" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C361" s="35" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D361" s="34" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E361" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F361" s="34">
+        <v>21.13414</v>
+      </c>
+      <c r="G361" s="34">
+        <v>105.33549</v>
+      </c>
+    </row>
+    <row r="362" ht="151.8" spans="1:7">
+      <c r="A362" s="37" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B362" s="34" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C362" s="35" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D362" s="34" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E362" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F362" s="34">
+        <v>21.245411</v>
+      </c>
+      <c r="G362" s="34">
+        <v>105.678974</v>
+      </c>
+    </row>
+    <row r="363" ht="110.4" spans="1:7">
+      <c r="A363" s="37" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B363" s="34" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C363" s="35" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D363" s="34" t="s">
+        <v>990</v>
+      </c>
+      <c r="E363" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F363" s="34">
+        <v>21.29877</v>
+      </c>
+      <c r="G363" s="34">
+        <v>105.5588</v>
+      </c>
+    </row>
+    <row r="364" ht="41.4" spans="1:7">
+      <c r="A364" s="37" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B364" s="34" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C364" s="35" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D364" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E364" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F364" s="34">
+        <v>21.16168</v>
+      </c>
+      <c r="G364" s="34">
+        <v>105.52325</v>
+      </c>
+    </row>
+    <row r="365" ht="55.2" spans="1:7">
+      <c r="A365" s="37" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B365" s="34" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C365" s="35" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D365" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E365" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F365" s="34">
+        <v>21.48349</v>
+      </c>
+      <c r="G365" s="34">
+        <v>105.56166</v>
+      </c>
+    </row>
+    <row r="366" ht="41.4" spans="1:7">
+      <c r="A366" s="37" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B366" s="34" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C366" s="35" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D366" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E366" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F366" s="34">
+        <v>21.37798</v>
+      </c>
+      <c r="G366" s="34">
+        <v>105.49945</v>
+      </c>
+    </row>
+    <row r="367" ht="110.4" spans="1:7">
+      <c r="A367" s="37" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B367" s="34" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C367" s="35" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D367" s="34" t="s">
+        <v>941</v>
+      </c>
+      <c r="E367" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F367" s="34">
+        <v>20.712599</v>
+      </c>
+      <c r="G367" s="34">
+        <v>105.32561</v>
+      </c>
+    </row>
+    <row r="368" ht="110.4" spans="1:7">
+      <c r="A368" s="37" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B368" s="34" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C368" s="35" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D368" s="34" t="s">
+        <v>941</v>
+      </c>
+      <c r="E368" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F368" s="34">
+        <v>20.712599</v>
+      </c>
+      <c r="G368" s="34">
+        <v>105.32561</v>
+      </c>
+    </row>
+    <row r="369" ht="124.2" spans="1:7">
+      <c r="A369" s="37" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B369" s="34" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C369" s="35" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D369" s="34" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E369" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F369" s="34">
+        <v>21.381407</v>
+      </c>
+      <c r="G369" s="34">
+        <v>105.53991</v>
+      </c>
+    </row>
+    <row r="370" ht="151.8" spans="1:7">
+      <c r="A370" s="37" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B370" s="34" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C370" s="35" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D370" s="34" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E370" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F370" s="34">
+        <v>21.234845</v>
+      </c>
+      <c r="G370" s="34">
+        <v>105.70565</v>
+      </c>
+    </row>
+    <row r="371" ht="138" spans="1:7">
+      <c r="A371" s="37" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B371" s="34" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C371" s="35" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D371" s="34" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E371" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F371" s="34">
+        <v>21.277999</v>
+      </c>
+      <c r="G371" s="34">
+        <v>105.72977</v>
+      </c>
+    </row>
+    <row r="372" ht="138" spans="1:7">
+      <c r="A372" s="37" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B372" s="34" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C372" s="35" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D372" s="34" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E372" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F372" s="34">
+        <v>21.205883</v>
+      </c>
+      <c r="G372" s="34">
+        <v>105.17894</v>
+      </c>
+    </row>
+    <row r="373" ht="138" spans="1:7">
+      <c r="A373" s="37" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B373" s="34" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C373" s="35" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D373" s="34" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E373" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F373" s="34">
+        <v>21.205883</v>
+      </c>
+      <c r="G373" s="34">
+        <v>105.17894</v>
+      </c>
+    </row>
+    <row r="374" ht="69" spans="1:7">
+      <c r="A374" s="37" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B374" s="34" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C374" s="35" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D374" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E374" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F374" s="34">
+        <v>21.51923</v>
+      </c>
+      <c r="G374" s="34">
+        <v>105.52273</v>
+      </c>
+    </row>
+    <row r="375" ht="55.2" spans="1:7">
+      <c r="A375" s="37" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B375" s="34" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C375" s="35" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D375" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E375" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F375" s="34">
+        <v>21.16295</v>
+      </c>
+      <c r="G375" s="34">
+        <v>105.50908</v>
+      </c>
+    </row>
+    <row r="376" ht="55.2" spans="1:7">
+      <c r="A376" s="37" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B376" s="34" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C376" s="35" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D376" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E376" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F376" s="34">
+        <v>21.52158</v>
+      </c>
+      <c r="G376" s="34">
+        <v>105.51651</v>
+      </c>
+    </row>
+    <row r="377" ht="55.2" spans="1:7">
+      <c r="A377" s="37" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B377" s="34" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C377" s="35" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D377" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E377" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F377" s="34">
+        <v>21.16218</v>
+      </c>
+      <c r="G377" s="34">
+        <v>105.5141</v>
+      </c>
+    </row>
+    <row r="378" ht="41.4" spans="1:7">
+      <c r="A378" s="37" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B378" s="34" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C378" s="35" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D378" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E378" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F378" s="34">
+        <v>21.4753</v>
+      </c>
+      <c r="G378" s="34">
+        <v>105.4524</v>
+      </c>
+    </row>
+    <row r="379" ht="69" spans="1:7">
+      <c r="A379" s="37" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B379" s="34" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C379" s="35" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D379" s="34" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E379" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F379" s="34">
+        <v>21.293455</v>
+      </c>
+      <c r="G379" s="34">
+        <v>105.126816</v>
+      </c>
+    </row>
+    <row r="380" ht="27.6" spans="1:7">
+      <c r="A380" s="37" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B380" s="34" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C380" s="35" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D380" s="34" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E380" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F380" s="34">
+        <v>20.947577</v>
+      </c>
+      <c r="G380" s="34">
+        <v>105.340202</v>
+      </c>
+    </row>
+    <row r="381" ht="55.2" spans="1:7">
+      <c r="A381" s="37" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B381" s="34" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C381" s="35" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D381" s="34" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E381" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F381" s="34">
+        <v>21.107878</v>
+      </c>
+      <c r="G381" s="34">
+        <v>105.234444</v>
+      </c>
+    </row>
+    <row r="382" ht="27.6" spans="1:7">
+      <c r="A382" s="37" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B382" s="34" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C382" s="35" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D382" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E382" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F382" s="34">
+        <v>21.481037</v>
+      </c>
+      <c r="G382" s="34">
+        <v>105.048241</v>
+      </c>
+    </row>
+    <row r="383" ht="41.4" spans="1:7">
+      <c r="A383" s="37" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B383" s="34" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C383" s="35" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D383" s="34" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E383" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F383" s="34">
+        <v>21.503065</v>
+      </c>
+      <c r="G383" s="34">
+        <v>105.038628</v>
+      </c>
+    </row>
+    <row r="384" ht="27.6" spans="1:7">
+      <c r="A384" s="37" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B384" s="34" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C384" s="35" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D384" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E384" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F384" s="34">
+        <v>21.117357</v>
+      </c>
+      <c r="G384" s="34">
+        <v>105.003342</v>
+      </c>
+    </row>
+    <row r="385" ht="27.6" spans="1:7">
+      <c r="A385" s="37" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B385" s="34" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C385" s="35" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D385" s="34" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E385" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F385" s="34">
+        <v>21.221247</v>
+      </c>
+      <c r="G385" s="34">
+        <v>105.005791</v>
+      </c>
+    </row>
+    <row r="386" ht="55.2" spans="1:7">
+      <c r="A386" s="37" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B386" s="34" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C386" s="35" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D386" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E386" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F386" s="34">
+        <v>21.52359</v>
+      </c>
+      <c r="G386" s="34">
+        <v>105.50499</v>
+      </c>
+    </row>
+    <row r="387" ht="138" spans="1:7">
+      <c r="A387" s="37" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B387" s="34" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C387" s="35" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D387" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E387" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F387" s="34">
+        <v>21.412158</v>
+      </c>
+      <c r="G387" s="34">
+        <v>105.470298</v>
+      </c>
+    </row>
+    <row r="388" ht="124.2" spans="1:7">
+      <c r="A388" s="37" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B388" s="34" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C388" s="35" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D388" s="34" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E388" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F388" s="34">
+        <v>21.138222</v>
+      </c>
+      <c r="G388" s="34">
+        <v>105.131859</v>
+      </c>
+    </row>
+    <row r="389" ht="69" spans="1:7">
+      <c r="A389" s="37" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B389" s="34" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C389" s="35" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D389" s="34" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E389" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F389" s="34">
+        <v>21.204323</v>
+      </c>
+      <c r="G389" s="34">
+        <v>105.179703</v>
+      </c>
+    </row>
+    <row r="390" ht="69" spans="1:7">
+      <c r="A390" s="37" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B390" s="34" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C390" s="35" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D390" s="34" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E390" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F390" s="34">
+        <v>21.220078</v>
+      </c>
+      <c r="G390" s="34">
+        <v>105.18486</v>
+      </c>
+    </row>
+    <row r="391" ht="138" spans="1:7">
+      <c r="A391" s="37" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B391" s="34" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C391" s="35" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D391" s="34" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E391" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F391" s="34">
+        <v>21.293781</v>
+      </c>
+      <c r="G391" s="34">
+        <v>105.461657</v>
+      </c>
+    </row>
+    <row r="392" ht="234.6" spans="1:7">
+      <c r="A392" s="38" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B392" s="34" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C392" s="35" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D392" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E392" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F392" s="34">
+        <v>21.30653</v>
+      </c>
+      <c r="G392" s="34">
+        <v>105.578141</v>
+      </c>
+    </row>
+    <row r="393" ht="41.4" spans="1:7">
+      <c r="A393" s="38" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B393" s="34" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C393" s="35" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D393" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E393" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F393" s="34">
+        <v>21.48269</v>
+      </c>
+      <c r="G393" s="34">
+        <v>105.55077</v>
+      </c>
+    </row>
+    <row r="394" ht="234.6" spans="1:7">
+      <c r="A394" s="38" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B394" s="34" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C394" s="35" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D394" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E394" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F394" s="34">
+        <v>21.30653</v>
+      </c>
+      <c r="G394" s="34">
+        <v>105.578141</v>
+      </c>
+    </row>
+    <row r="395" ht="55.2" spans="1:7">
+      <c r="A395" s="38" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B395" s="34" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C395" s="35" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D395" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E395" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F395" s="34">
+        <v>21.62335</v>
+      </c>
+      <c r="G395" s="34">
+        <v>105.52859</v>
+      </c>
+    </row>
+    <row r="396" ht="234.6" spans="1:7">
+      <c r="A396" s="38" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B396" s="34" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C396" s="35" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D396" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E396" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F396" s="34">
+        <v>21.30653</v>
+      </c>
+      <c r="G396" s="34">
+        <v>105.578141</v>
+      </c>
+    </row>
+    <row r="397" ht="234.6" spans="1:7">
+      <c r="A397" s="38" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B397" s="34" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C397" s="35" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D397" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E397" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F397" s="34">
+        <v>21.30653</v>
+      </c>
+      <c r="G397" s="34">
+        <v>105.578141</v>
+      </c>
+    </row>
+    <row r="398" ht="96.6" spans="1:7">
+      <c r="A398" s="38" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B398" s="34" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C398" s="35" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D398" s="34" t="s">
+        <v>980</v>
+      </c>
+      <c r="E398" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F398" s="34">
+        <v>21.374812</v>
+      </c>
+      <c r="G398" s="34">
+        <v>105.606402</v>
+      </c>
+    </row>
+    <row r="399" ht="69" spans="1:7">
+      <c r="A399" s="38" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B399" s="34" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C399" s="35" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D399" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E399" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F399" s="34">
+        <v>21.52156</v>
+      </c>
+      <c r="G399" s="34">
+        <v>105.51882</v>
+      </c>
+    </row>
+    <row r="400" ht="220.8" spans="1:7">
+      <c r="A400" s="38" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B400" s="34" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C400" s="35" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D400" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E400" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F400" s="34">
+        <v>21.308094</v>
+      </c>
+      <c r="G400" s="34">
+        <v>105.615988</v>
+      </c>
+    </row>
+    <row r="401" ht="151.8" spans="1:7">
+      <c r="A401" s="38" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B401" s="34" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C401" s="35" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D401" s="34" t="s">
+        <v>990</v>
+      </c>
+      <c r="E401" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F401" s="34">
+        <v>21.30597</v>
+      </c>
+      <c r="G401" s="34">
+        <v>105.57292</v>
+      </c>
+    </row>
+    <row r="402" ht="220.8" spans="1:7">
+      <c r="A402" s="38" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B402" s="34" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C402" s="35" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D402" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E402" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F402" s="34">
+        <v>21.308094</v>
+      </c>
+      <c r="G402" s="34">
+        <v>105.615988</v>
+      </c>
+    </row>
+    <row r="403" ht="55.2" spans="1:7">
+      <c r="A403" s="38" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B403" s="34" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C403" s="35" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D403" s="34" t="s">
+        <v>984</v>
+      </c>
+      <c r="E403" s="34" t="s">
+        <v>909</v>
+      </c>
+      <c r="F403" s="34">
+        <v>21.3699</v>
+      </c>
+      <c r="G403" s="34">
+        <v>105.5074</v>
       </c>
     </row>
   </sheetData>

--- a/du_lieu_tram.xlsx
+++ b/du_lieu_tram.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="187">
   <si>
     <t>ma_tram</t>
   </si>
@@ -260,6 +260,15 @@
     <t>Tiếng Anh xã Ngọc Thanh, huyện Phúc Yên, tỉnh Vĩnh Phúc</t>
   </si>
   <si>
+    <t>BSS-255141001087</t>
+  </si>
+  <si>
+    <t>B.VPH00063</t>
+  </si>
+  <si>
+    <t>Thị trấn Đại Đình</t>
+  </si>
+  <si>
     <t>BSS-254441000701</t>
   </si>
   <si>
@@ -498,6 +507,87 @@
   </si>
   <si>
     <t>Xã Vĩnh Thành</t>
+  </si>
+  <si>
+    <t>BSS-255041001135</t>
+  </si>
+  <si>
+    <t>B.PTH10663</t>
+  </si>
+  <si>
+    <t>Số nhà 313 đường Hùng Vương, Phường Tích Sơn, Thành phố Vĩnh Yên, Tỉnh Vĩnh Phúc(Gần cầu oai bệnh viện 109)</t>
+  </si>
+  <si>
+    <t>BSS-255241001278</t>
+  </si>
+  <si>
+    <t>B.PTH10626</t>
+  </si>
+  <si>
+    <t>Thôn Lục Liễu Đạo Trù</t>
+  </si>
+  <si>
+    <t>BSS-255041002438</t>
+  </si>
+  <si>
+    <t>BSS-255041001075</t>
+  </si>
+  <si>
+    <t>B.PTH10629</t>
+  </si>
+  <si>
+    <t>Thôn Hậu Lộc Vĩnh Ninh</t>
+  </si>
+  <si>
+    <t>BSS-255341000722</t>
+  </si>
+  <si>
+    <t>BSS-255241003215</t>
+  </si>
+  <si>
+    <t>BSS-255241002060</t>
+  </si>
+  <si>
+    <t>B.PTH10425</t>
+  </si>
+  <si>
+    <t>QL2B, Hợp Châu, Tam Đảo, Vĩnh Phúc</t>
+  </si>
+  <si>
+    <t>BSS-255341000360</t>
+  </si>
+  <si>
+    <t>B.PTH10622</t>
+  </si>
+  <si>
+    <t>BSS-255341000487</t>
+  </si>
+  <si>
+    <t>B.PTH10664</t>
+  </si>
+  <si>
+    <t>Số nhà 523 Đường Mê Linh,Phường Khai quang, Thành phố Vĩnh Yên, Tỉnh Vĩnh Phúc(Gần nhà thi đấu Vĩnh Yên).</t>
+  </si>
+  <si>
+    <t>BSS-255141002445</t>
+  </si>
+  <si>
+    <t>B.PTH10024</t>
+  </si>
+  <si>
+    <t>Số nhà 499, đường Hùng Vương, Phường Vĩnh Yên, Tỉnh Phú Thọ, Việt Nam</t>
+  </si>
+  <si>
+    <t>BSS-255241001914</t>
+  </si>
+  <si>
+    <t>BSS-260141000003</t>
+  </si>
+  <si>
+    <t>B.PTH10627</t>
+  </si>
+  <si>
+    <t>Thôn Viên Luận Đồng Ích</t>
   </si>
 </sst>
 </file>
@@ -510,7 +600,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,18 +614,6 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -701,18 +779,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1103,137 +1175,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1258,70 +1330,63 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2171,14 +2236,28 @@
         <v>105.722321</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="5"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+    <row r="23" ht="27.6" spans="1:7">
+      <c r="A23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="3">
+        <v>21.457937</v>
+      </c>
+      <c r="G23" s="3">
+        <v>105.564934</v>
+      </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="6"/>
@@ -2200,16 +2279,16 @@
     </row>
     <row r="26" ht="151.8" spans="1:7">
       <c r="A26" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>13</v>
@@ -2232,13 +2311,13 @@
     </row>
     <row r="28" ht="41.4" spans="1:7">
       <c r="A28" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>12</v>
@@ -2255,13 +2334,13 @@
     </row>
     <row r="29" ht="55.2" spans="1:7">
       <c r="A29" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>12</v>
@@ -2278,13 +2357,13 @@
     </row>
     <row r="30" ht="41.4" spans="1:7">
       <c r="A30" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>12</v>
@@ -2301,16 +2380,16 @@
     </row>
     <row r="31" ht="110.4" spans="1:7">
       <c r="A31" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>13</v>
@@ -2324,16 +2403,16 @@
     </row>
     <row r="32" ht="110.4" spans="1:7">
       <c r="A32" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="C32" s="8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>13</v>
@@ -2374,16 +2453,16 @@
     </row>
     <row r="36" ht="138" spans="1:7">
       <c r="A36" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>13</v>
@@ -2397,16 +2476,16 @@
     </row>
     <row r="37" ht="138" spans="1:7">
       <c r="A37" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="7" t="s">
-        <v>96</v>
-      </c>
       <c r="C37" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>13</v>
@@ -2420,13 +2499,13 @@
     </row>
     <row r="38" ht="69" spans="1:7">
       <c r="A38" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>12</v>
@@ -2443,13 +2522,13 @@
     </row>
     <row r="39" ht="55.2" spans="1:7">
       <c r="A39" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>12</v>
@@ -2466,13 +2545,13 @@
     </row>
     <row r="40" ht="55.2" spans="1:7">
       <c r="A40" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>12</v>
@@ -2489,13 +2568,13 @@
     </row>
     <row r="41" ht="55.2" spans="1:7">
       <c r="A41" s="9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>12</v>
@@ -2512,13 +2591,13 @@
     </row>
     <row r="42" ht="41.4" spans="1:7">
       <c r="A42" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>12</v>
@@ -2535,16 +2614,16 @@
     </row>
     <row r="43" ht="69" spans="1:7">
       <c r="A43" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>13</v>
@@ -2558,16 +2637,16 @@
     </row>
     <row r="44" ht="27.6" spans="1:7">
       <c r="A44" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>13</v>
@@ -2581,16 +2660,16 @@
     </row>
     <row r="45" ht="55.2" spans="1:7">
       <c r="A45" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>13</v>
@@ -2604,13 +2683,13 @@
     </row>
     <row r="46" ht="27.6" spans="1:7">
       <c r="A46" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>12</v>
@@ -2627,16 +2706,16 @@
     </row>
     <row r="47" ht="41.4" spans="1:7">
       <c r="A47" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>13</v>
@@ -2650,13 +2729,13 @@
     </row>
     <row r="48" ht="27.6" spans="1:7">
       <c r="A48" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>12</v>
@@ -2673,16 +2752,16 @@
     </row>
     <row r="49" ht="27.6" spans="1:7">
       <c r="A49" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>13</v>
@@ -2696,13 +2775,13 @@
     </row>
     <row r="50" ht="55.2" spans="1:7">
       <c r="A50" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>12</v>
@@ -2719,13 +2798,13 @@
     </row>
     <row r="51" ht="138" spans="1:7">
       <c r="A51" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>12</v>
@@ -2742,16 +2821,16 @@
     </row>
     <row r="52" ht="124.2" spans="1:7">
       <c r="A52" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>13</v>
@@ -2765,16 +2844,16 @@
     </row>
     <row r="53" ht="69" spans="1:7">
       <c r="A53" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>13</v>
@@ -2788,16 +2867,16 @@
     </row>
     <row r="54" ht="69" spans="1:7">
       <c r="A54" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>13</v>
@@ -2811,16 +2890,16 @@
     </row>
     <row r="55" ht="138" spans="1:7">
       <c r="A55" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>13</v>
@@ -2832,3137 +2911,3305 @@
         <v>105.461657</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="10"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="13"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="13"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="13"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="13"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="13"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="13"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="13"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="13"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="13"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="13"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="11"/>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="13"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="11"/>
+    <row r="56" ht="234.6" spans="1:7">
+      <c r="A56" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="7">
+        <v>21.30653</v>
+      </c>
+      <c r="G56" s="7">
+        <v>105.578141</v>
+      </c>
+    </row>
+    <row r="57" ht="41.4" spans="1:7">
+      <c r="A57" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="7">
+        <v>21.48269</v>
+      </c>
+      <c r="G57" s="7">
+        <v>105.55077</v>
+      </c>
+    </row>
+    <row r="58" ht="234.6" spans="1:7">
+      <c r="A58" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="7">
+        <v>21.30653</v>
+      </c>
+      <c r="G58" s="7">
+        <v>105.578141</v>
+      </c>
+    </row>
+    <row r="59" ht="55.2" spans="1:7">
+      <c r="A59" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="7">
+        <v>21.62335</v>
+      </c>
+      <c r="G59" s="7">
+        <v>105.52859</v>
+      </c>
+    </row>
+    <row r="60" ht="234.6" spans="1:7">
+      <c r="A60" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="7">
+        <v>21.30653</v>
+      </c>
+      <c r="G60" s="7">
+        <v>105.578141</v>
+      </c>
+    </row>
+    <row r="61" ht="234.6" spans="1:7">
+      <c r="A61" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="7">
+        <v>21.30653</v>
+      </c>
+      <c r="G61" s="7">
+        <v>105.578141</v>
+      </c>
+    </row>
+    <row r="62" ht="96.6" spans="1:7">
+      <c r="A62" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="7">
+        <v>21.374812</v>
+      </c>
+      <c r="G62" s="7">
+        <v>105.606402</v>
+      </c>
+    </row>
+    <row r="63" ht="69" spans="1:7">
+      <c r="A63" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="7">
+        <v>21.52156</v>
+      </c>
+      <c r="G63" s="7">
+        <v>105.51882</v>
+      </c>
+    </row>
+    <row r="64" ht="220.8" spans="1:7">
+      <c r="A64" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="7">
+        <v>21.308094</v>
+      </c>
+      <c r="G64" s="7">
+        <v>105.615988</v>
+      </c>
+    </row>
+    <row r="65" ht="151.8" spans="1:7">
+      <c r="A65" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="7">
+        <v>21.30597</v>
+      </c>
+      <c r="G65" s="7">
+        <v>105.57292</v>
+      </c>
+    </row>
+    <row r="66" ht="220.8" spans="1:7">
+      <c r="A66" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="7">
+        <v>21.308094</v>
+      </c>
+      <c r="G66" s="7">
+        <v>105.615988</v>
+      </c>
+    </row>
+    <row r="67" ht="55.2" spans="1:7">
+      <c r="A67" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="7">
+        <v>21.3699</v>
+      </c>
+      <c r="G67" s="7">
+        <v>105.5074</v>
+      </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="13"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
+      <c r="A68" s="10"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="7"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="14"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="15"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="14"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
+      <c r="A70" s="11"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="18"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
+      <c r="A71" s="15"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="13"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="14"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="14"/>
-      <c r="B73" s="15"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="18"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
+      <c r="A74" s="15"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="18"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
+      <c r="A75" s="15"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="18"/>
-      <c r="B76" s="15"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
+      <c r="A76" s="15"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="18"/>
-      <c r="B77" s="15"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
+      <c r="A77" s="15"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="18"/>
-      <c r="B78" s="15"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
+      <c r="A78" s="15"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="18"/>
-      <c r="B79" s="15"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
+      <c r="A79" s="15"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="18"/>
-      <c r="B80" s="15"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
+      <c r="A80" s="15"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="18"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
+      <c r="A81" s="15"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="18"/>
-      <c r="B82" s="15"/>
-      <c r="C82" s="16"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="19"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
+      <c r="A82" s="15"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="12"/>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="18"/>
-      <c r="B83" s="15"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="19"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
+      <c r="A83" s="15"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="13"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="12"/>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="14"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15"/>
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="14"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="15"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="15"/>
-      <c r="G85" s="15"/>
+      <c r="A85" s="11"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="16"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="12"/>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="18"/>
-      <c r="B86" s="15"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="15"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="15"/>
-      <c r="G86" s="15"/>
+      <c r="A86" s="15"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="18"/>
-      <c r="B87" s="15"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="15"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15"/>
+      <c r="A87" s="15"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="18"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="19"/>
-      <c r="F88" s="15"/>
-      <c r="G88" s="15"/>
+      <c r="A88" s="15"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" s="18"/>
-      <c r="B89" s="15"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="15"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="15"/>
-      <c r="G89" s="15"/>
+      <c r="A89" s="15"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="12"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="12"/>
     </row>
     <row r="90" spans="1:7">
-      <c r="A90" s="14"/>
-      <c r="B90" s="15"/>
-      <c r="C90" s="16"/>
-      <c r="D90" s="15"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="15"/>
-      <c r="G90" s="15"/>
+      <c r="A90" s="11"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="13"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12"/>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="18"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="15"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
+      <c r="A91" s="15"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="12"/>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="14"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
+      <c r="A92" s="11"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="12"/>
     </row>
     <row r="93" spans="1:7">
-      <c r="A93" s="18"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="16"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
+      <c r="A93" s="15"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="13"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="16"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="18"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="16"/>
-      <c r="D94" s="15"/>
-      <c r="E94" s="19"/>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15"/>
+      <c r="A94" s="15"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="16"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="18"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="20"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="19"/>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15"/>
+      <c r="A95" s="15"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="17"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
     </row>
     <row r="96" spans="1:7">
-      <c r="A96" s="18"/>
-      <c r="B96" s="15"/>
-      <c r="C96" s="20"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
+      <c r="A96" s="15"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="16"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="12"/>
     </row>
     <row r="97" spans="1:7">
-      <c r="A97" s="18"/>
-      <c r="B97" s="15"/>
-      <c r="C97" s="20"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
+      <c r="A97" s="15"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="16"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
     </row>
     <row r="98" spans="1:7">
-      <c r="A98" s="21"/>
-      <c r="B98" s="15"/>
-      <c r="C98" s="20"/>
-      <c r="D98" s="15"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
+      <c r="A98" s="18"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="17"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="16"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12"/>
     </row>
     <row r="99" spans="1:7">
-      <c r="A99" s="18"/>
-      <c r="B99" s="15"/>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="15"/>
-      <c r="G99" s="15"/>
+      <c r="A99" s="15"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
     </row>
     <row r="100" spans="1:7">
-      <c r="A100" s="18"/>
-      <c r="B100" s="15"/>
-      <c r="C100" s="16"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
+      <c r="A100" s="15"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="16"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12"/>
     </row>
     <row r="101" spans="1:7">
-      <c r="A101" s="18"/>
-      <c r="B101" s="15"/>
-      <c r="C101" s="16"/>
-      <c r="D101" s="22"/>
-      <c r="E101" s="23"/>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15"/>
+      <c r="A101" s="15"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="19"/>
+      <c r="E101" s="20"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="12"/>
     </row>
     <row r="102" spans="1:7">
-      <c r="A102" s="24"/>
-      <c r="B102" s="25"/>
-      <c r="C102" s="26"/>
-      <c r="D102" s="25"/>
-      <c r="E102" s="23"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="25"/>
+      <c r="A102" s="21"/>
+      <c r="B102" s="22"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="20"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="18"/>
-      <c r="B103" s="15"/>
-      <c r="C103" s="16"/>
-      <c r="D103" s="15"/>
-      <c r="E103" s="23"/>
-      <c r="F103" s="15"/>
-      <c r="G103" s="15"/>
+      <c r="A103" s="15"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="20"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="12"/>
     </row>
     <row r="104" spans="1:7">
-      <c r="A104" s="18"/>
-      <c r="B104" s="15"/>
-      <c r="C104" s="16"/>
-      <c r="D104" s="15"/>
-      <c r="E104" s="23"/>
-      <c r="F104" s="15"/>
-      <c r="G104" s="15"/>
+      <c r="A104" s="15"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="13"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="20"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="12"/>
     </row>
     <row r="105" spans="1:7">
-      <c r="A105" s="18"/>
-      <c r="B105" s="15"/>
-      <c r="C105" s="16"/>
-      <c r="D105" s="15"/>
-      <c r="E105" s="23"/>
-      <c r="F105" s="15"/>
-      <c r="G105" s="15"/>
+      <c r="A105" s="15"/>
+      <c r="B105" s="12"/>
+      <c r="C105" s="13"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="20"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="12"/>
     </row>
     <row r="106" spans="1:7">
-      <c r="A106" s="18"/>
-      <c r="B106" s="15"/>
-      <c r="C106" s="16"/>
-      <c r="D106" s="15"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="15"/>
-      <c r="G106" s="15"/>
+      <c r="A106" s="15"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="13"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
     </row>
     <row r="107" spans="1:7">
-      <c r="A107" s="18"/>
-      <c r="B107" s="15"/>
-      <c r="C107" s="16"/>
-      <c r="D107" s="15"/>
-      <c r="E107" s="23"/>
-      <c r="F107" s="15"/>
-      <c r="G107" s="15"/>
+      <c r="A107" s="15"/>
+      <c r="B107" s="12"/>
+      <c r="C107" s="13"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="20"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
     </row>
     <row r="108" spans="1:7">
-      <c r="A108" s="18"/>
-      <c r="B108" s="15"/>
-      <c r="C108" s="16"/>
-      <c r="D108" s="15"/>
-      <c r="E108" s="23"/>
-      <c r="F108" s="15"/>
-      <c r="G108" s="15"/>
+      <c r="A108" s="15"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="20"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="12"/>
     </row>
     <row r="109" spans="1:7">
-      <c r="A109" s="18"/>
-      <c r="B109" s="15"/>
-      <c r="C109" s="16"/>
-      <c r="D109" s="15"/>
-      <c r="E109" s="23"/>
-      <c r="F109" s="15"/>
-      <c r="G109" s="15"/>
+      <c r="A109" s="15"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="13"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="20"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="12"/>
     </row>
     <row r="110" spans="1:7">
-      <c r="A110" s="18"/>
-      <c r="B110" s="15"/>
-      <c r="C110" s="16"/>
-      <c r="D110" s="15"/>
-      <c r="E110" s="23"/>
-      <c r="F110" s="15"/>
-      <c r="G110" s="15"/>
+      <c r="A110" s="15"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="13"/>
+      <c r="D110" s="12"/>
+      <c r="E110" s="20"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
     </row>
     <row r="111" spans="1:7">
-      <c r="A111" s="18"/>
-      <c r="B111" s="15"/>
-      <c r="C111" s="16"/>
-      <c r="D111" s="15"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="15"/>
-      <c r="G111" s="15"/>
+      <c r="A111" s="15"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="13"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="20"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="12"/>
     </row>
     <row r="112" spans="1:7">
-      <c r="A112" s="18"/>
-      <c r="B112" s="15"/>
-      <c r="C112" s="16"/>
-      <c r="D112" s="15"/>
-      <c r="E112" s="23"/>
-      <c r="F112" s="15"/>
-      <c r="G112" s="15"/>
+      <c r="A112" s="15"/>
+      <c r="B112" s="12"/>
+      <c r="C112" s="13"/>
+      <c r="D112" s="12"/>
+      <c r="E112" s="20"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="12"/>
     </row>
     <row r="113" spans="1:7">
-      <c r="A113" s="18"/>
-      <c r="B113" s="15"/>
-      <c r="C113" s="16"/>
-      <c r="D113" s="15"/>
-      <c r="E113" s="23"/>
-      <c r="F113" s="15"/>
-      <c r="G113" s="15"/>
+      <c r="A113" s="15"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="20"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12"/>
     </row>
     <row r="114" spans="1:7">
-      <c r="A114" s="18"/>
-      <c r="B114" s="15"/>
-      <c r="C114" s="16"/>
-      <c r="D114" s="15"/>
-      <c r="E114" s="23"/>
-      <c r="F114" s="15"/>
-      <c r="G114" s="15"/>
+      <c r="A114" s="15"/>
+      <c r="B114" s="12"/>
+      <c r="C114" s="13"/>
+      <c r="D114" s="12"/>
+      <c r="E114" s="20"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="12"/>
     </row>
     <row r="115" spans="1:7">
-      <c r="A115" s="18"/>
-      <c r="B115" s="15"/>
-      <c r="C115" s="16"/>
-      <c r="D115" s="15"/>
-      <c r="E115" s="23"/>
-      <c r="F115" s="15"/>
-      <c r="G115" s="15"/>
+      <c r="A115" s="15"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="20"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="12"/>
     </row>
     <row r="116" spans="1:7">
-      <c r="A116" s="27"/>
-      <c r="B116" s="15"/>
-      <c r="C116" s="16"/>
-      <c r="D116" s="15"/>
-      <c r="E116" s="23"/>
-      <c r="F116" s="15"/>
-      <c r="G116" s="15"/>
+      <c r="A116" s="24"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="12"/>
+      <c r="E116" s="20"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="12"/>
     </row>
     <row r="117" spans="1:7">
-      <c r="A117" s="18"/>
-      <c r="B117" s="15"/>
-      <c r="C117" s="16"/>
-      <c r="D117" s="15"/>
-      <c r="E117" s="23"/>
-      <c r="F117" s="15"/>
-      <c r="G117" s="15"/>
+      <c r="A117" s="15"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="13"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="20"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
     </row>
     <row r="118" spans="1:7">
-      <c r="A118" s="18"/>
-      <c r="B118" s="15"/>
-      <c r="C118" s="16"/>
-      <c r="D118" s="15"/>
-      <c r="E118" s="23"/>
-      <c r="F118" s="15"/>
-      <c r="G118" s="15"/>
+      <c r="A118" s="15"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="13"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="20"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="12"/>
     </row>
     <row r="119" spans="1:7">
-      <c r="A119" s="18"/>
-      <c r="B119" s="15"/>
-      <c r="C119" s="16"/>
-      <c r="D119" s="15"/>
-      <c r="E119" s="23"/>
-      <c r="F119" s="15"/>
-      <c r="G119" s="15"/>
+      <c r="A119" s="15"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="13"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="20"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="12"/>
     </row>
     <row r="120" spans="1:7">
-      <c r="A120" s="18"/>
-      <c r="B120" s="15"/>
-      <c r="C120" s="16"/>
-      <c r="D120" s="15"/>
-      <c r="E120" s="23"/>
-      <c r="F120" s="15"/>
-      <c r="G120" s="15"/>
+      <c r="A120" s="15"/>
+      <c r="B120" s="12"/>
+      <c r="C120" s="13"/>
+      <c r="D120" s="12"/>
+      <c r="E120" s="20"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12"/>
     </row>
     <row r="121" spans="1:7">
-      <c r="A121" s="18"/>
-      <c r="B121" s="15"/>
-      <c r="C121" s="16"/>
-      <c r="D121" s="15"/>
-      <c r="E121" s="23"/>
-      <c r="F121" s="15"/>
-      <c r="G121" s="15"/>
+      <c r="A121" s="15"/>
+      <c r="B121" s="12"/>
+      <c r="C121" s="13"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="20"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12"/>
     </row>
     <row r="122" spans="1:7">
-      <c r="A122" s="18"/>
-      <c r="B122" s="15"/>
-      <c r="C122" s="16"/>
-      <c r="D122" s="15"/>
-      <c r="E122" s="23"/>
-      <c r="F122" s="15"/>
-      <c r="G122" s="15"/>
+      <c r="A122" s="15"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="13"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="20"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
     </row>
     <row r="123" spans="1:7">
-      <c r="A123" s="18"/>
-      <c r="B123" s="15"/>
-      <c r="C123" s="16"/>
-      <c r="D123" s="15"/>
-      <c r="E123" s="23"/>
-      <c r="F123" s="15"/>
-      <c r="G123" s="15"/>
+      <c r="A123" s="15"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="13"/>
+      <c r="D123" s="12"/>
+      <c r="E123" s="20"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="12"/>
     </row>
     <row r="124" spans="1:7">
-      <c r="A124" s="18"/>
-      <c r="B124" s="15"/>
-      <c r="C124" s="16"/>
-      <c r="D124" s="15"/>
-      <c r="E124" s="15"/>
-      <c r="F124" s="15"/>
-      <c r="G124" s="15"/>
+      <c r="A124" s="15"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="13"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
     </row>
     <row r="125" spans="1:7">
-      <c r="A125" s="18"/>
-      <c r="B125" s="15"/>
-      <c r="C125" s="16"/>
-      <c r="D125" s="15"/>
-      <c r="E125" s="15"/>
-      <c r="F125" s="15"/>
-      <c r="G125" s="15"/>
+      <c r="A125" s="15"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="13"/>
+      <c r="D125" s="12"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="12"/>
     </row>
     <row r="126" spans="1:7">
-      <c r="A126" s="24"/>
-      <c r="B126" s="25"/>
-      <c r="C126" s="26"/>
-      <c r="D126" s="25"/>
-      <c r="E126" s="15"/>
-      <c r="F126" s="25"/>
-      <c r="G126" s="25"/>
+      <c r="A126" s="21"/>
+      <c r="B126" s="22"/>
+      <c r="C126" s="23"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="22"/>
+      <c r="G126" s="22"/>
     </row>
     <row r="127" spans="1:7">
-      <c r="A127" s="14"/>
-      <c r="B127" s="15"/>
-      <c r="C127" s="16"/>
-      <c r="D127" s="15"/>
-      <c r="E127" s="15"/>
-      <c r="F127" s="15"/>
-      <c r="G127" s="15"/>
+      <c r="A127" s="11"/>
+      <c r="B127" s="12"/>
+      <c r="C127" s="13"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="12"/>
     </row>
     <row r="128" spans="1:7">
-      <c r="A128" s="18"/>
-      <c r="B128" s="15"/>
-      <c r="C128" s="16"/>
-      <c r="D128" s="15"/>
-      <c r="E128" s="15"/>
-      <c r="F128" s="15"/>
-      <c r="G128" s="15"/>
+      <c r="A128" s="15"/>
+      <c r="B128" s="12"/>
+      <c r="C128" s="13"/>
+      <c r="D128" s="12"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
     </row>
     <row r="129" spans="1:7">
-      <c r="A129" s="24"/>
-      <c r="B129" s="25"/>
-      <c r="C129" s="26"/>
-      <c r="D129" s="25"/>
-      <c r="E129" s="25"/>
-      <c r="F129" s="25"/>
-      <c r="G129" s="25"/>
+      <c r="A129" s="21"/>
+      <c r="B129" s="22"/>
+      <c r="C129" s="23"/>
+      <c r="D129" s="22"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22"/>
+      <c r="G129" s="22"/>
     </row>
     <row r="130" spans="1:7">
-      <c r="A130" s="28"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="30"/>
-      <c r="D130" s="29"/>
-      <c r="E130" s="29"/>
-      <c r="F130" s="29"/>
-      <c r="G130" s="29"/>
+      <c r="A130" s="25"/>
+      <c r="B130" s="26"/>
+      <c r="C130" s="27"/>
+      <c r="D130" s="26"/>
+      <c r="E130" s="26"/>
+      <c r="F130" s="26"/>
+      <c r="G130" s="26"/>
     </row>
     <row r="131" spans="1:7">
-      <c r="A131" s="28"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="30"/>
-      <c r="D131" s="29"/>
-      <c r="E131" s="29"/>
-      <c r="F131" s="29"/>
-      <c r="G131" s="29"/>
+      <c r="A131" s="25"/>
+      <c r="B131" s="26"/>
+      <c r="C131" s="27"/>
+      <c r="D131" s="26"/>
+      <c r="E131" s="26"/>
+      <c r="F131" s="26"/>
+      <c r="G131" s="26"/>
     </row>
     <row r="132" spans="1:7">
-      <c r="A132" s="28"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="30"/>
-      <c r="D132" s="29"/>
-      <c r="E132" s="29"/>
-      <c r="F132" s="29"/>
-      <c r="G132" s="29"/>
+      <c r="A132" s="25"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="27"/>
+      <c r="D132" s="26"/>
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
     </row>
     <row r="133" spans="1:7">
-      <c r="A133" s="28"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="30"/>
-      <c r="D133" s="29"/>
-      <c r="E133" s="29"/>
-      <c r="F133" s="29"/>
-      <c r="G133" s="29"/>
+      <c r="A133" s="25"/>
+      <c r="B133" s="26"/>
+      <c r="C133" s="27"/>
+      <c r="D133" s="26"/>
+      <c r="E133" s="26"/>
+      <c r="F133" s="26"/>
+      <c r="G133" s="26"/>
     </row>
     <row r="134" spans="1:7">
-      <c r="A134" s="28"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="30"/>
-      <c r="D134" s="29"/>
-      <c r="E134" s="29"/>
-      <c r="F134" s="29"/>
-      <c r="G134" s="29"/>
+      <c r="A134" s="25"/>
+      <c r="B134" s="26"/>
+      <c r="C134" s="27"/>
+      <c r="D134" s="26"/>
+      <c r="E134" s="26"/>
+      <c r="F134" s="26"/>
+      <c r="G134" s="26"/>
     </row>
     <row r="135" spans="1:7">
-      <c r="A135" s="28"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="30"/>
-      <c r="D135" s="29"/>
-      <c r="E135" s="29"/>
-      <c r="F135" s="29"/>
-      <c r="G135" s="29"/>
+      <c r="A135" s="25"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="27"/>
+      <c r="D135" s="26"/>
+      <c r="E135" s="26"/>
+      <c r="F135" s="26"/>
+      <c r="G135" s="26"/>
     </row>
     <row r="136" spans="1:7">
-      <c r="A136" s="28"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="30"/>
-      <c r="D136" s="29"/>
-      <c r="E136" s="29"/>
-      <c r="F136" s="29"/>
-      <c r="G136" s="29"/>
+      <c r="A136" s="25"/>
+      <c r="B136" s="26"/>
+      <c r="C136" s="27"/>
+      <c r="D136" s="26"/>
+      <c r="E136" s="26"/>
+      <c r="F136" s="26"/>
+      <c r="G136" s="26"/>
     </row>
     <row r="137" spans="1:7">
-      <c r="A137" s="28"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="30"/>
-      <c r="D137" s="29"/>
-      <c r="E137" s="29"/>
-      <c r="F137" s="29"/>
-      <c r="G137" s="29"/>
+      <c r="A137" s="25"/>
+      <c r="B137" s="26"/>
+      <c r="C137" s="27"/>
+      <c r="D137" s="26"/>
+      <c r="E137" s="26"/>
+      <c r="F137" s="26"/>
+      <c r="G137" s="26"/>
     </row>
     <row r="138" spans="1:7">
-      <c r="A138" s="28"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="30"/>
-      <c r="D138" s="29"/>
-      <c r="E138" s="29"/>
-      <c r="F138" s="29"/>
-      <c r="G138" s="29"/>
+      <c r="A138" s="25"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="27"/>
+      <c r="D138" s="26"/>
+      <c r="E138" s="26"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="26"/>
     </row>
     <row r="139" spans="1:7">
-      <c r="A139" s="28"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="30"/>
-      <c r="D139" s="29"/>
-      <c r="E139" s="29"/>
-      <c r="F139" s="29"/>
-      <c r="G139" s="29"/>
+      <c r="A139" s="25"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="27"/>
+      <c r="D139" s="26"/>
+      <c r="E139" s="26"/>
+      <c r="F139" s="26"/>
+      <c r="G139" s="26"/>
     </row>
     <row r="140" spans="1:7">
-      <c r="A140" s="28"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="30"/>
-      <c r="D140" s="29"/>
-      <c r="E140" s="29"/>
-      <c r="F140" s="29"/>
-      <c r="G140" s="29"/>
+      <c r="A140" s="25"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="27"/>
+      <c r="D140" s="26"/>
+      <c r="E140" s="26"/>
+      <c r="F140" s="26"/>
+      <c r="G140" s="26"/>
     </row>
     <row r="141" spans="1:7">
-      <c r="A141" s="28"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="30"/>
-      <c r="D141" s="29"/>
-      <c r="E141" s="29"/>
-      <c r="F141" s="29"/>
-      <c r="G141" s="29"/>
+      <c r="A141" s="25"/>
+      <c r="B141" s="26"/>
+      <c r="C141" s="27"/>
+      <c r="D141" s="26"/>
+      <c r="E141" s="26"/>
+      <c r="F141" s="26"/>
+      <c r="G141" s="26"/>
     </row>
     <row r="142" spans="1:7">
-      <c r="A142" s="28"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="30"/>
-      <c r="D142" s="29"/>
-      <c r="E142" s="29"/>
-      <c r="F142" s="29"/>
-      <c r="G142" s="29"/>
+      <c r="A142" s="25"/>
+      <c r="B142" s="26"/>
+      <c r="C142" s="27"/>
+      <c r="D142" s="26"/>
+      <c r="E142" s="26"/>
+      <c r="F142" s="26"/>
+      <c r="G142" s="26"/>
     </row>
     <row r="143" spans="1:7">
-      <c r="A143" s="28"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="30"/>
-      <c r="D143" s="29"/>
-      <c r="E143" s="29"/>
-      <c r="F143" s="29"/>
-      <c r="G143" s="29"/>
+      <c r="A143" s="25"/>
+      <c r="B143" s="26"/>
+      <c r="C143" s="27"/>
+      <c r="D143" s="26"/>
+      <c r="E143" s="26"/>
+      <c r="F143" s="26"/>
+      <c r="G143" s="26"/>
     </row>
     <row r="144" spans="1:7">
-      <c r="A144" s="28"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="30"/>
-      <c r="D144" s="29"/>
-      <c r="E144" s="29"/>
-      <c r="F144" s="29"/>
-      <c r="G144" s="29"/>
+      <c r="A144" s="25"/>
+      <c r="B144" s="26"/>
+      <c r="C144" s="27"/>
+      <c r="D144" s="26"/>
+      <c r="E144" s="26"/>
+      <c r="F144" s="26"/>
+      <c r="G144" s="26"/>
     </row>
     <row r="145" spans="1:7">
-      <c r="A145" s="28"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="30"/>
-      <c r="D145" s="29"/>
-      <c r="E145" s="29"/>
-      <c r="F145" s="29"/>
-      <c r="G145" s="29"/>
+      <c r="A145" s="25"/>
+      <c r="B145" s="26"/>
+      <c r="C145" s="27"/>
+      <c r="D145" s="26"/>
+      <c r="E145" s="26"/>
+      <c r="F145" s="26"/>
+      <c r="G145" s="26"/>
     </row>
     <row r="146" spans="1:7">
-      <c r="A146" s="28"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="30"/>
-      <c r="D146" s="29"/>
-      <c r="E146" s="29"/>
-      <c r="F146" s="29"/>
-      <c r="G146" s="29"/>
+      <c r="A146" s="25"/>
+      <c r="B146" s="26"/>
+      <c r="C146" s="27"/>
+      <c r="D146" s="26"/>
+      <c r="E146" s="26"/>
+      <c r="F146" s="26"/>
+      <c r="G146" s="26"/>
     </row>
     <row r="147" spans="1:7">
-      <c r="A147" s="28"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="30"/>
-      <c r="D147" s="29"/>
-      <c r="E147" s="29"/>
-      <c r="F147" s="29"/>
-      <c r="G147" s="29"/>
+      <c r="A147" s="25"/>
+      <c r="B147" s="26"/>
+      <c r="C147" s="27"/>
+      <c r="D147" s="26"/>
+      <c r="E147" s="26"/>
+      <c r="F147" s="26"/>
+      <c r="G147" s="26"/>
     </row>
     <row r="148" spans="1:7">
-      <c r="A148" s="28"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="30"/>
-      <c r="D148" s="29"/>
-      <c r="E148" s="29"/>
-      <c r="F148" s="29"/>
-      <c r="G148" s="29"/>
+      <c r="A148" s="25"/>
+      <c r="B148" s="26"/>
+      <c r="C148" s="27"/>
+      <c r="D148" s="26"/>
+      <c r="E148" s="26"/>
+      <c r="F148" s="26"/>
+      <c r="G148" s="26"/>
     </row>
     <row r="149" spans="1:7">
-      <c r="A149" s="28"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="30"/>
-      <c r="D149" s="29"/>
-      <c r="E149" s="29"/>
-      <c r="F149" s="29"/>
-      <c r="G149" s="29"/>
+      <c r="A149" s="25"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="27"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26"/>
     </row>
     <row r="150" spans="1:7">
-      <c r="A150" s="28"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="30"/>
-      <c r="D150" s="29"/>
-      <c r="E150" s="29"/>
-      <c r="F150" s="29"/>
-      <c r="G150" s="29"/>
+      <c r="A150" s="25"/>
+      <c r="B150" s="26"/>
+      <c r="C150" s="27"/>
+      <c r="D150" s="26"/>
+      <c r="E150" s="26"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="26"/>
     </row>
     <row r="151" spans="1:7">
-      <c r="A151" s="28"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="30"/>
-      <c r="D151" s="29"/>
-      <c r="E151" s="29"/>
-      <c r="F151" s="29"/>
-      <c r="G151" s="29"/>
+      <c r="A151" s="25"/>
+      <c r="B151" s="26"/>
+      <c r="C151" s="27"/>
+      <c r="D151" s="26"/>
+      <c r="E151" s="26"/>
+      <c r="F151" s="26"/>
+      <c r="G151" s="26"/>
     </row>
     <row r="152" spans="1:7">
-      <c r="A152" s="28"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="30"/>
-      <c r="D152" s="29"/>
-      <c r="E152" s="29"/>
-      <c r="F152" s="29"/>
-      <c r="G152" s="29"/>
+      <c r="A152" s="25"/>
+      <c r="B152" s="26"/>
+      <c r="C152" s="27"/>
+      <c r="D152" s="26"/>
+      <c r="E152" s="26"/>
+      <c r="F152" s="26"/>
+      <c r="G152" s="26"/>
     </row>
     <row r="153" spans="1:7">
-      <c r="A153" s="28"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="30"/>
-      <c r="D153" s="29"/>
-      <c r="E153" s="29"/>
-      <c r="F153" s="29"/>
-      <c r="G153" s="29"/>
+      <c r="A153" s="25"/>
+      <c r="B153" s="26"/>
+      <c r="C153" s="27"/>
+      <c r="D153" s="26"/>
+      <c r="E153" s="26"/>
+      <c r="F153" s="26"/>
+      <c r="G153" s="26"/>
     </row>
     <row r="154" spans="1:7">
-      <c r="A154" s="28"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="30"/>
-      <c r="D154" s="29"/>
-      <c r="E154" s="29"/>
-      <c r="F154" s="29"/>
-      <c r="G154" s="29"/>
+      <c r="A154" s="25"/>
+      <c r="B154" s="26"/>
+      <c r="C154" s="27"/>
+      <c r="D154" s="26"/>
+      <c r="E154" s="26"/>
+      <c r="F154" s="26"/>
+      <c r="G154" s="26"/>
     </row>
     <row r="155" spans="1:7">
-      <c r="A155" s="28"/>
-      <c r="B155" s="29"/>
-      <c r="C155" s="30"/>
-      <c r="D155" s="29"/>
-      <c r="E155" s="29"/>
-      <c r="F155" s="29"/>
-      <c r="G155" s="29"/>
+      <c r="A155" s="25"/>
+      <c r="B155" s="26"/>
+      <c r="C155" s="27"/>
+      <c r="D155" s="26"/>
+      <c r="E155" s="26"/>
+      <c r="F155" s="26"/>
+      <c r="G155" s="26"/>
     </row>
     <row r="156" spans="1:7">
-      <c r="A156" s="28"/>
-      <c r="B156" s="29"/>
-      <c r="C156" s="30"/>
-      <c r="D156" s="29"/>
-      <c r="E156" s="29"/>
-      <c r="F156" s="29"/>
-      <c r="G156" s="29"/>
+      <c r="A156" s="25"/>
+      <c r="B156" s="26"/>
+      <c r="C156" s="27"/>
+      <c r="D156" s="26"/>
+      <c r="E156" s="26"/>
+      <c r="F156" s="26"/>
+      <c r="G156" s="26"/>
     </row>
     <row r="157" spans="1:7">
-      <c r="A157" s="28"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="30"/>
-      <c r="D157" s="29"/>
-      <c r="E157" s="29"/>
-      <c r="F157" s="29"/>
-      <c r="G157" s="29"/>
+      <c r="A157" s="25"/>
+      <c r="B157" s="26"/>
+      <c r="C157" s="27"/>
+      <c r="D157" s="26"/>
+      <c r="E157" s="26"/>
+      <c r="F157" s="26"/>
+      <c r="G157" s="26"/>
     </row>
     <row r="158" spans="1:7">
-      <c r="A158" s="28"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="30"/>
-      <c r="D158" s="29"/>
-      <c r="E158" s="29"/>
-      <c r="F158" s="29"/>
-      <c r="G158" s="29"/>
+      <c r="A158" s="25"/>
+      <c r="B158" s="26"/>
+      <c r="C158" s="27"/>
+      <c r="D158" s="26"/>
+      <c r="E158" s="26"/>
+      <c r="F158" s="26"/>
+      <c r="G158" s="26"/>
     </row>
     <row r="159" spans="1:7">
-      <c r="A159" s="28"/>
-      <c r="B159" s="29"/>
-      <c r="C159" s="30"/>
-      <c r="D159" s="29"/>
-      <c r="E159" s="29"/>
-      <c r="F159" s="29"/>
-      <c r="G159" s="29"/>
+      <c r="A159" s="25"/>
+      <c r="B159" s="26"/>
+      <c r="C159" s="27"/>
+      <c r="D159" s="26"/>
+      <c r="E159" s="26"/>
+      <c r="F159" s="26"/>
+      <c r="G159" s="26"/>
     </row>
     <row r="160" spans="1:7">
-      <c r="A160" s="28"/>
-      <c r="B160" s="29"/>
-      <c r="C160" s="30"/>
-      <c r="D160" s="29"/>
-      <c r="E160" s="29"/>
-      <c r="F160" s="29"/>
-      <c r="G160" s="29"/>
+      <c r="A160" s="25"/>
+      <c r="B160" s="26"/>
+      <c r="C160" s="27"/>
+      <c r="D160" s="26"/>
+      <c r="E160" s="26"/>
+      <c r="F160" s="26"/>
+      <c r="G160" s="26"/>
     </row>
     <row r="161" spans="1:7">
-      <c r="A161" s="28"/>
-      <c r="B161" s="29"/>
-      <c r="C161" s="30"/>
-      <c r="D161" s="29"/>
-      <c r="E161" s="29"/>
-      <c r="F161" s="29"/>
-      <c r="G161" s="29"/>
+      <c r="A161" s="25"/>
+      <c r="B161" s="26"/>
+      <c r="C161" s="27"/>
+      <c r="D161" s="26"/>
+      <c r="E161" s="26"/>
+      <c r="F161" s="26"/>
+      <c r="G161" s="26"/>
     </row>
     <row r="162" spans="1:7">
-      <c r="A162" s="31"/>
-      <c r="B162" s="29"/>
-      <c r="C162" s="30"/>
-      <c r="D162" s="29"/>
-      <c r="E162" s="29"/>
-      <c r="F162" s="29"/>
-      <c r="G162" s="29"/>
+      <c r="A162" s="28"/>
+      <c r="B162" s="26"/>
+      <c r="C162" s="27"/>
+      <c r="D162" s="26"/>
+      <c r="E162" s="26"/>
+      <c r="F162" s="26"/>
+      <c r="G162" s="26"/>
     </row>
     <row r="163" spans="1:7">
-      <c r="A163" s="31"/>
-      <c r="B163" s="29"/>
-      <c r="C163" s="30"/>
-      <c r="D163" s="29"/>
-      <c r="E163" s="29"/>
-      <c r="F163" s="29"/>
-      <c r="G163" s="29"/>
+      <c r="A163" s="28"/>
+      <c r="B163" s="26"/>
+      <c r="C163" s="27"/>
+      <c r="D163" s="26"/>
+      <c r="E163" s="26"/>
+      <c r="F163" s="26"/>
+      <c r="G163" s="26"/>
     </row>
     <row r="164" spans="1:7">
-      <c r="A164" s="31"/>
-      <c r="B164" s="29"/>
-      <c r="C164" s="30"/>
-      <c r="D164" s="29"/>
-      <c r="E164" s="29"/>
-      <c r="F164" s="29"/>
-      <c r="G164" s="29"/>
+      <c r="A164" s="28"/>
+      <c r="B164" s="26"/>
+      <c r="C164" s="27"/>
+      <c r="D164" s="26"/>
+      <c r="E164" s="26"/>
+      <c r="F164" s="26"/>
+      <c r="G164" s="26"/>
     </row>
     <row r="165" spans="1:7">
-      <c r="A165" s="31"/>
-      <c r="B165" s="29"/>
-      <c r="C165" s="30"/>
-      <c r="D165" s="29"/>
-      <c r="E165" s="29"/>
-      <c r="F165" s="29"/>
-      <c r="G165" s="29"/>
+      <c r="A165" s="28"/>
+      <c r="B165" s="26"/>
+      <c r="C165" s="27"/>
+      <c r="D165" s="26"/>
+      <c r="E165" s="26"/>
+      <c r="F165" s="26"/>
+      <c r="G165" s="26"/>
     </row>
     <row r="166" spans="1:7">
-      <c r="A166" s="31"/>
-      <c r="B166" s="29"/>
-      <c r="C166" s="30"/>
-      <c r="D166" s="29"/>
-      <c r="E166" s="29"/>
-      <c r="F166" s="29"/>
-      <c r="G166" s="29"/>
+      <c r="A166" s="28"/>
+      <c r="B166" s="26"/>
+      <c r="C166" s="27"/>
+      <c r="D166" s="26"/>
+      <c r="E166" s="26"/>
+      <c r="F166" s="26"/>
+      <c r="G166" s="26"/>
     </row>
     <row r="167" spans="1:7">
-      <c r="A167" s="31"/>
-      <c r="B167" s="29"/>
-      <c r="C167" s="30"/>
-      <c r="D167" s="29"/>
-      <c r="E167" s="29"/>
-      <c r="F167" s="29"/>
-      <c r="G167" s="29"/>
+      <c r="A167" s="28"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="27"/>
+      <c r="D167" s="26"/>
+      <c r="E167" s="26"/>
+      <c r="F167" s="26"/>
+      <c r="G167" s="26"/>
     </row>
     <row r="168" spans="1:7">
-      <c r="A168" s="32"/>
-      <c r="B168" s="33"/>
-      <c r="C168" s="34"/>
-      <c r="D168" s="33"/>
-      <c r="E168" s="33"/>
-      <c r="F168" s="33"/>
-      <c r="G168" s="33"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="30"/>
+      <c r="C168" s="31"/>
+      <c r="D168" s="30"/>
+      <c r="E168" s="30"/>
+      <c r="F168" s="30"/>
+      <c r="G168" s="30"/>
     </row>
     <row r="169" spans="1:7">
-      <c r="A169" s="32"/>
-      <c r="B169" s="33"/>
-      <c r="C169" s="34"/>
-      <c r="D169" s="33"/>
-      <c r="E169" s="33"/>
-      <c r="F169" s="33"/>
-      <c r="G169" s="33"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="30"/>
+      <c r="C169" s="31"/>
+      <c r="D169" s="30"/>
+      <c r="E169" s="30"/>
+      <c r="F169" s="30"/>
+      <c r="G169" s="30"/>
     </row>
     <row r="170" spans="1:7">
-      <c r="A170" s="35"/>
-      <c r="B170" s="33"/>
-      <c r="C170" s="34"/>
-      <c r="D170" s="33"/>
-      <c r="E170" s="33"/>
-      <c r="F170" s="33"/>
-      <c r="G170" s="33"/>
+      <c r="A170" s="32"/>
+      <c r="B170" s="30"/>
+      <c r="C170" s="31"/>
+      <c r="D170" s="30"/>
+      <c r="E170" s="30"/>
+      <c r="F170" s="30"/>
+      <c r="G170" s="30"/>
     </row>
     <row r="171" spans="1:7">
-      <c r="A171" s="36"/>
-      <c r="B171" s="33"/>
-      <c r="C171" s="34"/>
-      <c r="D171" s="33"/>
-      <c r="E171" s="33"/>
-      <c r="F171" s="33"/>
-      <c r="G171" s="33"/>
+      <c r="A171" s="33"/>
+      <c r="B171" s="30"/>
+      <c r="C171" s="31"/>
+      <c r="D171" s="30"/>
+      <c r="E171" s="30"/>
+      <c r="F171" s="30"/>
+      <c r="G171" s="30"/>
     </row>
     <row r="172" spans="1:7">
-      <c r="A172" s="36"/>
-      <c r="B172" s="33"/>
-      <c r="C172" s="34"/>
-      <c r="D172" s="33"/>
-      <c r="E172" s="33"/>
-      <c r="F172" s="33"/>
-      <c r="G172" s="33"/>
+      <c r="A172" s="33"/>
+      <c r="B172" s="30"/>
+      <c r="C172" s="31"/>
+      <c r="D172" s="30"/>
+      <c r="E172" s="30"/>
+      <c r="F172" s="30"/>
+      <c r="G172" s="30"/>
     </row>
     <row r="173" spans="1:7">
-      <c r="A173" s="36"/>
-      <c r="B173" s="33"/>
-      <c r="C173" s="34"/>
-      <c r="D173" s="33"/>
-      <c r="E173" s="33"/>
-      <c r="F173" s="33"/>
-      <c r="G173" s="33"/>
+      <c r="A173" s="33"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="31"/>
+      <c r="D173" s="30"/>
+      <c r="E173" s="30"/>
+      <c r="F173" s="30"/>
+      <c r="G173" s="30"/>
     </row>
     <row r="174" spans="1:7">
-      <c r="A174" s="36"/>
-      <c r="B174" s="33"/>
-      <c r="C174" s="34"/>
-      <c r="D174" s="33"/>
-      <c r="E174" s="33"/>
-      <c r="F174" s="33"/>
-      <c r="G174" s="33"/>
+      <c r="A174" s="33"/>
+      <c r="B174" s="30"/>
+      <c r="C174" s="31"/>
+      <c r="D174" s="30"/>
+      <c r="E174" s="30"/>
+      <c r="F174" s="30"/>
+      <c r="G174" s="30"/>
     </row>
     <row r="175" spans="1:7">
-      <c r="A175" s="36"/>
-      <c r="B175" s="33"/>
-      <c r="C175" s="34"/>
-      <c r="D175" s="33"/>
-      <c r="E175" s="33"/>
-      <c r="F175" s="33"/>
-      <c r="G175" s="33"/>
+      <c r="A175" s="33"/>
+      <c r="B175" s="30"/>
+      <c r="C175" s="31"/>
+      <c r="D175" s="30"/>
+      <c r="E175" s="30"/>
+      <c r="F175" s="30"/>
+      <c r="G175" s="30"/>
     </row>
     <row r="176" spans="1:7">
-      <c r="A176" s="36"/>
-      <c r="B176" s="33"/>
-      <c r="C176" s="34"/>
-      <c r="D176" s="33"/>
-      <c r="E176" s="33"/>
-      <c r="F176" s="33"/>
-      <c r="G176" s="33"/>
+      <c r="A176" s="33"/>
+      <c r="B176" s="30"/>
+      <c r="C176" s="31"/>
+      <c r="D176" s="30"/>
+      <c r="E176" s="30"/>
+      <c r="F176" s="30"/>
+      <c r="G176" s="30"/>
     </row>
     <row r="177" spans="1:7">
-      <c r="A177" s="36"/>
-      <c r="B177" s="33"/>
-      <c r="C177" s="34"/>
-      <c r="D177" s="33"/>
-      <c r="E177" s="33"/>
-      <c r="F177" s="33"/>
-      <c r="G177" s="33"/>
+      <c r="A177" s="33"/>
+      <c r="B177" s="30"/>
+      <c r="C177" s="31"/>
+      <c r="D177" s="30"/>
+      <c r="E177" s="30"/>
+      <c r="F177" s="30"/>
+      <c r="G177" s="30"/>
     </row>
     <row r="178" spans="1:7">
-      <c r="A178" s="36"/>
-      <c r="B178" s="33"/>
-      <c r="C178" s="34"/>
-      <c r="D178" s="33"/>
-      <c r="E178" s="33"/>
-      <c r="F178" s="33"/>
-      <c r="G178" s="33"/>
+      <c r="A178" s="33"/>
+      <c r="B178" s="30"/>
+      <c r="C178" s="31"/>
+      <c r="D178" s="30"/>
+      <c r="E178" s="30"/>
+      <c r="F178" s="30"/>
+      <c r="G178" s="30"/>
     </row>
     <row r="179" spans="1:7">
-      <c r="A179" s="36"/>
-      <c r="B179" s="33"/>
-      <c r="C179" s="34"/>
-      <c r="D179" s="33"/>
-      <c r="E179" s="33"/>
-      <c r="F179" s="33"/>
-      <c r="G179" s="33"/>
+      <c r="A179" s="33"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="31"/>
+      <c r="D179" s="30"/>
+      <c r="E179" s="30"/>
+      <c r="F179" s="30"/>
+      <c r="G179" s="30"/>
     </row>
     <row r="180" spans="1:7">
-      <c r="A180" s="36"/>
-      <c r="B180" s="33"/>
-      <c r="C180" s="34"/>
-      <c r="D180" s="33"/>
-      <c r="E180" s="33"/>
-      <c r="F180" s="33"/>
-      <c r="G180" s="33"/>
+      <c r="A180" s="33"/>
+      <c r="B180" s="30"/>
+      <c r="C180" s="31"/>
+      <c r="D180" s="30"/>
+      <c r="E180" s="30"/>
+      <c r="F180" s="30"/>
+      <c r="G180" s="30"/>
     </row>
     <row r="181" spans="1:7">
-      <c r="A181" s="36"/>
-      <c r="B181" s="33"/>
-      <c r="C181" s="34"/>
-      <c r="D181" s="33"/>
-      <c r="E181" s="33"/>
-      <c r="F181" s="33"/>
-      <c r="G181" s="33"/>
+      <c r="A181" s="33"/>
+      <c r="B181" s="30"/>
+      <c r="C181" s="31"/>
+      <c r="D181" s="30"/>
+      <c r="E181" s="30"/>
+      <c r="F181" s="30"/>
+      <c r="G181" s="30"/>
     </row>
     <row r="182" spans="1:7">
-      <c r="A182" s="36"/>
-      <c r="B182" s="33"/>
-      <c r="C182" s="34"/>
-      <c r="D182" s="33"/>
-      <c r="E182" s="33"/>
-      <c r="F182" s="33"/>
-      <c r="G182" s="33"/>
+      <c r="A182" s="33"/>
+      <c r="B182" s="30"/>
+      <c r="C182" s="31"/>
+      <c r="D182" s="30"/>
+      <c r="E182" s="30"/>
+      <c r="F182" s="30"/>
+      <c r="G182" s="30"/>
     </row>
     <row r="183" spans="1:7">
-      <c r="A183" s="36"/>
-      <c r="B183" s="33"/>
-      <c r="C183" s="34"/>
-      <c r="D183" s="33"/>
-      <c r="E183" s="33"/>
-      <c r="F183" s="33"/>
-      <c r="G183" s="33"/>
+      <c r="A183" s="33"/>
+      <c r="B183" s="30"/>
+      <c r="C183" s="31"/>
+      <c r="D183" s="30"/>
+      <c r="E183" s="30"/>
+      <c r="F183" s="30"/>
+      <c r="G183" s="30"/>
     </row>
     <row r="184" spans="1:7">
-      <c r="A184" s="36"/>
-      <c r="B184" s="33"/>
-      <c r="C184" s="34"/>
-      <c r="D184" s="33"/>
-      <c r="E184" s="33"/>
-      <c r="F184" s="33"/>
-      <c r="G184" s="33"/>
+      <c r="A184" s="33"/>
+      <c r="B184" s="30"/>
+      <c r="C184" s="31"/>
+      <c r="D184" s="30"/>
+      <c r="E184" s="30"/>
+      <c r="F184" s="30"/>
+      <c r="G184" s="30"/>
     </row>
     <row r="185" spans="1:7">
-      <c r="A185" s="36"/>
-      <c r="B185" s="33"/>
-      <c r="C185" s="34"/>
-      <c r="D185" s="33"/>
-      <c r="E185" s="33"/>
-      <c r="F185" s="33"/>
-      <c r="G185" s="33"/>
+      <c r="A185" s="33"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="31"/>
+      <c r="D185" s="30"/>
+      <c r="E185" s="30"/>
+      <c r="F185" s="30"/>
+      <c r="G185" s="30"/>
     </row>
     <row r="186" spans="1:7">
-      <c r="A186" s="36"/>
-      <c r="B186" s="33"/>
-      <c r="C186" s="34"/>
-      <c r="D186" s="33"/>
-      <c r="E186" s="33"/>
-      <c r="F186" s="33"/>
-      <c r="G186" s="33"/>
+      <c r="A186" s="33"/>
+      <c r="B186" s="30"/>
+      <c r="C186" s="31"/>
+      <c r="D186" s="30"/>
+      <c r="E186" s="30"/>
+      <c r="F186" s="30"/>
+      <c r="G186" s="30"/>
     </row>
     <row r="187" spans="1:7">
-      <c r="A187" s="36"/>
-      <c r="B187" s="33"/>
-      <c r="C187" s="34"/>
-      <c r="D187" s="33"/>
-      <c r="E187" s="33"/>
-      <c r="F187" s="33"/>
-      <c r="G187" s="33"/>
+      <c r="A187" s="33"/>
+      <c r="B187" s="30"/>
+      <c r="C187" s="31"/>
+      <c r="D187" s="30"/>
+      <c r="E187" s="30"/>
+      <c r="F187" s="30"/>
+      <c r="G187" s="30"/>
     </row>
     <row r="188" spans="1:7">
-      <c r="A188" s="36"/>
-      <c r="B188" s="33"/>
-      <c r="C188" s="34"/>
-      <c r="D188" s="33"/>
-      <c r="E188" s="33"/>
-      <c r="F188" s="33"/>
-      <c r="G188" s="33"/>
+      <c r="A188" s="33"/>
+      <c r="B188" s="30"/>
+      <c r="C188" s="31"/>
+      <c r="D188" s="30"/>
+      <c r="E188" s="30"/>
+      <c r="F188" s="30"/>
+      <c r="G188" s="30"/>
     </row>
     <row r="189" spans="1:7">
-      <c r="A189" s="36"/>
-      <c r="B189" s="33"/>
-      <c r="C189" s="34"/>
-      <c r="D189" s="33"/>
-      <c r="E189" s="33"/>
-      <c r="F189" s="33"/>
-      <c r="G189" s="33"/>
+      <c r="A189" s="33"/>
+      <c r="B189" s="30"/>
+      <c r="C189" s="31"/>
+      <c r="D189" s="30"/>
+      <c r="E189" s="30"/>
+      <c r="F189" s="30"/>
+      <c r="G189" s="30"/>
     </row>
     <row r="190" spans="1:7">
-      <c r="A190" s="36"/>
-      <c r="B190" s="33"/>
-      <c r="C190" s="34"/>
-      <c r="D190" s="33"/>
-      <c r="E190" s="33"/>
-      <c r="F190" s="33"/>
-      <c r="G190" s="33"/>
+      <c r="A190" s="33"/>
+      <c r="B190" s="30"/>
+      <c r="C190" s="31"/>
+      <c r="D190" s="30"/>
+      <c r="E190" s="30"/>
+      <c r="F190" s="30"/>
+      <c r="G190" s="30"/>
     </row>
     <row r="191" spans="1:7">
-      <c r="A191" s="36"/>
-      <c r="B191" s="33"/>
-      <c r="C191" s="34"/>
-      <c r="D191" s="33"/>
-      <c r="E191" s="33"/>
-      <c r="F191" s="33"/>
-      <c r="G191" s="33"/>
+      <c r="A191" s="33"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="31"/>
+      <c r="D191" s="30"/>
+      <c r="E191" s="30"/>
+      <c r="F191" s="30"/>
+      <c r="G191" s="30"/>
     </row>
     <row r="192" spans="1:7">
-      <c r="A192" s="36"/>
-      <c r="B192" s="33"/>
-      <c r="C192" s="34"/>
-      <c r="D192" s="33"/>
-      <c r="E192" s="33"/>
-      <c r="F192" s="33"/>
-      <c r="G192" s="33"/>
+      <c r="A192" s="33"/>
+      <c r="B192" s="30"/>
+      <c r="C192" s="31"/>
+      <c r="D192" s="30"/>
+      <c r="E192" s="30"/>
+      <c r="F192" s="30"/>
+      <c r="G192" s="30"/>
     </row>
     <row r="193" spans="1:7">
-      <c r="A193" s="36"/>
-      <c r="B193" s="33"/>
-      <c r="C193" s="34"/>
-      <c r="D193" s="33"/>
-      <c r="E193" s="33"/>
-      <c r="F193" s="33"/>
-      <c r="G193" s="33"/>
+      <c r="A193" s="33"/>
+      <c r="B193" s="30"/>
+      <c r="C193" s="31"/>
+      <c r="D193" s="30"/>
+      <c r="E193" s="30"/>
+      <c r="F193" s="30"/>
+      <c r="G193" s="30"/>
     </row>
     <row r="194" spans="1:7">
-      <c r="A194" s="36"/>
-      <c r="B194" s="33"/>
-      <c r="C194" s="34"/>
-      <c r="D194" s="33"/>
-      <c r="E194" s="33"/>
-      <c r="F194" s="33"/>
-      <c r="G194" s="33"/>
+      <c r="A194" s="33"/>
+      <c r="B194" s="30"/>
+      <c r="C194" s="31"/>
+      <c r="D194" s="30"/>
+      <c r="E194" s="30"/>
+      <c r="F194" s="30"/>
+      <c r="G194" s="30"/>
     </row>
     <row r="195" spans="1:7">
-      <c r="A195" s="36"/>
-      <c r="B195" s="33"/>
-      <c r="C195" s="34"/>
-      <c r="D195" s="33"/>
-      <c r="E195" s="33"/>
-      <c r="F195" s="33"/>
-      <c r="G195" s="33"/>
+      <c r="A195" s="33"/>
+      <c r="B195" s="30"/>
+      <c r="C195" s="31"/>
+      <c r="D195" s="30"/>
+      <c r="E195" s="30"/>
+      <c r="F195" s="30"/>
+      <c r="G195" s="30"/>
     </row>
     <row r="196" spans="1:7">
-      <c r="A196" s="36"/>
-      <c r="B196" s="33"/>
-      <c r="C196" s="34"/>
-      <c r="D196" s="33"/>
-      <c r="E196" s="33"/>
-      <c r="F196" s="33"/>
-      <c r="G196" s="33"/>
+      <c r="A196" s="33"/>
+      <c r="B196" s="30"/>
+      <c r="C196" s="31"/>
+      <c r="D196" s="30"/>
+      <c r="E196" s="30"/>
+      <c r="F196" s="30"/>
+      <c r="G196" s="30"/>
     </row>
     <row r="197" spans="1:7">
-      <c r="A197" s="36"/>
-      <c r="B197" s="33"/>
-      <c r="C197" s="34"/>
-      <c r="D197" s="33"/>
-      <c r="E197" s="33"/>
-      <c r="F197" s="33"/>
-      <c r="G197" s="33"/>
+      <c r="A197" s="33"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="31"/>
+      <c r="D197" s="30"/>
+      <c r="E197" s="30"/>
+      <c r="F197" s="30"/>
+      <c r="G197" s="30"/>
     </row>
     <row r="198" spans="1:7">
-      <c r="A198" s="36"/>
-      <c r="B198" s="33"/>
-      <c r="C198" s="34"/>
-      <c r="D198" s="33"/>
-      <c r="E198" s="33"/>
-      <c r="F198" s="33"/>
-      <c r="G198" s="33"/>
+      <c r="A198" s="33"/>
+      <c r="B198" s="30"/>
+      <c r="C198" s="31"/>
+      <c r="D198" s="30"/>
+      <c r="E198" s="30"/>
+      <c r="F198" s="30"/>
+      <c r="G198" s="30"/>
     </row>
     <row r="199" spans="1:7">
-      <c r="A199" s="36"/>
-      <c r="B199" s="33"/>
-      <c r="C199" s="34"/>
-      <c r="D199" s="33"/>
-      <c r="E199" s="33"/>
-      <c r="F199" s="33"/>
-      <c r="G199" s="33"/>
+      <c r="A199" s="33"/>
+      <c r="B199" s="30"/>
+      <c r="C199" s="31"/>
+      <c r="D199" s="30"/>
+      <c r="E199" s="30"/>
+      <c r="F199" s="30"/>
+      <c r="G199" s="30"/>
     </row>
     <row r="200" spans="1:7">
-      <c r="A200" s="36"/>
-      <c r="B200" s="33"/>
-      <c r="C200" s="34"/>
-      <c r="D200" s="33"/>
-      <c r="E200" s="33"/>
-      <c r="F200" s="33"/>
-      <c r="G200" s="33"/>
+      <c r="A200" s="33"/>
+      <c r="B200" s="30"/>
+      <c r="C200" s="31"/>
+      <c r="D200" s="30"/>
+      <c r="E200" s="30"/>
+      <c r="F200" s="30"/>
+      <c r="G200" s="30"/>
     </row>
     <row r="201" spans="1:7">
-      <c r="A201" s="36"/>
-      <c r="B201" s="33"/>
-      <c r="C201" s="34"/>
-      <c r="D201" s="33"/>
-      <c r="E201" s="33"/>
-      <c r="F201" s="33"/>
-      <c r="G201" s="33"/>
+      <c r="A201" s="33"/>
+      <c r="B201" s="30"/>
+      <c r="C201" s="31"/>
+      <c r="D201" s="30"/>
+      <c r="E201" s="30"/>
+      <c r="F201" s="30"/>
+      <c r="G201" s="30"/>
     </row>
     <row r="202" spans="1:7">
-      <c r="A202" s="36"/>
-      <c r="B202" s="33"/>
-      <c r="C202" s="34"/>
-      <c r="D202" s="33"/>
-      <c r="E202" s="33"/>
-      <c r="F202" s="33"/>
-      <c r="G202" s="33"/>
+      <c r="A202" s="33"/>
+      <c r="B202" s="30"/>
+      <c r="C202" s="31"/>
+      <c r="D202" s="30"/>
+      <c r="E202" s="30"/>
+      <c r="F202" s="30"/>
+      <c r="G202" s="30"/>
     </row>
     <row r="203" spans="1:7">
-      <c r="A203" s="36"/>
-      <c r="B203" s="33"/>
-      <c r="C203" s="34"/>
-      <c r="D203" s="33"/>
-      <c r="E203" s="33"/>
-      <c r="F203" s="33"/>
-      <c r="G203" s="33"/>
+      <c r="A203" s="33"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="31"/>
+      <c r="D203" s="30"/>
+      <c r="E203" s="30"/>
+      <c r="F203" s="30"/>
+      <c r="G203" s="30"/>
     </row>
     <row r="204" spans="1:7">
-      <c r="A204" s="36"/>
-      <c r="B204" s="33"/>
-      <c r="C204" s="34"/>
-      <c r="D204" s="33"/>
-      <c r="E204" s="33"/>
-      <c r="F204" s="33"/>
-      <c r="G204" s="33"/>
+      <c r="A204" s="33"/>
+      <c r="B204" s="30"/>
+      <c r="C204" s="31"/>
+      <c r="D204" s="30"/>
+      <c r="E204" s="30"/>
+      <c r="F204" s="30"/>
+      <c r="G204" s="30"/>
     </row>
     <row r="205" spans="1:7">
-      <c r="A205" s="36"/>
-      <c r="B205" s="33"/>
-      <c r="C205" s="34"/>
-      <c r="D205" s="33"/>
-      <c r="E205" s="33"/>
-      <c r="F205" s="33"/>
-      <c r="G205" s="33"/>
+      <c r="A205" s="33"/>
+      <c r="B205" s="30"/>
+      <c r="C205" s="31"/>
+      <c r="D205" s="30"/>
+      <c r="E205" s="30"/>
+      <c r="F205" s="30"/>
+      <c r="G205" s="30"/>
     </row>
     <row r="206" spans="1:7">
-      <c r="A206" s="36"/>
-      <c r="B206" s="33"/>
-      <c r="C206" s="34"/>
-      <c r="D206" s="33"/>
-      <c r="E206" s="33"/>
-      <c r="F206" s="33"/>
-      <c r="G206" s="33"/>
+      <c r="A206" s="33"/>
+      <c r="B206" s="30"/>
+      <c r="C206" s="31"/>
+      <c r="D206" s="30"/>
+      <c r="E206" s="30"/>
+      <c r="F206" s="30"/>
+      <c r="G206" s="30"/>
     </row>
     <row r="207" spans="1:7">
-      <c r="A207" s="36"/>
-      <c r="B207" s="33"/>
-      <c r="C207" s="34"/>
-      <c r="D207" s="33"/>
-      <c r="E207" s="33"/>
-      <c r="F207" s="33"/>
-      <c r="G207" s="33"/>
+      <c r="A207" s="33"/>
+      <c r="B207" s="30"/>
+      <c r="C207" s="31"/>
+      <c r="D207" s="30"/>
+      <c r="E207" s="30"/>
+      <c r="F207" s="30"/>
+      <c r="G207" s="30"/>
     </row>
     <row r="208" spans="1:7">
-      <c r="A208" s="36"/>
-      <c r="B208" s="33"/>
-      <c r="C208" s="34"/>
-      <c r="D208" s="33"/>
-      <c r="E208" s="33"/>
-      <c r="F208" s="33"/>
-      <c r="G208" s="33"/>
+      <c r="A208" s="33"/>
+      <c r="B208" s="30"/>
+      <c r="C208" s="31"/>
+      <c r="D208" s="30"/>
+      <c r="E208" s="30"/>
+      <c r="F208" s="30"/>
+      <c r="G208" s="30"/>
     </row>
     <row r="209" spans="1:7">
-      <c r="A209" s="36"/>
-      <c r="B209" s="33"/>
-      <c r="C209" s="34"/>
-      <c r="D209" s="33"/>
-      <c r="E209" s="33"/>
-      <c r="F209" s="33"/>
-      <c r="G209" s="33"/>
+      <c r="A209" s="33"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="31"/>
+      <c r="D209" s="30"/>
+      <c r="E209" s="30"/>
+      <c r="F209" s="30"/>
+      <c r="G209" s="30"/>
     </row>
     <row r="210" spans="1:7">
-      <c r="A210" s="36"/>
-      <c r="B210" s="33"/>
-      <c r="C210" s="34"/>
-      <c r="D210" s="33"/>
-      <c r="E210" s="33"/>
-      <c r="F210" s="33"/>
-      <c r="G210" s="33"/>
+      <c r="A210" s="33"/>
+      <c r="B210" s="30"/>
+      <c r="C210" s="31"/>
+      <c r="D210" s="30"/>
+      <c r="E210" s="30"/>
+      <c r="F210" s="30"/>
+      <c r="G210" s="30"/>
     </row>
     <row r="211" spans="1:7">
-      <c r="A211" s="36"/>
-      <c r="B211" s="33"/>
-      <c r="C211" s="34"/>
-      <c r="D211" s="33"/>
-      <c r="E211" s="33"/>
-      <c r="F211" s="33"/>
-      <c r="G211" s="33"/>
+      <c r="A211" s="33"/>
+      <c r="B211" s="30"/>
+      <c r="C211" s="31"/>
+      <c r="D211" s="30"/>
+      <c r="E211" s="30"/>
+      <c r="F211" s="30"/>
+      <c r="G211" s="30"/>
     </row>
     <row r="212" spans="1:7">
-      <c r="A212" s="36"/>
-      <c r="B212" s="33"/>
-      <c r="C212" s="34"/>
-      <c r="D212" s="33"/>
-      <c r="E212" s="33"/>
-      <c r="F212" s="33"/>
-      <c r="G212" s="33"/>
+      <c r="A212" s="33"/>
+      <c r="B212" s="30"/>
+      <c r="C212" s="31"/>
+      <c r="D212" s="30"/>
+      <c r="E212" s="30"/>
+      <c r="F212" s="30"/>
+      <c r="G212" s="30"/>
     </row>
     <row r="213" spans="1:7">
-      <c r="A213" s="36"/>
-      <c r="B213" s="33"/>
-      <c r="C213" s="34"/>
-      <c r="D213" s="33"/>
-      <c r="E213" s="33"/>
-      <c r="F213" s="33"/>
-      <c r="G213" s="33"/>
+      <c r="A213" s="33"/>
+      <c r="B213" s="30"/>
+      <c r="C213" s="31"/>
+      <c r="D213" s="30"/>
+      <c r="E213" s="30"/>
+      <c r="F213" s="30"/>
+      <c r="G213" s="30"/>
     </row>
     <row r="214" spans="1:7">
-      <c r="A214" s="36"/>
-      <c r="B214" s="33"/>
-      <c r="C214" s="34"/>
-      <c r="D214" s="33"/>
-      <c r="E214" s="33"/>
-      <c r="F214" s="33"/>
-      <c r="G214" s="33"/>
+      <c r="A214" s="33"/>
+      <c r="B214" s="30"/>
+      <c r="C214" s="31"/>
+      <c r="D214" s="30"/>
+      <c r="E214" s="30"/>
+      <c r="F214" s="30"/>
+      <c r="G214" s="30"/>
     </row>
     <row r="215" spans="1:7">
-      <c r="A215" s="36"/>
-      <c r="B215" s="33"/>
-      <c r="C215" s="34"/>
-      <c r="D215" s="33"/>
-      <c r="E215" s="33"/>
-      <c r="F215" s="33"/>
-      <c r="G215" s="33"/>
+      <c r="A215" s="33"/>
+      <c r="B215" s="30"/>
+      <c r="C215" s="31"/>
+      <c r="D215" s="30"/>
+      <c r="E215" s="30"/>
+      <c r="F215" s="30"/>
+      <c r="G215" s="30"/>
     </row>
     <row r="216" spans="1:7">
-      <c r="A216" s="36"/>
-      <c r="B216" s="33"/>
-      <c r="C216" s="34"/>
-      <c r="D216" s="33"/>
-      <c r="E216" s="33"/>
-      <c r="F216" s="33"/>
-      <c r="G216" s="33"/>
+      <c r="A216" s="33"/>
+      <c r="B216" s="30"/>
+      <c r="C216" s="31"/>
+      <c r="D216" s="30"/>
+      <c r="E216" s="30"/>
+      <c r="F216" s="30"/>
+      <c r="G216" s="30"/>
     </row>
     <row r="217" spans="1:7">
-      <c r="A217" s="36"/>
-      <c r="B217" s="33"/>
-      <c r="C217" s="34"/>
-      <c r="D217" s="33"/>
-      <c r="E217" s="33"/>
-      <c r="F217" s="33"/>
-      <c r="G217" s="33"/>
+      <c r="A217" s="33"/>
+      <c r="B217" s="30"/>
+      <c r="C217" s="31"/>
+      <c r="D217" s="30"/>
+      <c r="E217" s="30"/>
+      <c r="F217" s="30"/>
+      <c r="G217" s="30"/>
     </row>
     <row r="218" spans="1:7">
-      <c r="A218" s="36"/>
-      <c r="B218" s="33"/>
-      <c r="C218" s="34"/>
-      <c r="D218" s="33"/>
-      <c r="E218" s="33"/>
-      <c r="F218" s="33"/>
-      <c r="G218" s="33"/>
+      <c r="A218" s="33"/>
+      <c r="B218" s="30"/>
+      <c r="C218" s="31"/>
+      <c r="D218" s="30"/>
+      <c r="E218" s="30"/>
+      <c r="F218" s="30"/>
+      <c r="G218" s="30"/>
     </row>
     <row r="219" spans="1:7">
-      <c r="A219" s="36"/>
-      <c r="B219" s="33"/>
-      <c r="C219" s="34"/>
-      <c r="D219" s="33"/>
-      <c r="E219" s="33"/>
-      <c r="F219" s="33"/>
-      <c r="G219" s="33"/>
+      <c r="A219" s="33"/>
+      <c r="B219" s="30"/>
+      <c r="C219" s="31"/>
+      <c r="D219" s="30"/>
+      <c r="E219" s="30"/>
+      <c r="F219" s="30"/>
+      <c r="G219" s="30"/>
     </row>
     <row r="220" spans="1:7">
-      <c r="A220" s="36"/>
-      <c r="B220" s="33"/>
-      <c r="C220" s="34"/>
-      <c r="D220" s="33"/>
-      <c r="E220" s="33"/>
-      <c r="F220" s="33"/>
-      <c r="G220" s="33"/>
+      <c r="A220" s="33"/>
+      <c r="B220" s="30"/>
+      <c r="C220" s="31"/>
+      <c r="D220" s="30"/>
+      <c r="E220" s="30"/>
+      <c r="F220" s="30"/>
+      <c r="G220" s="30"/>
     </row>
     <row r="221" spans="1:7">
-      <c r="A221" s="36"/>
-      <c r="B221" s="33"/>
-      <c r="C221" s="34"/>
-      <c r="D221" s="33"/>
-      <c r="E221" s="33"/>
-      <c r="F221" s="33"/>
-      <c r="G221" s="33"/>
+      <c r="A221" s="33"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="31"/>
+      <c r="D221" s="30"/>
+      <c r="E221" s="30"/>
+      <c r="F221" s="30"/>
+      <c r="G221" s="30"/>
     </row>
     <row r="222" spans="1:7">
-      <c r="A222" s="36"/>
-      <c r="B222" s="33"/>
-      <c r="C222" s="34"/>
-      <c r="D222" s="33"/>
-      <c r="E222" s="33"/>
-      <c r="F222" s="33"/>
-      <c r="G222" s="33"/>
+      <c r="A222" s="33"/>
+      <c r="B222" s="30"/>
+      <c r="C222" s="31"/>
+      <c r="D222" s="30"/>
+      <c r="E222" s="30"/>
+      <c r="F222" s="30"/>
+      <c r="G222" s="30"/>
     </row>
     <row r="223" spans="1:7">
-      <c r="A223" s="37"/>
-      <c r="B223" s="33"/>
-      <c r="C223" s="34"/>
-      <c r="D223" s="33"/>
-      <c r="E223" s="33"/>
-      <c r="F223" s="33"/>
-      <c r="G223" s="33"/>
+      <c r="A223" s="34"/>
+      <c r="B223" s="30"/>
+      <c r="C223" s="31"/>
+      <c r="D223" s="30"/>
+      <c r="E223" s="30"/>
+      <c r="F223" s="30"/>
+      <c r="G223" s="30"/>
     </row>
     <row r="224" spans="1:7">
-      <c r="A224" s="37"/>
-      <c r="B224" s="33"/>
-      <c r="C224" s="34"/>
-      <c r="D224" s="33"/>
-      <c r="E224" s="33"/>
-      <c r="F224" s="33"/>
-      <c r="G224" s="33"/>
+      <c r="A224" s="34"/>
+      <c r="B224" s="30"/>
+      <c r="C224" s="31"/>
+      <c r="D224" s="30"/>
+      <c r="E224" s="30"/>
+      <c r="F224" s="30"/>
+      <c r="G224" s="30"/>
     </row>
     <row r="225" spans="1:7">
-      <c r="A225" s="37"/>
-      <c r="B225" s="33"/>
-      <c r="C225" s="34"/>
-      <c r="D225" s="33"/>
-      <c r="E225" s="33"/>
-      <c r="F225" s="33"/>
-      <c r="G225" s="33"/>
+      <c r="A225" s="34"/>
+      <c r="B225" s="30"/>
+      <c r="C225" s="31"/>
+      <c r="D225" s="30"/>
+      <c r="E225" s="30"/>
+      <c r="F225" s="30"/>
+      <c r="G225" s="30"/>
     </row>
     <row r="226" spans="1:7">
-      <c r="A226" s="37"/>
-      <c r="B226" s="33"/>
-      <c r="C226" s="34"/>
-      <c r="D226" s="33"/>
-      <c r="E226" s="33"/>
-      <c r="F226" s="33"/>
-      <c r="G226" s="33"/>
+      <c r="A226" s="34"/>
+      <c r="B226" s="30"/>
+      <c r="C226" s="31"/>
+      <c r="D226" s="30"/>
+      <c r="E226" s="30"/>
+      <c r="F226" s="30"/>
+      <c r="G226" s="30"/>
     </row>
     <row r="227" spans="1:7">
-      <c r="A227" s="37"/>
-      <c r="B227" s="33"/>
-      <c r="C227" s="34"/>
-      <c r="D227" s="33"/>
-      <c r="E227" s="33"/>
-      <c r="F227" s="33"/>
-      <c r="G227" s="33"/>
+      <c r="A227" s="34"/>
+      <c r="B227" s="30"/>
+      <c r="C227" s="31"/>
+      <c r="D227" s="30"/>
+      <c r="E227" s="30"/>
+      <c r="F227" s="30"/>
+      <c r="G227" s="30"/>
     </row>
     <row r="228" spans="1:7">
-      <c r="A228" s="37"/>
-      <c r="B228" s="33"/>
-      <c r="C228" s="34"/>
-      <c r="D228" s="33"/>
-      <c r="E228" s="33"/>
-      <c r="F228" s="33"/>
-      <c r="G228" s="33"/>
+      <c r="A228" s="34"/>
+      <c r="B228" s="30"/>
+      <c r="C228" s="31"/>
+      <c r="D228" s="30"/>
+      <c r="E228" s="30"/>
+      <c r="F228" s="30"/>
+      <c r="G228" s="30"/>
     </row>
     <row r="229" spans="1:7">
-      <c r="A229" s="37"/>
-      <c r="B229" s="33"/>
-      <c r="C229" s="34"/>
-      <c r="D229" s="33"/>
-      <c r="E229" s="33"/>
-      <c r="F229" s="33"/>
-      <c r="G229" s="33"/>
+      <c r="A229" s="34"/>
+      <c r="B229" s="30"/>
+      <c r="C229" s="31"/>
+      <c r="D229" s="30"/>
+      <c r="E229" s="30"/>
+      <c r="F229" s="30"/>
+      <c r="G229" s="30"/>
     </row>
     <row r="230" spans="1:7">
-      <c r="A230" s="37"/>
-      <c r="B230" s="33"/>
-      <c r="C230" s="34"/>
-      <c r="D230" s="33"/>
-      <c r="E230" s="33"/>
-      <c r="F230" s="33"/>
-      <c r="G230" s="33"/>
+      <c r="A230" s="34"/>
+      <c r="B230" s="30"/>
+      <c r="C230" s="31"/>
+      <c r="D230" s="30"/>
+      <c r="E230" s="30"/>
+      <c r="F230" s="30"/>
+      <c r="G230" s="30"/>
     </row>
     <row r="231" spans="1:7">
-      <c r="A231" s="37"/>
-      <c r="B231" s="33"/>
-      <c r="C231" s="34"/>
-      <c r="D231" s="33"/>
-      <c r="E231" s="33"/>
-      <c r="F231" s="33"/>
-      <c r="G231" s="33"/>
+      <c r="A231" s="34"/>
+      <c r="B231" s="30"/>
+      <c r="C231" s="31"/>
+      <c r="D231" s="30"/>
+      <c r="E231" s="30"/>
+      <c r="F231" s="30"/>
+      <c r="G231" s="30"/>
     </row>
     <row r="232" spans="1:7">
-      <c r="A232" s="37"/>
-      <c r="B232" s="33"/>
-      <c r="C232" s="34"/>
-      <c r="D232" s="33"/>
-      <c r="E232" s="33"/>
-      <c r="F232" s="33"/>
-      <c r="G232" s="33"/>
+      <c r="A232" s="34"/>
+      <c r="B232" s="30"/>
+      <c r="C232" s="31"/>
+      <c r="D232" s="30"/>
+      <c r="E232" s="30"/>
+      <c r="F232" s="30"/>
+      <c r="G232" s="30"/>
     </row>
     <row r="233" spans="1:7">
-      <c r="A233" s="37"/>
-      <c r="B233" s="33"/>
-      <c r="C233" s="34"/>
-      <c r="D233" s="33"/>
-      <c r="E233" s="33"/>
-      <c r="F233" s="33"/>
-      <c r="G233" s="33"/>
+      <c r="A233" s="34"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="31"/>
+      <c r="D233" s="30"/>
+      <c r="E233" s="30"/>
+      <c r="F233" s="30"/>
+      <c r="G233" s="30"/>
     </row>
     <row r="234" spans="1:7">
-      <c r="A234" s="37"/>
-      <c r="B234" s="33"/>
-      <c r="C234" s="34"/>
-      <c r="D234" s="33"/>
-      <c r="E234" s="33"/>
-      <c r="F234" s="33"/>
-      <c r="G234" s="33"/>
+      <c r="A234" s="34"/>
+      <c r="B234" s="30"/>
+      <c r="C234" s="31"/>
+      <c r="D234" s="30"/>
+      <c r="E234" s="30"/>
+      <c r="F234" s="30"/>
+      <c r="G234" s="30"/>
     </row>
     <row r="235" spans="1:7">
-      <c r="A235" s="37"/>
-      <c r="B235" s="33"/>
-      <c r="C235" s="34"/>
-      <c r="D235" s="33"/>
-      <c r="E235" s="33"/>
-      <c r="F235" s="33"/>
-      <c r="G235" s="33"/>
+      <c r="A235" s="34"/>
+      <c r="B235" s="30"/>
+      <c r="C235" s="31"/>
+      <c r="D235" s="30"/>
+      <c r="E235" s="30"/>
+      <c r="F235" s="30"/>
+      <c r="G235" s="30"/>
     </row>
     <row r="236" spans="1:7">
-      <c r="A236" s="37"/>
-      <c r="B236" s="33"/>
-      <c r="C236" s="34"/>
-      <c r="D236" s="33"/>
-      <c r="E236" s="33"/>
-      <c r="F236" s="33"/>
-      <c r="G236" s="33"/>
+      <c r="A236" s="34"/>
+      <c r="B236" s="30"/>
+      <c r="C236" s="31"/>
+      <c r="D236" s="30"/>
+      <c r="E236" s="30"/>
+      <c r="F236" s="30"/>
+      <c r="G236" s="30"/>
     </row>
     <row r="237" spans="1:7">
-      <c r="A237" s="37"/>
-      <c r="B237" s="33"/>
-      <c r="C237" s="34"/>
-      <c r="D237" s="33"/>
-      <c r="E237" s="33"/>
-      <c r="F237" s="33"/>
-      <c r="G237" s="33"/>
+      <c r="A237" s="34"/>
+      <c r="B237" s="30"/>
+      <c r="C237" s="31"/>
+      <c r="D237" s="30"/>
+      <c r="E237" s="30"/>
+      <c r="F237" s="30"/>
+      <c r="G237" s="30"/>
     </row>
     <row r="238" spans="1:7">
-      <c r="A238" s="37"/>
-      <c r="B238" s="33"/>
-      <c r="C238" s="34"/>
-      <c r="D238" s="33"/>
-      <c r="E238" s="33"/>
-      <c r="F238" s="33"/>
-      <c r="G238" s="33"/>
+      <c r="A238" s="34"/>
+      <c r="B238" s="30"/>
+      <c r="C238" s="31"/>
+      <c r="D238" s="30"/>
+      <c r="E238" s="30"/>
+      <c r="F238" s="30"/>
+      <c r="G238" s="30"/>
     </row>
     <row r="239" spans="1:7">
-      <c r="A239" s="37"/>
-      <c r="B239" s="33"/>
-      <c r="C239" s="34"/>
-      <c r="D239" s="33"/>
-      <c r="E239" s="33"/>
-      <c r="F239" s="33"/>
-      <c r="G239" s="33"/>
+      <c r="A239" s="34"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="31"/>
+      <c r="D239" s="30"/>
+      <c r="E239" s="30"/>
+      <c r="F239" s="30"/>
+      <c r="G239" s="30"/>
     </row>
     <row r="240" spans="1:7">
-      <c r="A240" s="37"/>
-      <c r="B240" s="33"/>
-      <c r="C240" s="34"/>
-      <c r="D240" s="33"/>
-      <c r="E240" s="33"/>
-      <c r="F240" s="33"/>
-      <c r="G240" s="33"/>
+      <c r="A240" s="34"/>
+      <c r="B240" s="30"/>
+      <c r="C240" s="31"/>
+      <c r="D240" s="30"/>
+      <c r="E240" s="30"/>
+      <c r="F240" s="30"/>
+      <c r="G240" s="30"/>
     </row>
     <row r="241" spans="1:7">
-      <c r="A241" s="37"/>
-      <c r="B241" s="33"/>
-      <c r="C241" s="34"/>
-      <c r="D241" s="33"/>
-      <c r="E241" s="33"/>
-      <c r="F241" s="33"/>
-      <c r="G241" s="33"/>
+      <c r="A241" s="34"/>
+      <c r="B241" s="30"/>
+      <c r="C241" s="31"/>
+      <c r="D241" s="30"/>
+      <c r="E241" s="30"/>
+      <c r="F241" s="30"/>
+      <c r="G241" s="30"/>
     </row>
     <row r="242" spans="1:7">
-      <c r="A242" s="37"/>
-      <c r="B242" s="33"/>
-      <c r="C242" s="34"/>
-      <c r="D242" s="33"/>
-      <c r="E242" s="33"/>
-      <c r="F242" s="33"/>
-      <c r="G242" s="33"/>
+      <c r="A242" s="34"/>
+      <c r="B242" s="30"/>
+      <c r="C242" s="31"/>
+      <c r="D242" s="30"/>
+      <c r="E242" s="30"/>
+      <c r="F242" s="30"/>
+      <c r="G242" s="30"/>
     </row>
     <row r="243" spans="1:7">
-      <c r="A243" s="37"/>
-      <c r="B243" s="33"/>
-      <c r="C243" s="34"/>
-      <c r="D243" s="33"/>
-      <c r="E243" s="33"/>
-      <c r="F243" s="33"/>
-      <c r="G243" s="33"/>
+      <c r="A243" s="34"/>
+      <c r="B243" s="30"/>
+      <c r="C243" s="31"/>
+      <c r="D243" s="30"/>
+      <c r="E243" s="30"/>
+      <c r="F243" s="30"/>
+      <c r="G243" s="30"/>
     </row>
     <row r="244" spans="1:7">
-      <c r="A244" s="28"/>
-      <c r="B244" s="29"/>
-      <c r="C244" s="30"/>
-      <c r="D244" s="29"/>
-      <c r="E244" s="29"/>
-      <c r="F244" s="29"/>
-      <c r="G244" s="29"/>
+      <c r="A244" s="25"/>
+      <c r="B244" s="26"/>
+      <c r="C244" s="27"/>
+      <c r="D244" s="26"/>
+      <c r="E244" s="26"/>
+      <c r="F244" s="26"/>
+      <c r="G244" s="26"/>
     </row>
     <row r="245" spans="1:7">
-      <c r="A245" s="28"/>
-      <c r="B245" s="29"/>
-      <c r="C245" s="30"/>
-      <c r="D245" s="29"/>
-      <c r="E245" s="29"/>
-      <c r="F245" s="29"/>
-      <c r="G245" s="29"/>
+      <c r="A245" s="25"/>
+      <c r="B245" s="26"/>
+      <c r="C245" s="27"/>
+      <c r="D245" s="26"/>
+      <c r="E245" s="26"/>
+      <c r="F245" s="26"/>
+      <c r="G245" s="26"/>
     </row>
     <row r="246" spans="1:7">
-      <c r="A246" s="28"/>
-      <c r="B246" s="29"/>
-      <c r="C246" s="30"/>
-      <c r="D246" s="29"/>
-      <c r="E246" s="29"/>
-      <c r="F246" s="29"/>
-      <c r="G246" s="29"/>
+      <c r="A246" s="25"/>
+      <c r="B246" s="26"/>
+      <c r="C246" s="27"/>
+      <c r="D246" s="26"/>
+      <c r="E246" s="26"/>
+      <c r="F246" s="26"/>
+      <c r="G246" s="26"/>
     </row>
     <row r="247" spans="1:7">
-      <c r="A247" s="28"/>
-      <c r="B247" s="29"/>
-      <c r="C247" s="30"/>
-      <c r="D247" s="29"/>
-      <c r="E247" s="29"/>
-      <c r="F247" s="29"/>
-      <c r="G247" s="29"/>
+      <c r="A247" s="25"/>
+      <c r="B247" s="26"/>
+      <c r="C247" s="27"/>
+      <c r="D247" s="26"/>
+      <c r="E247" s="26"/>
+      <c r="F247" s="26"/>
+      <c r="G247" s="26"/>
     </row>
     <row r="248" spans="1:7">
-      <c r="A248" s="28"/>
-      <c r="B248" s="29"/>
-      <c r="C248" s="30"/>
-      <c r="D248" s="29"/>
-      <c r="E248" s="29"/>
-      <c r="F248" s="29"/>
-      <c r="G248" s="29"/>
+      <c r="A248" s="25"/>
+      <c r="B248" s="26"/>
+      <c r="C248" s="27"/>
+      <c r="D248" s="26"/>
+      <c r="E248" s="26"/>
+      <c r="F248" s="26"/>
+      <c r="G248" s="26"/>
     </row>
     <row r="249" spans="1:7">
-      <c r="A249" s="28"/>
-      <c r="B249" s="29"/>
-      <c r="C249" s="30"/>
-      <c r="D249" s="29"/>
-      <c r="E249" s="29"/>
-      <c r="F249" s="29"/>
-      <c r="G249" s="29"/>
+      <c r="A249" s="25"/>
+      <c r="B249" s="26"/>
+      <c r="C249" s="27"/>
+      <c r="D249" s="26"/>
+      <c r="E249" s="26"/>
+      <c r="F249" s="26"/>
+      <c r="G249" s="26"/>
     </row>
     <row r="250" spans="1:7">
-      <c r="A250" s="28"/>
-      <c r="B250" s="29"/>
-      <c r="C250" s="30"/>
-      <c r="D250" s="29"/>
-      <c r="E250" s="29"/>
-      <c r="F250" s="29"/>
-      <c r="G250" s="29"/>
+      <c r="A250" s="25"/>
+      <c r="B250" s="26"/>
+      <c r="C250" s="27"/>
+      <c r="D250" s="26"/>
+      <c r="E250" s="26"/>
+      <c r="F250" s="26"/>
+      <c r="G250" s="26"/>
     </row>
     <row r="251" spans="1:7">
-      <c r="A251" s="28"/>
-      <c r="B251" s="29"/>
-      <c r="C251" s="30"/>
-      <c r="D251" s="29"/>
-      <c r="E251" s="29"/>
-      <c r="F251" s="29"/>
-      <c r="G251" s="29"/>
+      <c r="A251" s="25"/>
+      <c r="B251" s="26"/>
+      <c r="C251" s="27"/>
+      <c r="D251" s="26"/>
+      <c r="E251" s="26"/>
+      <c r="F251" s="26"/>
+      <c r="G251" s="26"/>
     </row>
     <row r="252" spans="1:7">
-      <c r="A252" s="28"/>
-      <c r="B252" s="29"/>
-      <c r="C252" s="30"/>
-      <c r="D252" s="29"/>
-      <c r="E252" s="29"/>
-      <c r="F252" s="29"/>
-      <c r="G252" s="29"/>
+      <c r="A252" s="25"/>
+      <c r="B252" s="26"/>
+      <c r="C252" s="27"/>
+      <c r="D252" s="26"/>
+      <c r="E252" s="26"/>
+      <c r="F252" s="26"/>
+      <c r="G252" s="26"/>
     </row>
     <row r="253" spans="1:7">
-      <c r="A253" s="28"/>
-      <c r="B253" s="29"/>
-      <c r="C253" s="30"/>
-      <c r="D253" s="29"/>
-      <c r="E253" s="29"/>
-      <c r="F253" s="29"/>
-      <c r="G253" s="29"/>
+      <c r="A253" s="25"/>
+      <c r="B253" s="26"/>
+      <c r="C253" s="27"/>
+      <c r="D253" s="26"/>
+      <c r="E253" s="26"/>
+      <c r="F253" s="26"/>
+      <c r="G253" s="26"/>
     </row>
     <row r="254" spans="1:7">
-      <c r="A254" s="28"/>
-      <c r="B254" s="29"/>
-      <c r="C254" s="30"/>
-      <c r="D254" s="29"/>
-      <c r="E254" s="29"/>
-      <c r="F254" s="29"/>
-      <c r="G254" s="29"/>
+      <c r="A254" s="25"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="27"/>
+      <c r="D254" s="26"/>
+      <c r="E254" s="26"/>
+      <c r="F254" s="26"/>
+      <c r="G254" s="26"/>
     </row>
     <row r="255" spans="1:7">
-      <c r="A255" s="28"/>
-      <c r="B255" s="29"/>
-      <c r="C255" s="30"/>
-      <c r="D255" s="29"/>
-      <c r="E255" s="29"/>
-      <c r="F255" s="29"/>
-      <c r="G255" s="29"/>
+      <c r="A255" s="25"/>
+      <c r="B255" s="26"/>
+      <c r="C255" s="27"/>
+      <c r="D255" s="26"/>
+      <c r="E255" s="26"/>
+      <c r="F255" s="26"/>
+      <c r="G255" s="26"/>
     </row>
     <row r="256" spans="1:7">
-      <c r="A256" s="28"/>
-      <c r="B256" s="29"/>
-      <c r="C256" s="30"/>
-      <c r="D256" s="29"/>
-      <c r="E256" s="29"/>
-      <c r="F256" s="29"/>
-      <c r="G256" s="29"/>
+      <c r="A256" s="25"/>
+      <c r="B256" s="26"/>
+      <c r="C256" s="27"/>
+      <c r="D256" s="26"/>
+      <c r="E256" s="26"/>
+      <c r="F256" s="26"/>
+      <c r="G256" s="26"/>
     </row>
     <row r="257" spans="1:7">
-      <c r="A257" s="28"/>
-      <c r="B257" s="29"/>
-      <c r="C257" s="30"/>
-      <c r="D257" s="29"/>
-      <c r="E257" s="29"/>
-      <c r="F257" s="29"/>
-      <c r="G257" s="29"/>
+      <c r="A257" s="25"/>
+      <c r="B257" s="26"/>
+      <c r="C257" s="27"/>
+      <c r="D257" s="26"/>
+      <c r="E257" s="26"/>
+      <c r="F257" s="26"/>
+      <c r="G257" s="26"/>
     </row>
     <row r="258" spans="1:7">
-      <c r="A258" s="28"/>
-      <c r="B258" s="29"/>
-      <c r="C258" s="30"/>
-      <c r="D258" s="29"/>
-      <c r="E258" s="29"/>
-      <c r="F258" s="29"/>
-      <c r="G258" s="29"/>
+      <c r="A258" s="25"/>
+      <c r="B258" s="26"/>
+      <c r="C258" s="27"/>
+      <c r="D258" s="26"/>
+      <c r="E258" s="26"/>
+      <c r="F258" s="26"/>
+      <c r="G258" s="26"/>
     </row>
     <row r="259" spans="1:7">
-      <c r="A259" s="28"/>
-      <c r="B259" s="29"/>
-      <c r="C259" s="30"/>
-      <c r="D259" s="29"/>
-      <c r="E259" s="29"/>
-      <c r="F259" s="29"/>
-      <c r="G259" s="29"/>
+      <c r="A259" s="25"/>
+      <c r="B259" s="26"/>
+      <c r="C259" s="27"/>
+      <c r="D259" s="26"/>
+      <c r="E259" s="26"/>
+      <c r="F259" s="26"/>
+      <c r="G259" s="26"/>
     </row>
     <row r="260" spans="1:7">
-      <c r="A260" s="28"/>
-      <c r="B260" s="29"/>
-      <c r="C260" s="30"/>
-      <c r="D260" s="29"/>
-      <c r="E260" s="29"/>
-      <c r="F260" s="29"/>
-      <c r="G260" s="29"/>
+      <c r="A260" s="25"/>
+      <c r="B260" s="26"/>
+      <c r="C260" s="27"/>
+      <c r="D260" s="26"/>
+      <c r="E260" s="26"/>
+      <c r="F260" s="26"/>
+      <c r="G260" s="26"/>
     </row>
     <row r="261" spans="1:7">
-      <c r="A261" s="28"/>
-      <c r="B261" s="29"/>
-      <c r="C261" s="30"/>
-      <c r="D261" s="29"/>
-      <c r="E261" s="29"/>
-      <c r="F261" s="29"/>
-      <c r="G261" s="29"/>
+      <c r="A261" s="25"/>
+      <c r="B261" s="26"/>
+      <c r="C261" s="27"/>
+      <c r="D261" s="26"/>
+      <c r="E261" s="26"/>
+      <c r="F261" s="26"/>
+      <c r="G261" s="26"/>
     </row>
     <row r="262" spans="1:7">
-      <c r="A262" s="28"/>
-      <c r="B262" s="29"/>
-      <c r="C262" s="30"/>
-      <c r="D262" s="29"/>
-      <c r="E262" s="29"/>
-      <c r="F262" s="29"/>
-      <c r="G262" s="29"/>
+      <c r="A262" s="25"/>
+      <c r="B262" s="26"/>
+      <c r="C262" s="27"/>
+      <c r="D262" s="26"/>
+      <c r="E262" s="26"/>
+      <c r="F262" s="26"/>
+      <c r="G262" s="26"/>
     </row>
     <row r="263" spans="1:7">
-      <c r="A263" s="28"/>
-      <c r="B263" s="29"/>
-      <c r="C263" s="30"/>
-      <c r="D263" s="29"/>
-      <c r="E263" s="29"/>
-      <c r="F263" s="29"/>
-      <c r="G263" s="29"/>
+      <c r="A263" s="25"/>
+      <c r="B263" s="26"/>
+      <c r="C263" s="27"/>
+      <c r="D263" s="26"/>
+      <c r="E263" s="26"/>
+      <c r="F263" s="26"/>
+      <c r="G263" s="26"/>
     </row>
     <row r="264" spans="1:7">
-      <c r="A264" s="28"/>
-      <c r="B264" s="29"/>
-      <c r="C264" s="30"/>
-      <c r="D264" s="29"/>
-      <c r="E264" s="29"/>
-      <c r="F264" s="29"/>
-      <c r="G264" s="29"/>
+      <c r="A264" s="25"/>
+      <c r="B264" s="26"/>
+      <c r="C264" s="27"/>
+      <c r="D264" s="26"/>
+      <c r="E264" s="26"/>
+      <c r="F264" s="26"/>
+      <c r="G264" s="26"/>
     </row>
     <row r="265" spans="1:7">
-      <c r="A265" s="28"/>
-      <c r="B265" s="29"/>
-      <c r="C265" s="30"/>
-      <c r="D265" s="29"/>
-      <c r="E265" s="29"/>
-      <c r="F265" s="29"/>
-      <c r="G265" s="29"/>
+      <c r="A265" s="25"/>
+      <c r="B265" s="26"/>
+      <c r="C265" s="27"/>
+      <c r="D265" s="26"/>
+      <c r="E265" s="26"/>
+      <c r="F265" s="26"/>
+      <c r="G265" s="26"/>
     </row>
     <row r="266" spans="1:7">
-      <c r="A266" s="28"/>
-      <c r="B266" s="29"/>
-      <c r="C266" s="30"/>
-      <c r="D266" s="29"/>
-      <c r="E266" s="29"/>
-      <c r="F266" s="29"/>
-      <c r="G266" s="29"/>
+      <c r="A266" s="25"/>
+      <c r="B266" s="26"/>
+      <c r="C266" s="27"/>
+      <c r="D266" s="26"/>
+      <c r="E266" s="26"/>
+      <c r="F266" s="26"/>
+      <c r="G266" s="26"/>
     </row>
     <row r="267" spans="1:7">
-      <c r="A267" s="28"/>
-      <c r="B267" s="29"/>
-      <c r="C267" s="30"/>
-      <c r="D267" s="29"/>
-      <c r="E267" s="29"/>
-      <c r="F267" s="29"/>
-      <c r="G267" s="29"/>
+      <c r="A267" s="25"/>
+      <c r="B267" s="26"/>
+      <c r="C267" s="27"/>
+      <c r="D267" s="26"/>
+      <c r="E267" s="26"/>
+      <c r="F267" s="26"/>
+      <c r="G267" s="26"/>
     </row>
     <row r="268" spans="1:7">
-      <c r="A268" s="28"/>
-      <c r="B268" s="29"/>
-      <c r="C268" s="30"/>
-      <c r="D268" s="29"/>
-      <c r="E268" s="29"/>
-      <c r="F268" s="29"/>
-      <c r="G268" s="29"/>
+      <c r="A268" s="25"/>
+      <c r="B268" s="26"/>
+      <c r="C268" s="27"/>
+      <c r="D268" s="26"/>
+      <c r="E268" s="26"/>
+      <c r="F268" s="26"/>
+      <c r="G268" s="26"/>
     </row>
     <row r="269" spans="1:7">
-      <c r="A269" s="28"/>
-      <c r="B269" s="29"/>
-      <c r="C269" s="30"/>
-      <c r="D269" s="29"/>
-      <c r="E269" s="29"/>
-      <c r="F269" s="29"/>
-      <c r="G269" s="29"/>
+      <c r="A269" s="25"/>
+      <c r="B269" s="26"/>
+      <c r="C269" s="27"/>
+      <c r="D269" s="26"/>
+      <c r="E269" s="26"/>
+      <c r="F269" s="26"/>
+      <c r="G269" s="26"/>
     </row>
     <row r="270" spans="1:7">
-      <c r="A270" s="28"/>
-      <c r="B270" s="29"/>
-      <c r="C270" s="30"/>
-      <c r="D270" s="29"/>
-      <c r="E270" s="29"/>
-      <c r="F270" s="29"/>
-      <c r="G270" s="29"/>
+      <c r="A270" s="25"/>
+      <c r="B270" s="26"/>
+      <c r="C270" s="27"/>
+      <c r="D270" s="26"/>
+      <c r="E270" s="26"/>
+      <c r="F270" s="26"/>
+      <c r="G270" s="26"/>
     </row>
     <row r="271" spans="1:7">
-      <c r="A271" s="28"/>
-      <c r="B271" s="29"/>
-      <c r="C271" s="30"/>
-      <c r="D271" s="29"/>
-      <c r="E271" s="29"/>
-      <c r="F271" s="29"/>
-      <c r="G271" s="29"/>
+      <c r="A271" s="25"/>
+      <c r="B271" s="26"/>
+      <c r="C271" s="27"/>
+      <c r="D271" s="26"/>
+      <c r="E271" s="26"/>
+      <c r="F271" s="26"/>
+      <c r="G271" s="26"/>
     </row>
     <row r="272" spans="1:7">
-      <c r="A272" s="28"/>
-      <c r="B272" s="29"/>
-      <c r="C272" s="30"/>
-      <c r="D272" s="29"/>
-      <c r="E272" s="29"/>
-      <c r="F272" s="29"/>
-      <c r="G272" s="29"/>
+      <c r="A272" s="25"/>
+      <c r="B272" s="26"/>
+      <c r="C272" s="27"/>
+      <c r="D272" s="26"/>
+      <c r="E272" s="26"/>
+      <c r="F272" s="26"/>
+      <c r="G272" s="26"/>
     </row>
     <row r="273" spans="1:7">
-      <c r="A273" s="28"/>
-      <c r="B273" s="29"/>
-      <c r="C273" s="30"/>
-      <c r="D273" s="29"/>
-      <c r="E273" s="29"/>
-      <c r="F273" s="29"/>
-      <c r="G273" s="29"/>
+      <c r="A273" s="25"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="27"/>
+      <c r="D273" s="26"/>
+      <c r="E273" s="26"/>
+      <c r="F273" s="26"/>
+      <c r="G273" s="26"/>
     </row>
     <row r="274" spans="1:7">
-      <c r="A274" s="28"/>
-      <c r="B274" s="29"/>
-      <c r="C274" s="30"/>
-      <c r="D274" s="29"/>
-      <c r="E274" s="29"/>
-      <c r="F274" s="29"/>
-      <c r="G274" s="29"/>
+      <c r="A274" s="25"/>
+      <c r="B274" s="26"/>
+      <c r="C274" s="27"/>
+      <c r="D274" s="26"/>
+      <c r="E274" s="26"/>
+      <c r="F274" s="26"/>
+      <c r="G274" s="26"/>
     </row>
     <row r="275" spans="1:7">
-      <c r="A275" s="28"/>
-      <c r="B275" s="29"/>
-      <c r="C275" s="30"/>
-      <c r="D275" s="29"/>
-      <c r="E275" s="29"/>
-      <c r="F275" s="29"/>
-      <c r="G275" s="29"/>
+      <c r="A275" s="25"/>
+      <c r="B275" s="26"/>
+      <c r="C275" s="27"/>
+      <c r="D275" s="26"/>
+      <c r="E275" s="26"/>
+      <c r="F275" s="26"/>
+      <c r="G275" s="26"/>
     </row>
     <row r="276" spans="1:7">
-      <c r="A276" s="28"/>
-      <c r="B276" s="29"/>
-      <c r="C276" s="30"/>
-      <c r="D276" s="29"/>
-      <c r="E276" s="29"/>
-      <c r="F276" s="29"/>
-      <c r="G276" s="29"/>
+      <c r="A276" s="25"/>
+      <c r="B276" s="26"/>
+      <c r="C276" s="27"/>
+      <c r="D276" s="26"/>
+      <c r="E276" s="26"/>
+      <c r="F276" s="26"/>
+      <c r="G276" s="26"/>
     </row>
     <row r="277" spans="1:7">
-      <c r="A277" s="28"/>
-      <c r="B277" s="29"/>
-      <c r="C277" s="30"/>
-      <c r="D277" s="29"/>
-      <c r="E277" s="29"/>
-      <c r="F277" s="29"/>
-      <c r="G277" s="29"/>
+      <c r="A277" s="25"/>
+      <c r="B277" s="26"/>
+      <c r="C277" s="27"/>
+      <c r="D277" s="26"/>
+      <c r="E277" s="26"/>
+      <c r="F277" s="26"/>
+      <c r="G277" s="26"/>
     </row>
     <row r="278" spans="1:7">
-      <c r="A278" s="28"/>
-      <c r="B278" s="29"/>
-      <c r="C278" s="30"/>
-      <c r="D278" s="29"/>
-      <c r="E278" s="29"/>
-      <c r="F278" s="29"/>
-      <c r="G278" s="29"/>
+      <c r="A278" s="25"/>
+      <c r="B278" s="26"/>
+      <c r="C278" s="27"/>
+      <c r="D278" s="26"/>
+      <c r="E278" s="26"/>
+      <c r="F278" s="26"/>
+      <c r="G278" s="26"/>
     </row>
     <row r="279" spans="1:7">
-      <c r="A279" s="28"/>
-      <c r="B279" s="29"/>
-      <c r="C279" s="30"/>
-      <c r="D279" s="29"/>
-      <c r="E279" s="29"/>
-      <c r="F279" s="29"/>
-      <c r="G279" s="29"/>
+      <c r="A279" s="25"/>
+      <c r="B279" s="26"/>
+      <c r="C279" s="27"/>
+      <c r="D279" s="26"/>
+      <c r="E279" s="26"/>
+      <c r="F279" s="26"/>
+      <c r="G279" s="26"/>
     </row>
     <row r="280" spans="1:7">
-      <c r="A280" s="28"/>
-      <c r="B280" s="29"/>
-      <c r="C280" s="30"/>
-      <c r="D280" s="29"/>
-      <c r="E280" s="29"/>
-      <c r="F280" s="29"/>
-      <c r="G280" s="29"/>
+      <c r="A280" s="25"/>
+      <c r="B280" s="26"/>
+      <c r="C280" s="27"/>
+      <c r="D280" s="26"/>
+      <c r="E280" s="26"/>
+      <c r="F280" s="26"/>
+      <c r="G280" s="26"/>
     </row>
     <row r="281" spans="1:7">
-      <c r="A281" s="28"/>
-      <c r="B281" s="29"/>
-      <c r="C281" s="30"/>
-      <c r="D281" s="29"/>
-      <c r="E281" s="29"/>
-      <c r="F281" s="29"/>
-      <c r="G281" s="29"/>
+      <c r="A281" s="25"/>
+      <c r="B281" s="26"/>
+      <c r="C281" s="27"/>
+      <c r="D281" s="26"/>
+      <c r="E281" s="26"/>
+      <c r="F281" s="26"/>
+      <c r="G281" s="26"/>
     </row>
     <row r="282" spans="1:7">
-      <c r="A282" s="28"/>
-      <c r="B282" s="29"/>
-      <c r="C282" s="30"/>
-      <c r="D282" s="29"/>
-      <c r="E282" s="29"/>
-      <c r="F282" s="29"/>
-      <c r="G282" s="29"/>
+      <c r="A282" s="25"/>
+      <c r="B282" s="26"/>
+      <c r="C282" s="27"/>
+      <c r="D282" s="26"/>
+      <c r="E282" s="26"/>
+      <c r="F282" s="26"/>
+      <c r="G282" s="26"/>
     </row>
     <row r="283" spans="1:7">
-      <c r="A283" s="28"/>
-      <c r="B283" s="29"/>
-      <c r="C283" s="30"/>
-      <c r="D283" s="29"/>
-      <c r="E283" s="29"/>
-      <c r="F283" s="29"/>
-      <c r="G283" s="29"/>
+      <c r="A283" s="25"/>
+      <c r="B283" s="26"/>
+      <c r="C283" s="27"/>
+      <c r="D283" s="26"/>
+      <c r="E283" s="26"/>
+      <c r="F283" s="26"/>
+      <c r="G283" s="26"/>
     </row>
     <row r="284" spans="1:7">
-      <c r="A284" s="28"/>
-      <c r="B284" s="29"/>
-      <c r="C284" s="30"/>
-      <c r="D284" s="29"/>
-      <c r="E284" s="29"/>
-      <c r="F284" s="29"/>
-      <c r="G284" s="29"/>
+      <c r="A284" s="25"/>
+      <c r="B284" s="26"/>
+      <c r="C284" s="27"/>
+      <c r="D284" s="26"/>
+      <c r="E284" s="26"/>
+      <c r="F284" s="26"/>
+      <c r="G284" s="26"/>
     </row>
     <row r="285" spans="1:7">
-      <c r="A285" s="28"/>
-      <c r="B285" s="29"/>
-      <c r="C285" s="30"/>
-      <c r="D285" s="29"/>
-      <c r="E285" s="29"/>
-      <c r="F285" s="29"/>
-      <c r="G285" s="29"/>
+      <c r="A285" s="25"/>
+      <c r="B285" s="26"/>
+      <c r="C285" s="27"/>
+      <c r="D285" s="26"/>
+      <c r="E285" s="26"/>
+      <c r="F285" s="26"/>
+      <c r="G285" s="26"/>
     </row>
     <row r="286" spans="1:7">
-      <c r="A286" s="28"/>
-      <c r="B286" s="29"/>
-      <c r="C286" s="30"/>
-      <c r="D286" s="29"/>
-      <c r="E286" s="29"/>
-      <c r="F286" s="29"/>
-      <c r="G286" s="29"/>
+      <c r="A286" s="25"/>
+      <c r="B286" s="26"/>
+      <c r="C286" s="27"/>
+      <c r="D286" s="26"/>
+      <c r="E286" s="26"/>
+      <c r="F286" s="26"/>
+      <c r="G286" s="26"/>
     </row>
     <row r="287" spans="1:7">
-      <c r="A287" s="28"/>
-      <c r="B287" s="29"/>
-      <c r="C287" s="30"/>
-      <c r="D287" s="29"/>
-      <c r="E287" s="29"/>
-      <c r="F287" s="29"/>
-      <c r="G287" s="29"/>
+      <c r="A287" s="25"/>
+      <c r="B287" s="26"/>
+      <c r="C287" s="27"/>
+      <c r="D287" s="26"/>
+      <c r="E287" s="26"/>
+      <c r="F287" s="26"/>
+      <c r="G287" s="26"/>
     </row>
     <row r="288" spans="1:7">
-      <c r="A288" s="28"/>
-      <c r="B288" s="29"/>
-      <c r="C288" s="30"/>
-      <c r="D288" s="29"/>
-      <c r="E288" s="29"/>
-      <c r="F288" s="29"/>
-      <c r="G288" s="29"/>
+      <c r="A288" s="25"/>
+      <c r="B288" s="26"/>
+      <c r="C288" s="27"/>
+      <c r="D288" s="26"/>
+      <c r="E288" s="26"/>
+      <c r="F288" s="26"/>
+      <c r="G288" s="26"/>
     </row>
     <row r="289" spans="1:7">
-      <c r="A289" s="28"/>
-      <c r="B289" s="29"/>
-      <c r="C289" s="30"/>
-      <c r="D289" s="29"/>
-      <c r="E289" s="29"/>
-      <c r="F289" s="29"/>
-      <c r="G289" s="29"/>
+      <c r="A289" s="25"/>
+      <c r="B289" s="26"/>
+      <c r="C289" s="27"/>
+      <c r="D289" s="26"/>
+      <c r="E289" s="26"/>
+      <c r="F289" s="26"/>
+      <c r="G289" s="26"/>
     </row>
     <row r="290" spans="1:7">
-      <c r="A290" s="28"/>
-      <c r="B290" s="29"/>
-      <c r="C290" s="30"/>
-      <c r="D290" s="29"/>
-      <c r="E290" s="29"/>
-      <c r="F290" s="29"/>
-      <c r="G290" s="29"/>
+      <c r="A290" s="25"/>
+      <c r="B290" s="26"/>
+      <c r="C290" s="27"/>
+      <c r="D290" s="26"/>
+      <c r="E290" s="26"/>
+      <c r="F290" s="26"/>
+      <c r="G290" s="26"/>
     </row>
     <row r="291" spans="1:7">
-      <c r="A291" s="31"/>
-      <c r="B291" s="29"/>
-      <c r="C291" s="30"/>
-      <c r="D291" s="29"/>
-      <c r="E291" s="29"/>
-      <c r="F291" s="29"/>
-      <c r="G291" s="29"/>
+      <c r="A291" s="28"/>
+      <c r="B291" s="26"/>
+      <c r="C291" s="27"/>
+      <c r="D291" s="26"/>
+      <c r="E291" s="26"/>
+      <c r="F291" s="26"/>
+      <c r="G291" s="26"/>
     </row>
     <row r="292" spans="1:7">
-      <c r="A292" s="31"/>
-      <c r="B292" s="29"/>
-      <c r="C292" s="30"/>
-      <c r="D292" s="29"/>
-      <c r="E292" s="29"/>
-      <c r="F292" s="29"/>
-      <c r="G292" s="29"/>
+      <c r="A292" s="28"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="27"/>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="26"/>
+      <c r="G292" s="26"/>
     </row>
     <row r="293" spans="1:7">
-      <c r="A293" s="31"/>
-      <c r="B293" s="29"/>
-      <c r="C293" s="30"/>
-      <c r="D293" s="29"/>
-      <c r="E293" s="29"/>
-      <c r="F293" s="29"/>
-      <c r="G293" s="29"/>
+      <c r="A293" s="28"/>
+      <c r="B293" s="26"/>
+      <c r="C293" s="27"/>
+      <c r="D293" s="26"/>
+      <c r="E293" s="26"/>
+      <c r="F293" s="26"/>
+      <c r="G293" s="26"/>
     </row>
     <row r="294" spans="1:7">
-      <c r="A294" s="31"/>
-      <c r="B294" s="29"/>
-      <c r="C294" s="30"/>
-      <c r="D294" s="29"/>
-      <c r="E294" s="29"/>
-      <c r="F294" s="29"/>
-      <c r="G294" s="29"/>
+      <c r="A294" s="28"/>
+      <c r="B294" s="26"/>
+      <c r="C294" s="27"/>
+      <c r="D294" s="26"/>
+      <c r="E294" s="26"/>
+      <c r="F294" s="26"/>
+      <c r="G294" s="26"/>
     </row>
     <row r="295" spans="1:7">
-      <c r="A295" s="31"/>
-      <c r="B295" s="29"/>
-      <c r="C295" s="30"/>
-      <c r="D295" s="29"/>
-      <c r="E295" s="29"/>
-      <c r="F295" s="29"/>
-      <c r="G295" s="29"/>
+      <c r="A295" s="28"/>
+      <c r="B295" s="26"/>
+      <c r="C295" s="27"/>
+      <c r="D295" s="26"/>
+      <c r="E295" s="26"/>
+      <c r="F295" s="26"/>
+      <c r="G295" s="26"/>
     </row>
     <row r="296" spans="1:7">
-      <c r="A296" s="31"/>
-      <c r="B296" s="29"/>
-      <c r="C296" s="30"/>
-      <c r="D296" s="29"/>
-      <c r="E296" s="29"/>
-      <c r="F296" s="29"/>
-      <c r="G296" s="29"/>
+      <c r="A296" s="28"/>
+      <c r="B296" s="26"/>
+      <c r="C296" s="27"/>
+      <c r="D296" s="26"/>
+      <c r="E296" s="26"/>
+      <c r="F296" s="26"/>
+      <c r="G296" s="26"/>
     </row>
     <row r="297" spans="1:7">
-      <c r="A297" s="31"/>
-      <c r="B297" s="29"/>
-      <c r="C297" s="30"/>
-      <c r="D297" s="29"/>
-      <c r="E297" s="29"/>
-      <c r="F297" s="29"/>
-      <c r="G297" s="29"/>
+      <c r="A297" s="28"/>
+      <c r="B297" s="26"/>
+      <c r="C297" s="27"/>
+      <c r="D297" s="26"/>
+      <c r="E297" s="26"/>
+      <c r="F297" s="26"/>
+      <c r="G297" s="26"/>
     </row>
     <row r="298" spans="1:7">
-      <c r="A298" s="31"/>
-      <c r="B298" s="29"/>
-      <c r="C298" s="30"/>
-      <c r="D298" s="29"/>
-      <c r="E298" s="29"/>
-      <c r="F298" s="29"/>
-      <c r="G298" s="29"/>
+      <c r="A298" s="28"/>
+      <c r="B298" s="26"/>
+      <c r="C298" s="27"/>
+      <c r="D298" s="26"/>
+      <c r="E298" s="26"/>
+      <c r="F298" s="26"/>
+      <c r="G298" s="26"/>
     </row>
     <row r="299" spans="1:7">
-      <c r="A299" s="31"/>
-      <c r="B299" s="29"/>
-      <c r="C299" s="30"/>
-      <c r="D299" s="29"/>
-      <c r="E299" s="29"/>
-      <c r="F299" s="29"/>
-      <c r="G299" s="29"/>
+      <c r="A299" s="28"/>
+      <c r="B299" s="26"/>
+      <c r="C299" s="27"/>
+      <c r="D299" s="26"/>
+      <c r="E299" s="26"/>
+      <c r="F299" s="26"/>
+      <c r="G299" s="26"/>
     </row>
     <row r="300" spans="1:7">
-      <c r="A300" s="31"/>
-      <c r="B300" s="29"/>
-      <c r="C300" s="30"/>
-      <c r="D300" s="29"/>
-      <c r="E300" s="29"/>
-      <c r="F300" s="29"/>
-      <c r="G300" s="29"/>
+      <c r="A300" s="28"/>
+      <c r="B300" s="26"/>
+      <c r="C300" s="27"/>
+      <c r="D300" s="26"/>
+      <c r="E300" s="26"/>
+      <c r="F300" s="26"/>
+      <c r="G300" s="26"/>
     </row>
     <row r="301" spans="1:7">
-      <c r="A301" s="31"/>
-      <c r="B301" s="29"/>
-      <c r="C301" s="30"/>
-      <c r="D301" s="29"/>
-      <c r="E301" s="29"/>
-      <c r="F301" s="29"/>
-      <c r="G301" s="29"/>
+      <c r="A301" s="28"/>
+      <c r="B301" s="26"/>
+      <c r="C301" s="27"/>
+      <c r="D301" s="26"/>
+      <c r="E301" s="26"/>
+      <c r="F301" s="26"/>
+      <c r="G301" s="26"/>
     </row>
     <row r="302" spans="1:7">
-      <c r="A302" s="31"/>
-      <c r="B302" s="29"/>
-      <c r="C302" s="30"/>
-      <c r="D302" s="29"/>
-      <c r="E302" s="29"/>
-      <c r="F302" s="29"/>
-      <c r="G302" s="29"/>
+      <c r="A302" s="28"/>
+      <c r="B302" s="26"/>
+      <c r="C302" s="27"/>
+      <c r="D302" s="26"/>
+      <c r="E302" s="26"/>
+      <c r="F302" s="26"/>
+      <c r="G302" s="26"/>
     </row>
     <row r="303" spans="1:7">
-      <c r="A303" s="28"/>
-      <c r="B303" s="29"/>
-      <c r="C303" s="30"/>
-      <c r="D303" s="29"/>
-      <c r="E303" s="29"/>
-      <c r="F303" s="29"/>
-      <c r="G303" s="29"/>
+      <c r="A303" s="25"/>
+      <c r="B303" s="26"/>
+      <c r="C303" s="27"/>
+      <c r="D303" s="26"/>
+      <c r="E303" s="26"/>
+      <c r="F303" s="26"/>
+      <c r="G303" s="26"/>
     </row>
     <row r="304" spans="1:7">
-      <c r="A304" s="28"/>
-      <c r="B304" s="29"/>
-      <c r="C304" s="30"/>
-      <c r="D304" s="29"/>
-      <c r="E304" s="29"/>
-      <c r="F304" s="29"/>
-      <c r="G304" s="29"/>
+      <c r="A304" s="25"/>
+      <c r="B304" s="26"/>
+      <c r="C304" s="27"/>
+      <c r="D304" s="26"/>
+      <c r="E304" s="26"/>
+      <c r="F304" s="26"/>
+      <c r="G304" s="26"/>
     </row>
     <row r="305" spans="1:7">
-      <c r="A305" s="28"/>
-      <c r="B305" s="29"/>
-      <c r="C305" s="30"/>
-      <c r="D305" s="29"/>
-      <c r="E305" s="29"/>
-      <c r="F305" s="29"/>
-      <c r="G305" s="29"/>
+      <c r="A305" s="25"/>
+      <c r="B305" s="26"/>
+      <c r="C305" s="27"/>
+      <c r="D305" s="26"/>
+      <c r="E305" s="26"/>
+      <c r="F305" s="26"/>
+      <c r="G305" s="26"/>
     </row>
     <row r="306" spans="1:7">
-      <c r="A306" s="28"/>
-      <c r="B306" s="29"/>
-      <c r="C306" s="30"/>
-      <c r="D306" s="29"/>
-      <c r="E306" s="29"/>
-      <c r="F306" s="29"/>
-      <c r="G306" s="29"/>
+      <c r="A306" s="25"/>
+      <c r="B306" s="26"/>
+      <c r="C306" s="27"/>
+      <c r="D306" s="26"/>
+      <c r="E306" s="26"/>
+      <c r="F306" s="26"/>
+      <c r="G306" s="26"/>
     </row>
     <row r="307" spans="1:7">
-      <c r="A307" s="28"/>
-      <c r="B307" s="29"/>
-      <c r="C307" s="30"/>
-      <c r="D307" s="29"/>
-      <c r="E307" s="29"/>
-      <c r="F307" s="29"/>
-      <c r="G307" s="29"/>
+      <c r="A307" s="25"/>
+      <c r="B307" s="26"/>
+      <c r="C307" s="27"/>
+      <c r="D307" s="26"/>
+      <c r="E307" s="26"/>
+      <c r="F307" s="26"/>
+      <c r="G307" s="26"/>
     </row>
     <row r="308" spans="1:7">
-      <c r="A308" s="28"/>
-      <c r="B308" s="29"/>
-      <c r="C308" s="30"/>
-      <c r="D308" s="29"/>
-      <c r="E308" s="29"/>
-      <c r="F308" s="29"/>
-      <c r="G308" s="29"/>
+      <c r="A308" s="25"/>
+      <c r="B308" s="26"/>
+      <c r="C308" s="27"/>
+      <c r="D308" s="26"/>
+      <c r="E308" s="26"/>
+      <c r="F308" s="26"/>
+      <c r="G308" s="26"/>
     </row>
     <row r="309" spans="1:7">
-      <c r="A309" s="28"/>
-      <c r="B309" s="29"/>
-      <c r="C309" s="30"/>
-      <c r="D309" s="29"/>
-      <c r="E309" s="29"/>
-      <c r="F309" s="29"/>
-      <c r="G309" s="29"/>
+      <c r="A309" s="25"/>
+      <c r="B309" s="26"/>
+      <c r="C309" s="27"/>
+      <c r="D309" s="26"/>
+      <c r="E309" s="26"/>
+      <c r="F309" s="26"/>
+      <c r="G309" s="26"/>
     </row>
     <row r="310" spans="1:7">
-      <c r="A310" s="28"/>
-      <c r="B310" s="29"/>
-      <c r="C310" s="30"/>
-      <c r="D310" s="29"/>
-      <c r="E310" s="29"/>
-      <c r="F310" s="29"/>
-      <c r="G310" s="29"/>
+      <c r="A310" s="25"/>
+      <c r="B310" s="26"/>
+      <c r="C310" s="27"/>
+      <c r="D310" s="26"/>
+      <c r="E310" s="26"/>
+      <c r="F310" s="26"/>
+      <c r="G310" s="26"/>
     </row>
     <row r="311" spans="1:7">
-      <c r="A311" s="28"/>
-      <c r="B311" s="29"/>
-      <c r="C311" s="30"/>
-      <c r="D311" s="29"/>
-      <c r="E311" s="29"/>
-      <c r="F311" s="29"/>
-      <c r="G311" s="29"/>
+      <c r="A311" s="25"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="27"/>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="26"/>
+      <c r="G311" s="26"/>
     </row>
     <row r="312" spans="1:7">
-      <c r="A312" s="28"/>
-      <c r="B312" s="29"/>
-      <c r="C312" s="30"/>
-      <c r="D312" s="29"/>
-      <c r="E312" s="29"/>
-      <c r="F312" s="29"/>
-      <c r="G312" s="29"/>
+      <c r="A312" s="25"/>
+      <c r="B312" s="26"/>
+      <c r="C312" s="27"/>
+      <c r="D312" s="26"/>
+      <c r="E312" s="26"/>
+      <c r="F312" s="26"/>
+      <c r="G312" s="26"/>
     </row>
     <row r="313" spans="1:7">
-      <c r="A313" s="28"/>
-      <c r="B313" s="29"/>
-      <c r="C313" s="30"/>
-      <c r="D313" s="29"/>
-      <c r="E313" s="29"/>
-      <c r="F313" s="29"/>
-      <c r="G313" s="29"/>
+      <c r="A313" s="25"/>
+      <c r="B313" s="26"/>
+      <c r="C313" s="27"/>
+      <c r="D313" s="26"/>
+      <c r="E313" s="26"/>
+      <c r="F313" s="26"/>
+      <c r="G313" s="26"/>
     </row>
     <row r="314" spans="1:7">
-      <c r="A314" s="28"/>
-      <c r="B314" s="29"/>
-      <c r="C314" s="30"/>
-      <c r="D314" s="29"/>
-      <c r="E314" s="29"/>
-      <c r="F314" s="29"/>
-      <c r="G314" s="29"/>
+      <c r="A314" s="25"/>
+      <c r="B314" s="26"/>
+      <c r="C314" s="27"/>
+      <c r="D314" s="26"/>
+      <c r="E314" s="26"/>
+      <c r="F314" s="26"/>
+      <c r="G314" s="26"/>
     </row>
     <row r="315" spans="1:7">
-      <c r="A315" s="28"/>
-      <c r="B315" s="29"/>
-      <c r="C315" s="30"/>
-      <c r="D315" s="29"/>
-      <c r="E315" s="29"/>
-      <c r="F315" s="29"/>
-      <c r="G315" s="29"/>
+      <c r="A315" s="25"/>
+      <c r="B315" s="26"/>
+      <c r="C315" s="27"/>
+      <c r="D315" s="26"/>
+      <c r="E315" s="26"/>
+      <c r="F315" s="26"/>
+      <c r="G315" s="26"/>
     </row>
     <row r="316" spans="1:7">
-      <c r="A316" s="28"/>
-      <c r="B316" s="29"/>
-      <c r="C316" s="30"/>
-      <c r="D316" s="29"/>
-      <c r="E316" s="29"/>
-      <c r="F316" s="29"/>
-      <c r="G316" s="29"/>
+      <c r="A316" s="25"/>
+      <c r="B316" s="26"/>
+      <c r="C316" s="27"/>
+      <c r="D316" s="26"/>
+      <c r="E316" s="26"/>
+      <c r="F316" s="26"/>
+      <c r="G316" s="26"/>
     </row>
     <row r="317" spans="1:7">
-      <c r="A317" s="28"/>
-      <c r="B317" s="29"/>
-      <c r="C317" s="30"/>
-      <c r="D317" s="29"/>
-      <c r="E317" s="29"/>
-      <c r="F317" s="29"/>
-      <c r="G317" s="29"/>
+      <c r="A317" s="25"/>
+      <c r="B317" s="26"/>
+      <c r="C317" s="27"/>
+      <c r="D317" s="26"/>
+      <c r="E317" s="26"/>
+      <c r="F317" s="26"/>
+      <c r="G317" s="26"/>
     </row>
     <row r="318" spans="1:7">
-      <c r="A318" s="28"/>
-      <c r="B318" s="29"/>
-      <c r="C318" s="30"/>
-      <c r="D318" s="29"/>
-      <c r="E318" s="29"/>
-      <c r="F318" s="29"/>
-      <c r="G318" s="29"/>
+      <c r="A318" s="25"/>
+      <c r="B318" s="26"/>
+      <c r="C318" s="27"/>
+      <c r="D318" s="26"/>
+      <c r="E318" s="26"/>
+      <c r="F318" s="26"/>
+      <c r="G318" s="26"/>
     </row>
     <row r="319" spans="1:7">
-      <c r="A319" s="28"/>
-      <c r="B319" s="29"/>
-      <c r="C319" s="30"/>
-      <c r="D319" s="29"/>
-      <c r="E319" s="29"/>
-      <c r="F319" s="29"/>
-      <c r="G319" s="29"/>
+      <c r="A319" s="25"/>
+      <c r="B319" s="26"/>
+      <c r="C319" s="27"/>
+      <c r="D319" s="26"/>
+      <c r="E319" s="26"/>
+      <c r="F319" s="26"/>
+      <c r="G319" s="26"/>
     </row>
     <row r="320" spans="1:7">
-      <c r="A320" s="28"/>
-      <c r="B320" s="29"/>
-      <c r="C320" s="30"/>
-      <c r="D320" s="29"/>
-      <c r="E320" s="29"/>
-      <c r="F320" s="29"/>
-      <c r="G320" s="29"/>
+      <c r="A320" s="25"/>
+      <c r="B320" s="26"/>
+      <c r="C320" s="27"/>
+      <c r="D320" s="26"/>
+      <c r="E320" s="26"/>
+      <c r="F320" s="26"/>
+      <c r="G320" s="26"/>
     </row>
     <row r="321" spans="1:7">
-      <c r="A321" s="28"/>
-      <c r="B321" s="29"/>
-      <c r="C321" s="30"/>
-      <c r="D321" s="29"/>
-      <c r="E321" s="29"/>
-      <c r="F321" s="29"/>
-      <c r="G321" s="29"/>
+      <c r="A321" s="25"/>
+      <c r="B321" s="26"/>
+      <c r="C321" s="27"/>
+      <c r="D321" s="26"/>
+      <c r="E321" s="26"/>
+      <c r="F321" s="26"/>
+      <c r="G321" s="26"/>
     </row>
     <row r="322" spans="1:7">
-      <c r="A322" s="28"/>
-      <c r="B322" s="29"/>
-      <c r="C322" s="30"/>
-      <c r="D322" s="29"/>
-      <c r="E322" s="29"/>
-      <c r="F322" s="29"/>
-      <c r="G322" s="29"/>
+      <c r="A322" s="25"/>
+      <c r="B322" s="26"/>
+      <c r="C322" s="27"/>
+      <c r="D322" s="26"/>
+      <c r="E322" s="26"/>
+      <c r="F322" s="26"/>
+      <c r="G322" s="26"/>
     </row>
     <row r="323" spans="1:7">
-      <c r="A323" s="28"/>
-      <c r="B323" s="29"/>
-      <c r="C323" s="30"/>
-      <c r="D323" s="29"/>
-      <c r="E323" s="29"/>
-      <c r="F323" s="29"/>
-      <c r="G323" s="29"/>
+      <c r="A323" s="25"/>
+      <c r="B323" s="26"/>
+      <c r="C323" s="27"/>
+      <c r="D323" s="26"/>
+      <c r="E323" s="26"/>
+      <c r="F323" s="26"/>
+      <c r="G323" s="26"/>
     </row>
     <row r="324" spans="1:7">
-      <c r="A324" s="28"/>
-      <c r="B324" s="29"/>
-      <c r="C324" s="30"/>
-      <c r="D324" s="29"/>
-      <c r="E324" s="29"/>
-      <c r="F324" s="29"/>
-      <c r="G324" s="29"/>
+      <c r="A324" s="25"/>
+      <c r="B324" s="26"/>
+      <c r="C324" s="27"/>
+      <c r="D324" s="26"/>
+      <c r="E324" s="26"/>
+      <c r="F324" s="26"/>
+      <c r="G324" s="26"/>
     </row>
     <row r="325" spans="1:7">
-      <c r="A325" s="28"/>
-      <c r="B325" s="29"/>
-      <c r="C325" s="30"/>
-      <c r="D325" s="29"/>
-      <c r="E325" s="29"/>
-      <c r="F325" s="29"/>
-      <c r="G325" s="29"/>
+      <c r="A325" s="25"/>
+      <c r="B325" s="26"/>
+      <c r="C325" s="27"/>
+      <c r="D325" s="26"/>
+      <c r="E325" s="26"/>
+      <c r="F325" s="26"/>
+      <c r="G325" s="26"/>
     </row>
     <row r="326" spans="1:7">
-      <c r="A326" s="28"/>
-      <c r="B326" s="29"/>
-      <c r="C326" s="30"/>
-      <c r="D326" s="29"/>
-      <c r="E326" s="29"/>
-      <c r="F326" s="29"/>
-      <c r="G326" s="29"/>
+      <c r="A326" s="25"/>
+      <c r="B326" s="26"/>
+      <c r="C326" s="27"/>
+      <c r="D326" s="26"/>
+      <c r="E326" s="26"/>
+      <c r="F326" s="26"/>
+      <c r="G326" s="26"/>
     </row>
     <row r="327" spans="1:7">
-      <c r="A327" s="28"/>
-      <c r="B327" s="29"/>
-      <c r="C327" s="30"/>
-      <c r="D327" s="29"/>
-      <c r="E327" s="29"/>
-      <c r="F327" s="29"/>
-      <c r="G327" s="29"/>
+      <c r="A327" s="25"/>
+      <c r="B327" s="26"/>
+      <c r="C327" s="27"/>
+      <c r="D327" s="26"/>
+      <c r="E327" s="26"/>
+      <c r="F327" s="26"/>
+      <c r="G327" s="26"/>
     </row>
     <row r="328" spans="1:7">
-      <c r="A328" s="28"/>
-      <c r="B328" s="29"/>
-      <c r="C328" s="30"/>
-      <c r="D328" s="29"/>
-      <c r="E328" s="29"/>
-      <c r="F328" s="29"/>
-      <c r="G328" s="29"/>
+      <c r="A328" s="25"/>
+      <c r="B328" s="26"/>
+      <c r="C328" s="27"/>
+      <c r="D328" s="26"/>
+      <c r="E328" s="26"/>
+      <c r="F328" s="26"/>
+      <c r="G328" s="26"/>
     </row>
     <row r="329" spans="1:7">
-      <c r="A329" s="28"/>
-      <c r="B329" s="29"/>
-      <c r="C329" s="30"/>
-      <c r="D329" s="29"/>
-      <c r="E329" s="29"/>
-      <c r="F329" s="29"/>
-      <c r="G329" s="29"/>
+      <c r="A329" s="25"/>
+      <c r="B329" s="26"/>
+      <c r="C329" s="27"/>
+      <c r="D329" s="26"/>
+      <c r="E329" s="26"/>
+      <c r="F329" s="26"/>
+      <c r="G329" s="26"/>
     </row>
     <row r="330" spans="1:7">
-      <c r="A330" s="28"/>
-      <c r="B330" s="29"/>
-      <c r="C330" s="30"/>
-      <c r="D330" s="29"/>
-      <c r="E330" s="29"/>
-      <c r="F330" s="29"/>
-      <c r="G330" s="29"/>
+      <c r="A330" s="25"/>
+      <c r="B330" s="26"/>
+      <c r="C330" s="27"/>
+      <c r="D330" s="26"/>
+      <c r="E330" s="26"/>
+      <c r="F330" s="26"/>
+      <c r="G330" s="26"/>
     </row>
     <row r="331" spans="1:7">
-      <c r="A331" s="28"/>
-      <c r="B331" s="29"/>
-      <c r="C331" s="30"/>
-      <c r="D331" s="29"/>
-      <c r="E331" s="29"/>
-      <c r="F331" s="29"/>
-      <c r="G331" s="29"/>
+      <c r="A331" s="25"/>
+      <c r="B331" s="26"/>
+      <c r="C331" s="27"/>
+      <c r="D331" s="26"/>
+      <c r="E331" s="26"/>
+      <c r="F331" s="26"/>
+      <c r="G331" s="26"/>
     </row>
     <row r="332" spans="1:7">
-      <c r="A332" s="28"/>
-      <c r="B332" s="29"/>
-      <c r="C332" s="30"/>
-      <c r="D332" s="29"/>
-      <c r="E332" s="29"/>
-      <c r="F332" s="29"/>
-      <c r="G332" s="29"/>
+      <c r="A332" s="25"/>
+      <c r="B332" s="26"/>
+      <c r="C332" s="27"/>
+      <c r="D332" s="26"/>
+      <c r="E332" s="26"/>
+      <c r="F332" s="26"/>
+      <c r="G332" s="26"/>
     </row>
     <row r="333" spans="1:7">
-      <c r="A333" s="28"/>
-      <c r="B333" s="29"/>
-      <c r="C333" s="30"/>
-      <c r="D333" s="29"/>
-      <c r="E333" s="29"/>
-      <c r="F333" s="29"/>
-      <c r="G333" s="29"/>
+      <c r="A333" s="25"/>
+      <c r="B333" s="26"/>
+      <c r="C333" s="27"/>
+      <c r="D333" s="26"/>
+      <c r="E333" s="26"/>
+      <c r="F333" s="26"/>
+      <c r="G333" s="26"/>
     </row>
     <row r="334" spans="1:7">
-      <c r="A334" s="28"/>
-      <c r="B334" s="29"/>
-      <c r="C334" s="30"/>
-      <c r="D334" s="29"/>
-      <c r="E334" s="29"/>
-      <c r="F334" s="29"/>
-      <c r="G334" s="29"/>
+      <c r="A334" s="25"/>
+      <c r="B334" s="26"/>
+      <c r="C334" s="27"/>
+      <c r="D334" s="26"/>
+      <c r="E334" s="26"/>
+      <c r="F334" s="26"/>
+      <c r="G334" s="26"/>
     </row>
     <row r="335" spans="1:7">
-      <c r="A335" s="31"/>
-      <c r="B335" s="29"/>
-      <c r="C335" s="30"/>
-      <c r="D335" s="29"/>
-      <c r="E335" s="29"/>
-      <c r="F335" s="29"/>
-      <c r="G335" s="29"/>
+      <c r="A335" s="28"/>
+      <c r="B335" s="26"/>
+      <c r="C335" s="27"/>
+      <c r="D335" s="26"/>
+      <c r="E335" s="26"/>
+      <c r="F335" s="26"/>
+      <c r="G335" s="26"/>
     </row>
     <row r="336" spans="1:7">
-      <c r="A336" s="31"/>
-      <c r="B336" s="29"/>
-      <c r="C336" s="30"/>
-      <c r="D336" s="29"/>
-      <c r="E336" s="29"/>
-      <c r="F336" s="29"/>
-      <c r="G336" s="29"/>
+      <c r="A336" s="28"/>
+      <c r="B336" s="26"/>
+      <c r="C336" s="27"/>
+      <c r="D336" s="26"/>
+      <c r="E336" s="26"/>
+      <c r="F336" s="26"/>
+      <c r="G336" s="26"/>
     </row>
     <row r="337" spans="1:7">
-      <c r="A337" s="28"/>
-      <c r="B337" s="29"/>
-      <c r="C337" s="30"/>
-      <c r="D337" s="29"/>
-      <c r="E337" s="29"/>
-      <c r="F337" s="29"/>
-      <c r="G337" s="29"/>
+      <c r="A337" s="25"/>
+      <c r="B337" s="26"/>
+      <c r="C337" s="27"/>
+      <c r="D337" s="26"/>
+      <c r="E337" s="26"/>
+      <c r="F337" s="26"/>
+      <c r="G337" s="26"/>
     </row>
     <row r="338" spans="1:7">
-      <c r="A338" s="28"/>
-      <c r="B338" s="29"/>
-      <c r="C338" s="30"/>
-      <c r="D338" s="29"/>
-      <c r="E338" s="29"/>
-      <c r="F338" s="29"/>
-      <c r="G338" s="29"/>
+      <c r="A338" s="25"/>
+      <c r="B338" s="26"/>
+      <c r="C338" s="27"/>
+      <c r="D338" s="26"/>
+      <c r="E338" s="26"/>
+      <c r="F338" s="26"/>
+      <c r="G338" s="26"/>
     </row>
     <row r="339" spans="1:7">
-      <c r="A339" s="28"/>
-      <c r="B339" s="29"/>
-      <c r="C339" s="30"/>
-      <c r="D339" s="29"/>
-      <c r="E339" s="29"/>
-      <c r="F339" s="29"/>
-      <c r="G339" s="29"/>
+      <c r="A339" s="25"/>
+      <c r="B339" s="26"/>
+      <c r="C339" s="27"/>
+      <c r="D339" s="26"/>
+      <c r="E339" s="26"/>
+      <c r="F339" s="26"/>
+      <c r="G339" s="26"/>
     </row>
     <row r="340" spans="1:7">
-      <c r="A340" s="28"/>
-      <c r="B340" s="29"/>
-      <c r="C340" s="30"/>
-      <c r="D340" s="29"/>
-      <c r="E340" s="29"/>
-      <c r="F340" s="29"/>
-      <c r="G340" s="29"/>
+      <c r="A340" s="25"/>
+      <c r="B340" s="26"/>
+      <c r="C340" s="27"/>
+      <c r="D340" s="26"/>
+      <c r="E340" s="26"/>
+      <c r="F340" s="26"/>
+      <c r="G340" s="26"/>
     </row>
     <row r="341" spans="1:7">
-      <c r="A341" s="28"/>
-      <c r="B341" s="29"/>
-      <c r="C341" s="30"/>
-      <c r="D341" s="29"/>
-      <c r="E341" s="29"/>
-      <c r="F341" s="29"/>
-      <c r="G341" s="29"/>
+      <c r="A341" s="25"/>
+      <c r="B341" s="26"/>
+      <c r="C341" s="27"/>
+      <c r="D341" s="26"/>
+      <c r="E341" s="26"/>
+      <c r="F341" s="26"/>
+      <c r="G341" s="26"/>
     </row>
     <row r="342" spans="1:7">
-      <c r="A342" s="28"/>
-      <c r="B342" s="29"/>
-      <c r="C342" s="30"/>
-      <c r="D342" s="29"/>
-      <c r="E342" s="29"/>
-      <c r="F342" s="29"/>
-      <c r="G342" s="29"/>
+      <c r="A342" s="25"/>
+      <c r="B342" s="26"/>
+      <c r="C342" s="27"/>
+      <c r="D342" s="26"/>
+      <c r="E342" s="26"/>
+      <c r="F342" s="26"/>
+      <c r="G342" s="26"/>
     </row>
     <row r="343" spans="1:7">
-      <c r="A343" s="28"/>
-      <c r="B343" s="29"/>
-      <c r="C343" s="30"/>
-      <c r="D343" s="29"/>
-      <c r="E343" s="29"/>
-      <c r="F343" s="29"/>
-      <c r="G343" s="29"/>
+      <c r="A343" s="25"/>
+      <c r="B343" s="26"/>
+      <c r="C343" s="27"/>
+      <c r="D343" s="26"/>
+      <c r="E343" s="26"/>
+      <c r="F343" s="26"/>
+      <c r="G343" s="26"/>
     </row>
     <row r="344" spans="1:7">
-      <c r="A344" s="28"/>
-      <c r="B344" s="29"/>
-      <c r="C344" s="30"/>
-      <c r="D344" s="29"/>
-      <c r="E344" s="29"/>
-      <c r="F344" s="29"/>
-      <c r="G344" s="29"/>
+      <c r="A344" s="25"/>
+      <c r="B344" s="26"/>
+      <c r="C344" s="27"/>
+      <c r="D344" s="26"/>
+      <c r="E344" s="26"/>
+      <c r="F344" s="26"/>
+      <c r="G344" s="26"/>
     </row>
     <row r="345" spans="1:7">
-      <c r="A345" s="28"/>
-      <c r="B345" s="29"/>
-      <c r="C345" s="30"/>
-      <c r="D345" s="29"/>
-      <c r="E345" s="29"/>
-      <c r="F345" s="29"/>
-      <c r="G345" s="29"/>
+      <c r="A345" s="25"/>
+      <c r="B345" s="26"/>
+      <c r="C345" s="27"/>
+      <c r="D345" s="26"/>
+      <c r="E345" s="26"/>
+      <c r="F345" s="26"/>
+      <c r="G345" s="26"/>
     </row>
     <row r="346" spans="1:7">
-      <c r="A346" s="28"/>
-      <c r="B346" s="29"/>
-      <c r="C346" s="30"/>
-      <c r="D346" s="29"/>
-      <c r="E346" s="29"/>
-      <c r="F346" s="29"/>
-      <c r="G346" s="29"/>
+      <c r="A346" s="25"/>
+      <c r="B346" s="26"/>
+      <c r="C346" s="27"/>
+      <c r="D346" s="26"/>
+      <c r="E346" s="26"/>
+      <c r="F346" s="26"/>
+      <c r="G346" s="26"/>
     </row>
     <row r="347" spans="1:7">
-      <c r="A347" s="28"/>
-      <c r="B347" s="29"/>
-      <c r="C347" s="30"/>
-      <c r="D347" s="29"/>
-      <c r="E347" s="29"/>
-      <c r="F347" s="29"/>
-      <c r="G347" s="29"/>
+      <c r="A347" s="25"/>
+      <c r="B347" s="26"/>
+      <c r="C347" s="27"/>
+      <c r="D347" s="26"/>
+      <c r="E347" s="26"/>
+      <c r="F347" s="26"/>
+      <c r="G347" s="26"/>
     </row>
     <row r="348" spans="1:7">
-      <c r="A348" s="28"/>
-      <c r="B348" s="29"/>
-      <c r="C348" s="30"/>
-      <c r="D348" s="29"/>
-      <c r="E348" s="29"/>
-      <c r="F348" s="29"/>
-      <c r="G348" s="29"/>
+      <c r="A348" s="25"/>
+      <c r="B348" s="26"/>
+      <c r="C348" s="27"/>
+      <c r="D348" s="26"/>
+      <c r="E348" s="26"/>
+      <c r="F348" s="26"/>
+      <c r="G348" s="26"/>
     </row>
     <row r="349" spans="1:7">
-      <c r="A349" s="28"/>
-      <c r="B349" s="29"/>
-      <c r="C349" s="30"/>
-      <c r="D349" s="29"/>
-      <c r="E349" s="29"/>
-      <c r="F349" s="29"/>
-      <c r="G349" s="29"/>
+      <c r="A349" s="25"/>
+      <c r="B349" s="26"/>
+      <c r="C349" s="27"/>
+      <c r="D349" s="26"/>
+      <c r="E349" s="26"/>
+      <c r="F349" s="26"/>
+      <c r="G349" s="26"/>
     </row>
     <row r="350" spans="1:7">
-      <c r="A350" s="28"/>
-      <c r="B350" s="29"/>
-      <c r="C350" s="30"/>
-      <c r="D350" s="29"/>
-      <c r="E350" s="29"/>
-      <c r="F350" s="29"/>
-      <c r="G350" s="29"/>
+      <c r="A350" s="25"/>
+      <c r="B350" s="26"/>
+      <c r="C350" s="27"/>
+      <c r="D350" s="26"/>
+      <c r="E350" s="26"/>
+      <c r="F350" s="26"/>
+      <c r="G350" s="26"/>
     </row>
     <row r="351" spans="1:7">
-      <c r="A351" s="28"/>
-      <c r="B351" s="29"/>
-      <c r="C351" s="30"/>
-      <c r="D351" s="29"/>
-      <c r="E351" s="29"/>
-      <c r="F351" s="29"/>
-      <c r="G351" s="29"/>
+      <c r="A351" s="25"/>
+      <c r="B351" s="26"/>
+      <c r="C351" s="27"/>
+      <c r="D351" s="26"/>
+      <c r="E351" s="26"/>
+      <c r="F351" s="26"/>
+      <c r="G351" s="26"/>
     </row>
     <row r="352" spans="1:7">
-      <c r="A352" s="28"/>
-      <c r="B352" s="29"/>
-      <c r="C352" s="30"/>
-      <c r="D352" s="29"/>
-      <c r="E352" s="29"/>
-      <c r="F352" s="29"/>
-      <c r="G352" s="29"/>
+      <c r="A352" s="25"/>
+      <c r="B352" s="26"/>
+      <c r="C352" s="27"/>
+      <c r="D352" s="26"/>
+      <c r="E352" s="26"/>
+      <c r="F352" s="26"/>
+      <c r="G352" s="26"/>
     </row>
     <row r="353" spans="1:7">
-      <c r="A353" s="28"/>
-      <c r="B353" s="29"/>
-      <c r="C353" s="30"/>
-      <c r="D353" s="29"/>
-      <c r="E353" s="29"/>
-      <c r="F353" s="29"/>
-      <c r="G353" s="29"/>
+      <c r="A353" s="25"/>
+      <c r="B353" s="26"/>
+      <c r="C353" s="27"/>
+      <c r="D353" s="26"/>
+      <c r="E353" s="26"/>
+      <c r="F353" s="26"/>
+      <c r="G353" s="26"/>
     </row>
     <row r="354" spans="1:7">
-      <c r="A354" s="28"/>
-      <c r="B354" s="29"/>
-      <c r="C354" s="30"/>
-      <c r="D354" s="29"/>
-      <c r="E354" s="29"/>
-      <c r="F354" s="29"/>
-      <c r="G354" s="29"/>
+      <c r="A354" s="25"/>
+      <c r="B354" s="26"/>
+      <c r="C354" s="27"/>
+      <c r="D354" s="26"/>
+      <c r="E354" s="26"/>
+      <c r="F354" s="26"/>
+      <c r="G354" s="26"/>
     </row>
     <row r="355" spans="1:7">
-      <c r="A355" s="28"/>
-      <c r="B355" s="29"/>
-      <c r="C355" s="30"/>
-      <c r="D355" s="29"/>
-      <c r="E355" s="29"/>
-      <c r="F355" s="29"/>
-      <c r="G355" s="29"/>
+      <c r="A355" s="25"/>
+      <c r="B355" s="26"/>
+      <c r="C355" s="27"/>
+      <c r="D355" s="26"/>
+      <c r="E355" s="26"/>
+      <c r="F355" s="26"/>
+      <c r="G355" s="26"/>
     </row>
     <row r="356" spans="1:7">
-      <c r="A356" s="28"/>
-      <c r="B356" s="29"/>
-      <c r="C356" s="30"/>
-      <c r="D356" s="29"/>
-      <c r="E356" s="29"/>
-      <c r="F356" s="29"/>
-      <c r="G356" s="29"/>
+      <c r="A356" s="25"/>
+      <c r="B356" s="26"/>
+      <c r="C356" s="27"/>
+      <c r="D356" s="26"/>
+      <c r="E356" s="26"/>
+      <c r="F356" s="26"/>
+      <c r="G356" s="26"/>
     </row>
     <row r="357" spans="1:7">
-      <c r="A357" s="28"/>
-      <c r="B357" s="29"/>
-      <c r="C357" s="30"/>
-      <c r="D357" s="29"/>
-      <c r="E357" s="29"/>
-      <c r="F357" s="29"/>
-      <c r="G357" s="29"/>
+      <c r="A357" s="25"/>
+      <c r="B357" s="26"/>
+      <c r="C357" s="27"/>
+      <c r="D357" s="26"/>
+      <c r="E357" s="26"/>
+      <c r="F357" s="26"/>
+      <c r="G357" s="26"/>
     </row>
     <row r="358" spans="1:7">
-      <c r="A358" s="28"/>
-      <c r="B358" s="29"/>
-      <c r="C358" s="30"/>
-      <c r="D358" s="29"/>
-      <c r="E358" s="29"/>
-      <c r="F358" s="29"/>
-      <c r="G358" s="29"/>
+      <c r="A358" s="25"/>
+      <c r="B358" s="26"/>
+      <c r="C358" s="27"/>
+      <c r="D358" s="26"/>
+      <c r="E358" s="26"/>
+      <c r="F358" s="26"/>
+      <c r="G358" s="26"/>
     </row>
     <row r="359" spans="1:7">
-      <c r="A359" s="31"/>
-      <c r="B359" s="29"/>
-      <c r="C359" s="30"/>
-      <c r="D359" s="29"/>
-      <c r="E359" s="29"/>
-      <c r="F359" s="29"/>
-      <c r="G359" s="29"/>
+      <c r="A359" s="28"/>
+      <c r="B359" s="26"/>
+      <c r="C359" s="27"/>
+      <c r="D359" s="26"/>
+      <c r="E359" s="26"/>
+      <c r="F359" s="26"/>
+      <c r="G359" s="26"/>
     </row>
     <row r="360" spans="1:7">
-      <c r="A360" s="35"/>
-      <c r="B360" s="33"/>
-      <c r="C360" s="34"/>
-      <c r="D360" s="33"/>
-      <c r="E360" s="33"/>
-      <c r="F360" s="33"/>
-      <c r="G360" s="33"/>
+      <c r="A360" s="32"/>
+      <c r="B360" s="30"/>
+      <c r="C360" s="31"/>
+      <c r="D360" s="30"/>
+      <c r="E360" s="30"/>
+      <c r="F360" s="30"/>
+      <c r="G360" s="30"/>
     </row>
     <row r="361" spans="1:7">
-      <c r="A361" s="35"/>
-      <c r="B361" s="33"/>
-      <c r="C361" s="34"/>
-      <c r="D361" s="33"/>
-      <c r="E361" s="33"/>
-      <c r="F361" s="33"/>
-      <c r="G361" s="33"/>
+      <c r="A361" s="32"/>
+      <c r="B361" s="30"/>
+      <c r="C361" s="31"/>
+      <c r="D361" s="30"/>
+      <c r="E361" s="30"/>
+      <c r="F361" s="30"/>
+      <c r="G361" s="30"/>
     </row>
     <row r="362" spans="1:7">
-      <c r="A362" s="36"/>
-      <c r="B362" s="33"/>
-      <c r="C362" s="34"/>
-      <c r="D362" s="33"/>
-      <c r="E362" s="33"/>
-      <c r="F362" s="33"/>
-      <c r="G362" s="33"/>
+      <c r="A362" s="33"/>
+      <c r="B362" s="30"/>
+      <c r="C362" s="31"/>
+      <c r="D362" s="30"/>
+      <c r="E362" s="30"/>
+      <c r="F362" s="30"/>
+      <c r="G362" s="30"/>
     </row>
     <row r="363" spans="1:7">
-      <c r="A363" s="36"/>
-      <c r="B363" s="33"/>
-      <c r="C363" s="34"/>
-      <c r="D363" s="33"/>
-      <c r="E363" s="33"/>
-      <c r="F363" s="33"/>
-      <c r="G363" s="33"/>
+      <c r="A363" s="33"/>
+      <c r="B363" s="30"/>
+      <c r="C363" s="31"/>
+      <c r="D363" s="30"/>
+      <c r="E363" s="30"/>
+      <c r="F363" s="30"/>
+      <c r="G363" s="30"/>
     </row>
     <row r="364" spans="1:7">
-      <c r="A364" s="36"/>
-      <c r="B364" s="33"/>
-      <c r="C364" s="34"/>
-      <c r="D364" s="33"/>
-      <c r="E364" s="33"/>
-      <c r="F364" s="33"/>
-      <c r="G364" s="33"/>
+      <c r="A364" s="33"/>
+      <c r="B364" s="30"/>
+      <c r="C364" s="31"/>
+      <c r="D364" s="30"/>
+      <c r="E364" s="30"/>
+      <c r="F364" s="30"/>
+      <c r="G364" s="30"/>
     </row>
     <row r="365" spans="1:7">
-      <c r="A365" s="36"/>
-      <c r="B365" s="33"/>
-      <c r="C365" s="34"/>
-      <c r="D365" s="33"/>
-      <c r="E365" s="33"/>
-      <c r="F365" s="33"/>
-      <c r="G365" s="33"/>
+      <c r="A365" s="33"/>
+      <c r="B365" s="30"/>
+      <c r="C365" s="31"/>
+      <c r="D365" s="30"/>
+      <c r="E365" s="30"/>
+      <c r="F365" s="30"/>
+      <c r="G365" s="30"/>
     </row>
     <row r="366" spans="1:7">
-      <c r="A366" s="36"/>
-      <c r="B366" s="33"/>
-      <c r="C366" s="34"/>
-      <c r="D366" s="33"/>
-      <c r="E366" s="33"/>
-      <c r="F366" s="33"/>
-      <c r="G366" s="33"/>
+      <c r="A366" s="33"/>
+      <c r="B366" s="30"/>
+      <c r="C366" s="31"/>
+      <c r="D366" s="30"/>
+      <c r="E366" s="30"/>
+      <c r="F366" s="30"/>
+      <c r="G366" s="30"/>
     </row>
     <row r="367" spans="1:7">
-      <c r="A367" s="36"/>
-      <c r="B367" s="33"/>
-      <c r="C367" s="34"/>
-      <c r="D367" s="33"/>
-      <c r="E367" s="33"/>
-      <c r="F367" s="33"/>
-      <c r="G367" s="33"/>
+      <c r="A367" s="33"/>
+      <c r="B367" s="30"/>
+      <c r="C367" s="31"/>
+      <c r="D367" s="30"/>
+      <c r="E367" s="30"/>
+      <c r="F367" s="30"/>
+      <c r="G367" s="30"/>
     </row>
     <row r="368" spans="1:7">
-      <c r="A368" s="36"/>
-      <c r="B368" s="33"/>
-      <c r="C368" s="34"/>
-      <c r="D368" s="33"/>
-      <c r="E368" s="33"/>
-      <c r="F368" s="33"/>
-      <c r="G368" s="33"/>
+      <c r="A368" s="33"/>
+      <c r="B368" s="30"/>
+      <c r="C368" s="31"/>
+      <c r="D368" s="30"/>
+      <c r="E368" s="30"/>
+      <c r="F368" s="30"/>
+      <c r="G368" s="30"/>
     </row>
     <row r="369" spans="1:7">
-      <c r="A369" s="36"/>
-      <c r="B369" s="33"/>
-      <c r="C369" s="34"/>
-      <c r="D369" s="33"/>
-      <c r="E369" s="33"/>
-      <c r="F369" s="33"/>
-      <c r="G369" s="33"/>
+      <c r="A369" s="33"/>
+      <c r="B369" s="30"/>
+      <c r="C369" s="31"/>
+      <c r="D369" s="30"/>
+      <c r="E369" s="30"/>
+      <c r="F369" s="30"/>
+      <c r="G369" s="30"/>
     </row>
     <row r="370" spans="1:7">
-      <c r="A370" s="36"/>
-      <c r="B370" s="33"/>
-      <c r="C370" s="34"/>
-      <c r="D370" s="33"/>
-      <c r="E370" s="33"/>
-      <c r="F370" s="33"/>
-      <c r="G370" s="33"/>
+      <c r="A370" s="33"/>
+      <c r="B370" s="30"/>
+      <c r="C370" s="31"/>
+      <c r="D370" s="30"/>
+      <c r="E370" s="30"/>
+      <c r="F370" s="30"/>
+      <c r="G370" s="30"/>
     </row>
     <row r="371" spans="1:7">
-      <c r="A371" s="36"/>
-      <c r="B371" s="33"/>
-      <c r="C371" s="34"/>
-      <c r="D371" s="33"/>
-      <c r="E371" s="33"/>
-      <c r="F371" s="33"/>
-      <c r="G371" s="33"/>
+      <c r="A371" s="33"/>
+      <c r="B371" s="30"/>
+      <c r="C371" s="31"/>
+      <c r="D371" s="30"/>
+      <c r="E371" s="30"/>
+      <c r="F371" s="30"/>
+      <c r="G371" s="30"/>
     </row>
     <row r="372" spans="1:7">
-      <c r="A372" s="36"/>
-      <c r="B372" s="33"/>
-      <c r="C372" s="34"/>
-      <c r="D372" s="33"/>
-      <c r="E372" s="33"/>
-      <c r="F372" s="33"/>
-      <c r="G372" s="33"/>
+      <c r="A372" s="33"/>
+      <c r="B372" s="30"/>
+      <c r="C372" s="31"/>
+      <c r="D372" s="30"/>
+      <c r="E372" s="30"/>
+      <c r="F372" s="30"/>
+      <c r="G372" s="30"/>
     </row>
     <row r="373" spans="1:7">
-      <c r="A373" s="36"/>
-      <c r="B373" s="33"/>
-      <c r="C373" s="34"/>
-      <c r="D373" s="33"/>
-      <c r="E373" s="33"/>
-      <c r="F373" s="33"/>
-      <c r="G373" s="33"/>
+      <c r="A373" s="33"/>
+      <c r="B373" s="30"/>
+      <c r="C373" s="31"/>
+      <c r="D373" s="30"/>
+      <c r="E373" s="30"/>
+      <c r="F373" s="30"/>
+      <c r="G373" s="30"/>
     </row>
     <row r="374" spans="1:7">
-      <c r="A374" s="36"/>
-      <c r="B374" s="33"/>
-      <c r="C374" s="34"/>
-      <c r="D374" s="33"/>
-      <c r="E374" s="33"/>
-      <c r="F374" s="33"/>
-      <c r="G374" s="33"/>
+      <c r="A374" s="33"/>
+      <c r="B374" s="30"/>
+      <c r="C374" s="31"/>
+      <c r="D374" s="30"/>
+      <c r="E374" s="30"/>
+      <c r="F374" s="30"/>
+      <c r="G374" s="30"/>
     </row>
     <row r="375" spans="1:7">
-      <c r="A375" s="36"/>
-      <c r="B375" s="33"/>
-      <c r="C375" s="34"/>
-      <c r="D375" s="33"/>
-      <c r="E375" s="33"/>
-      <c r="F375" s="33"/>
-      <c r="G375" s="33"/>
+      <c r="A375" s="33"/>
+      <c r="B375" s="30"/>
+      <c r="C375" s="31"/>
+      <c r="D375" s="30"/>
+      <c r="E375" s="30"/>
+      <c r="F375" s="30"/>
+      <c r="G375" s="30"/>
     </row>
     <row r="376" spans="1:7">
-      <c r="A376" s="36"/>
-      <c r="B376" s="33"/>
-      <c r="C376" s="34"/>
-      <c r="D376" s="33"/>
-      <c r="E376" s="33"/>
-      <c r="F376" s="33"/>
-      <c r="G376" s="33"/>
+      <c r="A376" s="33"/>
+      <c r="B376" s="30"/>
+      <c r="C376" s="31"/>
+      <c r="D376" s="30"/>
+      <c r="E376" s="30"/>
+      <c r="F376" s="30"/>
+      <c r="G376" s="30"/>
     </row>
     <row r="377" spans="1:7">
-      <c r="A377" s="36"/>
-      <c r="B377" s="33"/>
-      <c r="C377" s="34"/>
-      <c r="D377" s="33"/>
-      <c r="E377" s="33"/>
-      <c r="F377" s="33"/>
-      <c r="G377" s="33"/>
+      <c r="A377" s="33"/>
+      <c r="B377" s="30"/>
+      <c r="C377" s="31"/>
+      <c r="D377" s="30"/>
+      <c r="E377" s="30"/>
+      <c r="F377" s="30"/>
+      <c r="G377" s="30"/>
     </row>
     <row r="378" spans="1:7">
-      <c r="A378" s="36"/>
-      <c r="B378" s="33"/>
-      <c r="C378" s="34"/>
-      <c r="D378" s="33"/>
-      <c r="E378" s="33"/>
-      <c r="F378" s="33"/>
-      <c r="G378" s="33"/>
+      <c r="A378" s="33"/>
+      <c r="B378" s="30"/>
+      <c r="C378" s="31"/>
+      <c r="D378" s="30"/>
+      <c r="E378" s="30"/>
+      <c r="F378" s="30"/>
+      <c r="G378" s="30"/>
     </row>
     <row r="379" spans="1:7">
-      <c r="A379" s="36"/>
-      <c r="B379" s="33"/>
-      <c r="C379" s="34"/>
-      <c r="D379" s="33"/>
-      <c r="E379" s="33"/>
-      <c r="F379" s="33"/>
-      <c r="G379" s="33"/>
+      <c r="A379" s="33"/>
+      <c r="B379" s="30"/>
+      <c r="C379" s="31"/>
+      <c r="D379" s="30"/>
+      <c r="E379" s="30"/>
+      <c r="F379" s="30"/>
+      <c r="G379" s="30"/>
     </row>
     <row r="380" spans="1:7">
-      <c r="A380" s="36"/>
-      <c r="B380" s="33"/>
-      <c r="C380" s="34"/>
-      <c r="D380" s="33"/>
-      <c r="E380" s="33"/>
-      <c r="F380" s="33"/>
-      <c r="G380" s="33"/>
+      <c r="A380" s="33"/>
+      <c r="B380" s="30"/>
+      <c r="C380" s="31"/>
+      <c r="D380" s="30"/>
+      <c r="E380" s="30"/>
+      <c r="F380" s="30"/>
+      <c r="G380" s="30"/>
     </row>
     <row r="381" spans="1:7">
-      <c r="A381" s="36"/>
-      <c r="B381" s="33"/>
-      <c r="C381" s="34"/>
-      <c r="D381" s="33"/>
-      <c r="E381" s="33"/>
-      <c r="F381" s="33"/>
-      <c r="G381" s="33"/>
+      <c r="A381" s="33"/>
+      <c r="B381" s="30"/>
+      <c r="C381" s="31"/>
+      <c r="D381" s="30"/>
+      <c r="E381" s="30"/>
+      <c r="F381" s="30"/>
+      <c r="G381" s="30"/>
     </row>
     <row r="382" spans="1:7">
-      <c r="A382" s="36"/>
-      <c r="B382" s="33"/>
-      <c r="C382" s="34"/>
-      <c r="D382" s="33"/>
-      <c r="E382" s="33"/>
-      <c r="F382" s="33"/>
-      <c r="G382" s="33"/>
+      <c r="A382" s="33"/>
+      <c r="B382" s="30"/>
+      <c r="C382" s="31"/>
+      <c r="D382" s="30"/>
+      <c r="E382" s="30"/>
+      <c r="F382" s="30"/>
+      <c r="G382" s="30"/>
     </row>
     <row r="383" spans="1:7">
-      <c r="A383" s="36"/>
-      <c r="B383" s="33"/>
-      <c r="C383" s="34"/>
-      <c r="D383" s="33"/>
-      <c r="E383" s="33"/>
-      <c r="F383" s="33"/>
-      <c r="G383" s="33"/>
+      <c r="A383" s="33"/>
+      <c r="B383" s="30"/>
+      <c r="C383" s="31"/>
+      <c r="D383" s="30"/>
+      <c r="E383" s="30"/>
+      <c r="F383" s="30"/>
+      <c r="G383" s="30"/>
     </row>
     <row r="384" spans="1:7">
-      <c r="A384" s="36"/>
-      <c r="B384" s="33"/>
-      <c r="C384" s="34"/>
-      <c r="D384" s="33"/>
-      <c r="E384" s="33"/>
-      <c r="F384" s="33"/>
-      <c r="G384" s="33"/>
+      <c r="A384" s="33"/>
+      <c r="B384" s="30"/>
+      <c r="C384" s="31"/>
+      <c r="D384" s="30"/>
+      <c r="E384" s="30"/>
+      <c r="F384" s="30"/>
+      <c r="G384" s="30"/>
     </row>
     <row r="385" spans="1:7">
-      <c r="A385" s="36"/>
-      <c r="B385" s="33"/>
-      <c r="C385" s="34"/>
-      <c r="D385" s="33"/>
-      <c r="E385" s="33"/>
-      <c r="F385" s="33"/>
-      <c r="G385" s="33"/>
+      <c r="A385" s="33"/>
+      <c r="B385" s="30"/>
+      <c r="C385" s="31"/>
+      <c r="D385" s="30"/>
+      <c r="E385" s="30"/>
+      <c r="F385" s="30"/>
+      <c r="G385" s="30"/>
     </row>
     <row r="386" spans="1:7">
-      <c r="A386" s="36"/>
-      <c r="B386" s="33"/>
-      <c r="C386" s="34"/>
-      <c r="D386" s="33"/>
-      <c r="E386" s="33"/>
-      <c r="F386" s="33"/>
-      <c r="G386" s="33"/>
+      <c r="A386" s="33"/>
+      <c r="B386" s="30"/>
+      <c r="C386" s="31"/>
+      <c r="D386" s="30"/>
+      <c r="E386" s="30"/>
+      <c r="F386" s="30"/>
+      <c r="G386" s="30"/>
     </row>
     <row r="387" spans="1:7">
-      <c r="A387" s="36"/>
-      <c r="B387" s="33"/>
-      <c r="C387" s="34"/>
-      <c r="D387" s="33"/>
-      <c r="E387" s="33"/>
-      <c r="F387" s="33"/>
-      <c r="G387" s="33"/>
+      <c r="A387" s="33"/>
+      <c r="B387" s="30"/>
+      <c r="C387" s="31"/>
+      <c r="D387" s="30"/>
+      <c r="E387" s="30"/>
+      <c r="F387" s="30"/>
+      <c r="G387" s="30"/>
     </row>
     <row r="388" spans="1:7">
-      <c r="A388" s="36"/>
-      <c r="B388" s="33"/>
-      <c r="C388" s="34"/>
-      <c r="D388" s="33"/>
-      <c r="E388" s="33"/>
-      <c r="F388" s="33"/>
-      <c r="G388" s="33"/>
+      <c r="A388" s="33"/>
+      <c r="B388" s="30"/>
+      <c r="C388" s="31"/>
+      <c r="D388" s="30"/>
+      <c r="E388" s="30"/>
+      <c r="F388" s="30"/>
+      <c r="G388" s="30"/>
     </row>
     <row r="389" spans="1:7">
-      <c r="A389" s="36"/>
-      <c r="B389" s="33"/>
-      <c r="C389" s="34"/>
-      <c r="D389" s="33"/>
-      <c r="E389" s="33"/>
-      <c r="F389" s="33"/>
-      <c r="G389" s="33"/>
+      <c r="A389" s="33"/>
+      <c r="B389" s="30"/>
+      <c r="C389" s="31"/>
+      <c r="D389" s="30"/>
+      <c r="E389" s="30"/>
+      <c r="F389" s="30"/>
+      <c r="G389" s="30"/>
     </row>
     <row r="390" spans="1:7">
-      <c r="A390" s="36"/>
-      <c r="B390" s="33"/>
-      <c r="C390" s="34"/>
-      <c r="D390" s="33"/>
-      <c r="E390" s="33"/>
-      <c r="F390" s="33"/>
-      <c r="G390" s="33"/>
+      <c r="A390" s="33"/>
+      <c r="B390" s="30"/>
+      <c r="C390" s="31"/>
+      <c r="D390" s="30"/>
+      <c r="E390" s="30"/>
+      <c r="F390" s="30"/>
+      <c r="G390" s="30"/>
     </row>
     <row r="391" spans="1:7">
-      <c r="A391" s="36"/>
-      <c r="B391" s="33"/>
-      <c r="C391" s="34"/>
-      <c r="D391" s="33"/>
-      <c r="E391" s="33"/>
-      <c r="F391" s="33"/>
-      <c r="G391" s="33"/>
+      <c r="A391" s="33"/>
+      <c r="B391" s="30"/>
+      <c r="C391" s="31"/>
+      <c r="D391" s="30"/>
+      <c r="E391" s="30"/>
+      <c r="F391" s="30"/>
+      <c r="G391" s="30"/>
     </row>
     <row r="392" spans="1:7">
-      <c r="A392" s="37"/>
-      <c r="B392" s="33"/>
-      <c r="C392" s="34"/>
-      <c r="D392" s="33"/>
-      <c r="E392" s="33"/>
-      <c r="F392" s="33"/>
-      <c r="G392" s="33"/>
+      <c r="A392" s="34"/>
+      <c r="B392" s="30"/>
+      <c r="C392" s="31"/>
+      <c r="D392" s="30"/>
+      <c r="E392" s="30"/>
+      <c r="F392" s="30"/>
+      <c r="G392" s="30"/>
     </row>
     <row r="393" spans="1:7">
-      <c r="A393" s="37"/>
-      <c r="B393" s="33"/>
-      <c r="C393" s="34"/>
-      <c r="D393" s="33"/>
-      <c r="E393" s="33"/>
-      <c r="F393" s="33"/>
-      <c r="G393" s="33"/>
+      <c r="A393" s="34"/>
+      <c r="B393" s="30"/>
+      <c r="C393" s="31"/>
+      <c r="D393" s="30"/>
+      <c r="E393" s="30"/>
+      <c r="F393" s="30"/>
+      <c r="G393" s="30"/>
     </row>
     <row r="394" spans="1:7">
-      <c r="A394" s="37"/>
-      <c r="B394" s="33"/>
-      <c r="C394" s="34"/>
-      <c r="D394" s="33"/>
-      <c r="E394" s="33"/>
-      <c r="F394" s="33"/>
-      <c r="G394" s="33"/>
+      <c r="A394" s="34"/>
+      <c r="B394" s="30"/>
+      <c r="C394" s="31"/>
+      <c r="D394" s="30"/>
+      <c r="E394" s="30"/>
+      <c r="F394" s="30"/>
+      <c r="G394" s="30"/>
     </row>
     <row r="395" spans="1:7">
-      <c r="A395" s="37"/>
-      <c r="B395" s="33"/>
-      <c r="C395" s="34"/>
-      <c r="D395" s="33"/>
-      <c r="E395" s="33"/>
-      <c r="F395" s="33"/>
-      <c r="G395" s="33"/>
+      <c r="A395" s="34"/>
+      <c r="B395" s="30"/>
+      <c r="C395" s="31"/>
+      <c r="D395" s="30"/>
+      <c r="E395" s="30"/>
+      <c r="F395" s="30"/>
+      <c r="G395" s="30"/>
     </row>
     <row r="396" spans="1:7">
-      <c r="A396" s="37"/>
-      <c r="B396" s="33"/>
-      <c r="C396" s="34"/>
-      <c r="D396" s="33"/>
-      <c r="E396" s="33"/>
-      <c r="F396" s="33"/>
-      <c r="G396" s="33"/>
+      <c r="A396" s="34"/>
+      <c r="B396" s="30"/>
+      <c r="C396" s="31"/>
+      <c r="D396" s="30"/>
+      <c r="E396" s="30"/>
+      <c r="F396" s="30"/>
+      <c r="G396" s="30"/>
     </row>
     <row r="397" spans="1:7">
-      <c r="A397" s="37"/>
-      <c r="B397" s="33"/>
-      <c r="C397" s="34"/>
-      <c r="D397" s="33"/>
-      <c r="E397" s="33"/>
-      <c r="F397" s="33"/>
-      <c r="G397" s="33"/>
+      <c r="A397" s="34"/>
+      <c r="B397" s="30"/>
+      <c r="C397" s="31"/>
+      <c r="D397" s="30"/>
+      <c r="E397" s="30"/>
+      <c r="F397" s="30"/>
+      <c r="G397" s="30"/>
     </row>
     <row r="398" spans="1:7">
-      <c r="A398" s="37"/>
-      <c r="B398" s="33"/>
-      <c r="C398" s="34"/>
-      <c r="D398" s="33"/>
-      <c r="E398" s="33"/>
-      <c r="F398" s="33"/>
-      <c r="G398" s="33"/>
+      <c r="A398" s="34"/>
+      <c r="B398" s="30"/>
+      <c r="C398" s="31"/>
+      <c r="D398" s="30"/>
+      <c r="E398" s="30"/>
+      <c r="F398" s="30"/>
+      <c r="G398" s="30"/>
     </row>
     <row r="399" spans="1:7">
-      <c r="A399" s="37"/>
-      <c r="B399" s="33"/>
-      <c r="C399" s="34"/>
-      <c r="D399" s="33"/>
-      <c r="E399" s="33"/>
-      <c r="F399" s="33"/>
-      <c r="G399" s="33"/>
+      <c r="A399" s="34"/>
+      <c r="B399" s="30"/>
+      <c r="C399" s="31"/>
+      <c r="D399" s="30"/>
+      <c r="E399" s="30"/>
+      <c r="F399" s="30"/>
+      <c r="G399" s="30"/>
     </row>
     <row r="400" spans="1:7">
-      <c r="A400" s="37"/>
-      <c r="B400" s="33"/>
-      <c r="C400" s="34"/>
-      <c r="D400" s="33"/>
-      <c r="E400" s="33"/>
-      <c r="F400" s="33"/>
-      <c r="G400" s="33"/>
+      <c r="A400" s="34"/>
+      <c r="B400" s="30"/>
+      <c r="C400" s="31"/>
+      <c r="D400" s="30"/>
+      <c r="E400" s="30"/>
+      <c r="F400" s="30"/>
+      <c r="G400" s="30"/>
     </row>
     <row r="401" spans="1:7">
-      <c r="A401" s="37"/>
-      <c r="B401" s="33"/>
-      <c r="C401" s="34"/>
-      <c r="D401" s="33"/>
-      <c r="E401" s="33"/>
-      <c r="F401" s="33"/>
-      <c r="G401" s="33"/>
+      <c r="A401" s="34"/>
+      <c r="B401" s="30"/>
+      <c r="C401" s="31"/>
+      <c r="D401" s="30"/>
+      <c r="E401" s="30"/>
+      <c r="F401" s="30"/>
+      <c r="G401" s="30"/>
     </row>
     <row r="402" spans="1:7">
-      <c r="A402" s="37"/>
-      <c r="B402" s="33"/>
-      <c r="C402" s="34"/>
-      <c r="D402" s="33"/>
-      <c r="E402" s="33"/>
-      <c r="F402" s="33"/>
-      <c r="G402" s="33"/>
+      <c r="A402" s="34"/>
+      <c r="B402" s="30"/>
+      <c r="C402" s="31"/>
+      <c r="D402" s="30"/>
+      <c r="E402" s="30"/>
+      <c r="F402" s="30"/>
+      <c r="G402" s="30"/>
     </row>
     <row r="403" spans="1:7">
-      <c r="A403" s="37"/>
-      <c r="B403" s="33"/>
-      <c r="C403" s="34"/>
-      <c r="D403" s="33"/>
-      <c r="E403" s="33"/>
-      <c r="F403" s="33"/>
-      <c r="G403" s="33"/>
+      <c r="A403" s="34"/>
+      <c r="B403" s="30"/>
+      <c r="C403" s="31"/>
+      <c r="D403" s="30"/>
+      <c r="E403" s="30"/>
+      <c r="F403" s="30"/>
+      <c r="G403" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/du_lieu_tram.xlsx
+++ b/du_lieu_tram.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -245,7 +245,7 @@
     <t>Xã Mỹ Đức</t>
   </si>
   <si>
-    <t>20.69501166666667 105.73785333333332</t>
+    <t>20.69501166666667, 105.73785333333332</t>
   </si>
   <si>
     <t>BSS-254441000460</t>
@@ -1174,7 +1174,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>

--- a/du_lieu_tram.xlsx
+++ b/du_lieu_tram.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
   <si>
     <t>ma_tram</t>
   </si>
@@ -71,10 +71,7 @@
     <t>Thành phố Trung ương Hà Nội</t>
   </si>
   <si>
-    <t>20,988386</t>
-  </si>
-  <si>
-    <t>105,941887</t>
+    <t>20.9276364, 105.8495719</t>
   </si>
   <si>
     <t>BSS-254641000939</t>
@@ -89,10 +86,10 @@
     <t>Xã Quốc Oai</t>
   </si>
   <si>
-    <t>20,93153</t>
-  </si>
-  <si>
-    <t>105,568413</t>
+    <t>20.93153</t>
+  </si>
+  <si>
+    <t>105.568413</t>
   </si>
   <si>
     <t>BSS-254441000104</t>
@@ -107,10 +104,10 @@
     <t>Phường Từ Liêm</t>
   </si>
   <si>
-    <t>21,007984</t>
-  </si>
-  <si>
-    <t>105,742035</t>
+    <t>21.007984</t>
+  </si>
+  <si>
+    <t>105.742035</t>
   </si>
   <si>
     <t>BSS-254741000123</t>
@@ -122,10 +119,10 @@
     <t>Xóm Ngang, Thôn 1, Xã Cộng Hòa</t>
   </si>
   <si>
-    <t>21,01531</t>
-  </si>
-  <si>
-    <t>105,64933</t>
+    <t>21.01531</t>
+  </si>
+  <si>
+    <t>105.64933</t>
   </si>
   <si>
     <t>BSS-254441000519</t>
@@ -140,6 +137,9 @@
     <t>ba đình</t>
   </si>
   <si>
+    <t>21.051241, 105.8014737</t>
+  </si>
+  <si>
     <t>BSS-255241000648</t>
   </si>
   <si>
@@ -152,10 +152,10 @@
     <t>Xã Thạch Thất</t>
   </si>
   <si>
-    <t>21,0581</t>
-  </si>
-  <si>
-    <t>105,57488</t>
+    <t>21.0581</t>
+  </si>
+  <si>
+    <t>105.57488</t>
   </si>
   <si>
     <t>BSS-254641000073</t>
@@ -167,10 +167,10 @@
     <t>Xí nghiệp Trung đại tu Cầu Bươu, Thanh Liệt, Thanh Trì, Hà Nội</t>
   </si>
   <si>
-    <t>20,9541</t>
-  </si>
-  <si>
-    <t>105,814697</t>
+    <t>20.9541</t>
+  </si>
+  <si>
+    <t>105.814697</t>
   </si>
   <si>
     <t>BSS-254641000030</t>
@@ -245,7 +245,7 @@
     <t>Xã Mỹ Đức</t>
   </si>
   <si>
-    <t>20.69501166666667, 105.73785333333332</t>
+    <t>20.6950116666666, 105.73785333333332</t>
   </si>
   <si>
     <t>BSS-254441000460</t>
@@ -1622,103 +1622,99 @@
       <c r="F2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="G2" s="6"/>
       <c r="J2" s="31"/>
       <c r="K2" s="32"/>
     </row>
     <row r="3" ht="83.55" spans="1:7">
       <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" ht="166.35" spans="1:7">
       <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" ht="69.75" spans="1:7">
       <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" ht="124.95" spans="1:12">
       <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>15</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G6" s="6"/>
       <c r="L6" s="31"/>
     </row>
     <row r="7" ht="138.75" spans="1:7">

--- a/du_lieu_tram.xlsx
+++ b/du_lieu_tram.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2871,11 +2871,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L403"/>
+  <dimension ref="A1:L402"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="45.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="31.6666666666667" customWidth="1"/>
     <col min="6" max="6" width="16.2222222222222" customWidth="1"/>
     <col min="7" max="7" width="22.7777777777778" customWidth="1"/>
     <col min="8" max="8" width="29.5555555555556" customWidth="1"/>
@@ -2937,389 +2938,403 @@
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
+      <c r="A3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="8">
+        <v>19.181562</v>
+      </c>
+      <c r="G3" s="8">
+        <v>105.729461</v>
+      </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="8">
-        <v>19.181562</v>
-      </c>
-      <c r="G4" s="8">
-        <v>105.729461</v>
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3">
+        <v>18.793152</v>
+      </c>
+      <c r="G4" s="3">
+        <v>105.698672</v>
       </c>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3">
-        <v>18.793152</v>
-      </c>
-      <c r="G5" s="3">
-        <v>105.698672</v>
+      <c r="A5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8">
+        <v>19.44466</v>
+      </c>
+      <c r="G5" s="8">
+        <v>104.976532</v>
       </c>
       <c r="H5" s="4"/>
+      <c r="L5" s="5"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3">
+        <v>18.7824</v>
+      </c>
+      <c r="G6" s="3">
+        <v>105.64686</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="E7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="8">
         <v>19.44466</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G7" s="8">
         <v>104.976532</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="L6" s="5"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="3">
-        <v>18.7824</v>
-      </c>
-      <c r="G7" s="3">
-        <v>105.64686</v>
-      </c>
       <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="8">
-        <v>19.44466</v>
+        <v>18.991734</v>
       </c>
       <c r="G8" s="8">
-        <v>104.976532</v>
+        <v>105.510989</v>
       </c>
       <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="8">
+        <v>19.059305</v>
+      </c>
+      <c r="G9" s="8">
+        <v>105.574425</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="8">
-        <v>18.991734</v>
-      </c>
-      <c r="G9" s="8">
-        <v>105.510989</v>
-      </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="8">
-        <v>19.059305</v>
-      </c>
-      <c r="G10" s="8">
-        <v>105.574425</v>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3">
+        <v>18.7065</v>
+      </c>
+      <c r="G10" s="3">
+        <v>105.707897</v>
       </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="3">
-        <v>18.7065</v>
-      </c>
-      <c r="G11" s="3">
-        <v>105.707897</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="A12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="8">
+        <v>19.445549</v>
+      </c>
+      <c r="G12" s="8">
+        <v>105.27652</v>
+      </c>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F13" s="8">
-        <v>19.445549</v>
+        <v>19.197676</v>
       </c>
       <c r="G13" s="8">
-        <v>105.27652</v>
+        <v>105.67611</v>
       </c>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="8">
-        <v>19.197676</v>
-      </c>
-      <c r="G14" s="8">
-        <v>105.67611</v>
+      <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3">
+        <v>18.7065</v>
+      </c>
+      <c r="G14" s="3">
+        <v>105.707897</v>
       </c>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="3">
-        <v>18.7065</v>
-      </c>
-      <c r="G15" s="3">
-        <v>105.707897</v>
-      </c>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="A16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="8">
+        <v>19.270563</v>
+      </c>
+      <c r="G16" s="8">
+        <v>105.485615</v>
+      </c>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F17" s="8">
-        <v>19.270563</v>
+        <v>19.154678</v>
       </c>
       <c r="G17" s="8">
-        <v>105.485615</v>
+        <v>105.638443</v>
       </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="8">
-        <v>19.154678</v>
-      </c>
-      <c r="G18" s="8">
-        <v>105.638443</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="A19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="3">
+        <v>18.73325</v>
+      </c>
+      <c r="G19" s="3">
+        <v>105.722155</v>
+      </c>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="3">
-        <v>18.73325</v>
-      </c>
-      <c r="G20" s="3">
-        <v>105.722155</v>
+      <c r="A20" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="8">
+        <v>19.331221</v>
+      </c>
+      <c r="G20" s="8">
+        <v>105.146004</v>
       </c>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>65</v>
@@ -3340,55 +3355,55 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F22" s="8">
-        <v>19.331221</v>
+        <v>19.31661</v>
       </c>
       <c r="G22" s="8">
-        <v>105.146004</v>
+        <v>105.446236</v>
       </c>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="8">
-        <v>19.31661</v>
+        <v>19.331221</v>
       </c>
       <c r="G23" s="8">
-        <v>105.446236</v>
+        <v>105.146004</v>
       </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>73</v>
@@ -3412,34 +3427,34 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="8">
-        <v>19.331221</v>
+        <v>19.316675</v>
       </c>
       <c r="G25" s="8">
-        <v>105.146004</v>
+        <v>105.446007</v>
       </c>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>77</v>
@@ -3460,13 +3475,13 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>71</v>
@@ -3475,46 +3490,46 @@
         <v>13</v>
       </c>
       <c r="F27" s="8">
-        <v>19.316675</v>
+        <v>19.31661</v>
       </c>
       <c r="G27" s="8">
-        <v>105.446007</v>
+        <v>105.446236</v>
       </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F28" s="8">
-        <v>19.31661</v>
+        <v>19.32519</v>
       </c>
       <c r="G28" s="8">
-        <v>105.446236</v>
+        <v>105.1679</v>
       </c>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>45</v>
@@ -3523,67 +3538,67 @@
         <v>13</v>
       </c>
       <c r="F29" s="8">
-        <v>19.32519</v>
+        <v>19.35498</v>
       </c>
       <c r="G29" s="8">
-        <v>105.1679</v>
+        <v>105.284073</v>
       </c>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F30" s="8">
-        <v>19.35498</v>
+        <v>19.634117</v>
       </c>
       <c r="G30" s="8">
-        <v>105.284073</v>
+        <v>104.9468</v>
       </c>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="8">
-        <v>19.634117</v>
-      </c>
-      <c r="G31" s="8">
-        <v>104.9468</v>
+      <c r="A31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="3">
+        <v>18.722527</v>
+      </c>
+      <c r="G31" s="3">
+        <v>105.744011</v>
       </c>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>94</v>
@@ -3603,52 +3618,37 @@
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F33" s="3">
-        <v>18.722527</v>
-      </c>
-      <c r="G33" s="3">
-        <v>105.744011</v>
+      <c r="A33" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33" s="8">
+        <v>19.32618</v>
+      </c>
+      <c r="G33" s="8">
+        <v>105.19944</v>
       </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="8">
-        <v>19.32618</v>
-      </c>
-      <c r="G34" s="8">
-        <v>105.19944</v>
-      </c>
-      <c r="H34" s="4"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="2"/>
@@ -3678,334 +3678,334 @@
       <c r="G37" s="3"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
+      <c r="A38" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="8">
+        <v>18.793604</v>
+      </c>
+      <c r="G38" s="8">
+        <v>105.335304</v>
+      </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="7" t="s">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="8">
+        <v>19.322224</v>
+      </c>
+      <c r="G40" s="8">
+        <v>105.43194</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="8">
-        <v>18.793604</v>
-      </c>
-      <c r="G39" s="8">
-        <v>105.335304</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F41" s="8">
-        <v>19.322224</v>
-      </c>
-      <c r="G41" s="8">
-        <v>105.43194</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+      <c r="E42" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="8">
+        <v>18.836752</v>
+      </c>
+      <c r="G42" s="8">
+        <v>105.251633</v>
+      </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="8">
-        <v>18.836752</v>
-      </c>
-      <c r="G43" s="8">
-        <v>105.251633</v>
+      <c r="A43" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="3">
+        <v>18.699401</v>
+      </c>
+      <c r="G43" s="3">
+        <v>105.418453</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="3">
-        <v>18.699401</v>
-      </c>
-      <c r="G44" s="3">
-        <v>105.418453</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+      <c r="E45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="3">
+        <v>18.762844</v>
+      </c>
+      <c r="G45" s="3">
+        <v>105.305916</v>
+      </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="3">
-        <v>18.762844</v>
-      </c>
-      <c r="G46" s="3">
-        <v>105.305916</v>
+      <c r="A46" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="8">
+        <v>19.189569</v>
+      </c>
+      <c r="G46" s="8">
+        <v>105.535439</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="8">
-        <v>19.189569</v>
+        <v>18.89864</v>
       </c>
       <c r="G47" s="8">
-        <v>105.535439</v>
+        <v>105.331139</v>
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="8">
-        <v>18.89864</v>
-      </c>
-      <c r="G48" s="8">
-        <v>105.331139</v>
+      <c r="A48" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="3">
+        <v>18.706059</v>
+      </c>
+      <c r="G48" s="3">
+        <v>105.494881</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="3">
-        <v>18.706059</v>
+        <v>18.666382</v>
       </c>
       <c r="G49" s="3">
-        <v>105.494881</v>
+        <v>105.68161</v>
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="3">
-        <v>18.666382</v>
-      </c>
-      <c r="G50" s="3">
-        <v>105.68161</v>
-      </c>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+      <c r="A51" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="3">
+        <v>18.7065</v>
+      </c>
+      <c r="G51" s="3">
+        <v>105.707897</v>
+      </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="3">
-        <v>18.7065</v>
-      </c>
-      <c r="G52" s="3">
-        <v>105.707897</v>
-      </c>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
+      <c r="A53" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="3">
+        <v>18.692221</v>
+      </c>
+      <c r="G53" s="3">
+        <v>105.300652</v>
+      </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F54" s="3">
-        <v>18.692221</v>
+        <v>18.705521</v>
       </c>
       <c r="G54" s="3">
-        <v>105.300652</v>
+        <v>105.495049</v>
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="3">
-        <v>18.705521</v>
-      </c>
-      <c r="G55" s="3">
-        <v>105.495049</v>
-      </c>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2"/>
@@ -4017,23 +4017,37 @@
       <c r="G56" s="3"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
+      <c r="A57" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="3">
+        <v>18.745052</v>
+      </c>
+      <c r="G57" s="3">
+        <v>105.447617</v>
+      </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>126</v>
@@ -4042,41 +4056,41 @@
         <v>13</v>
       </c>
       <c r="F58" s="3">
-        <v>18.745052</v>
+        <v>18.706059</v>
       </c>
       <c r="G58" s="3">
-        <v>105.447617</v>
+        <v>105.494881</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F59" s="3">
-        <v>18.706059</v>
+        <v>18.71048</v>
       </c>
       <c r="G59" s="3">
-        <v>105.494881</v>
+        <v>105.61998</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>144</v>
@@ -4096,13 +4110,13 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>12</v>
@@ -4111,18 +4125,18 @@
         <v>13</v>
       </c>
       <c r="F61" s="3">
-        <v>18.71048</v>
+        <v>18.695251</v>
       </c>
       <c r="G61" s="3">
-        <v>105.61998</v>
+        <v>105.622763</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>149</v>
@@ -4134,18 +4148,18 @@
         <v>13</v>
       </c>
       <c r="F62" s="3">
-        <v>18.695251</v>
+        <v>18.689804</v>
       </c>
       <c r="G62" s="3">
-        <v>105.622763</v>
+        <v>105.624165</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>149</v>
@@ -4165,10 +4179,10 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>149</v>
@@ -4188,10 +4202,10 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>149</v>
@@ -4211,10 +4225,10 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>149</v>
@@ -4226,80 +4240,66 @@
         <v>13</v>
       </c>
       <c r="F66" s="3">
-        <v>18.689804</v>
+        <v>18.695251</v>
       </c>
       <c r="G66" s="3">
-        <v>105.624165</v>
+        <v>105.622763</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F67" s="3">
-        <v>18.695251</v>
+        <v>18.705521</v>
       </c>
       <c r="G67" s="3">
-        <v>105.622763</v>
+        <v>105.495049</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F68" s="3">
-        <v>18.705521</v>
+        <v>18.73325</v>
       </c>
       <c r="G68" s="3">
-        <v>105.495049</v>
+        <v>105.722155</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="3">
-        <v>18.73325</v>
-      </c>
-      <c r="G69" s="3">
-        <v>105.722155</v>
-      </c>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2"/>
@@ -4311,43 +4311,57 @@
       <c r="G70" s="3"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
+      <c r="A71" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="8">
+        <v>19.350458</v>
+      </c>
+      <c r="G71" s="8">
+        <v>105.290434</v>
+      </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="8">
-        <v>19.350458</v>
-      </c>
-      <c r="G72" s="8">
-        <v>105.290434</v>
+      <c r="A72" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="3">
+        <v>18.587675</v>
+      </c>
+      <c r="G72" s="3">
+        <v>105.600265</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>170</v>
@@ -4367,10 +4381,10 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>170</v>
@@ -4382,41 +4396,41 @@
         <v>13</v>
       </c>
       <c r="F74" s="3">
-        <v>18.587675</v>
+        <v>18.588904</v>
       </c>
       <c r="G74" s="3">
-        <v>105.600265</v>
+        <v>105.601941</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F75" s="3">
-        <v>18.588904</v>
+        <v>18.67785</v>
       </c>
       <c r="G75" s="3">
-        <v>105.601941</v>
+        <v>105.60767</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>177</v>
@@ -4436,10 +4450,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>177</v>
@@ -4459,72 +4473,58 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>177</v>
+        <v>61</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F78" s="3">
-        <v>18.67785</v>
+        <v>18.73325</v>
       </c>
       <c r="G78" s="3">
-        <v>105.60767</v>
+        <v>105.722155</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>61</v>
+        <v>186</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="3">
-        <v>18.73325</v>
+        <v>18.62482</v>
       </c>
       <c r="G79" s="3">
-        <v>105.722155</v>
+        <v>105.68213</v>
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="3">
-        <v>18.62482</v>
-      </c>
-      <c r="G80" s="3">
-        <v>105.68213</v>
-      </c>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2"/>
@@ -4554,59 +4554,59 @@
       <c r="G83" s="3"/>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
+      <c r="A84" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="8">
+        <v>19.028191</v>
+      </c>
+      <c r="G84" s="8">
+        <v>104.96543</v>
+      </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="8">
-        <v>19.028191</v>
-      </c>
-      <c r="G85" s="8">
-        <v>104.96543</v>
+      <c r="A85" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="3">
+        <v>18.759558</v>
+      </c>
+      <c r="G85" s="3">
+        <v>105.739808</v>
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F86" s="3">
-        <v>18.759558</v>
-      </c>
-      <c r="G86" s="3">
-        <v>105.739808</v>
-      </c>
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="2"/>
@@ -4636,43 +4636,57 @@
       <c r="G89" s="3"/>
     </row>
     <row r="90" spans="1:7">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
+      <c r="A90" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="3">
+        <v>18.758576</v>
+      </c>
+      <c r="G90" s="3">
+        <v>105.736902</v>
+      </c>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="3">
-        <v>18.758576</v>
-      </c>
-      <c r="G91" s="3">
-        <v>105.736902</v>
+      <c r="A91" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" s="8">
+        <v>18.995224</v>
+      </c>
+      <c r="G91" s="8">
+        <v>105.596093</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="7" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>200</v>
@@ -4692,56 +4706,56 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F93" s="8">
-        <v>18.995224</v>
+        <v>18.925505</v>
       </c>
       <c r="G93" s="8">
-        <v>105.596093</v>
+        <v>105.469532</v>
       </c>
     </row>
     <row r="94" spans="1:7">
-      <c r="A94" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="8">
-        <v>18.925505</v>
-      </c>
-      <c r="G94" s="8">
-        <v>105.469532</v>
+      <c r="A94" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="3">
+        <v>18.732319</v>
+      </c>
+      <c r="G94" s="3">
+        <v>105.721443</v>
       </c>
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>209</v>
@@ -4761,33 +4775,33 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F96" s="3">
-        <v>18.732319</v>
+        <v>18.697869</v>
       </c>
       <c r="G96" s="3">
-        <v>105.721443</v>
+        <v>105.50042</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>214</v>
@@ -4807,49 +4821,35 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F98" s="3">
-        <v>18.697869</v>
+        <v>18.5839</v>
       </c>
       <c r="G98" s="3">
-        <v>105.50042</v>
+        <v>105.65327</v>
       </c>
     </row>
     <row r="99" spans="1:7">
-      <c r="A99" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="3">
-        <v>18.5839</v>
-      </c>
-      <c r="G99" s="3">
-        <v>105.65327</v>
-      </c>
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="2"/>
@@ -4861,23 +4861,37 @@
       <c r="G100" s="3"/>
     </row>
     <row r="101" spans="1:7">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
+      <c r="A101" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="8">
+        <v>19.137468</v>
+      </c>
+      <c r="G101" s="8">
+        <v>105.622632</v>
+      </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>58</v>
@@ -4886,110 +4900,110 @@
         <v>13</v>
       </c>
       <c r="F102" s="8">
-        <v>19.137468</v>
+        <v>19.116659</v>
       </c>
       <c r="G102" s="8">
-        <v>105.622632</v>
+        <v>105.60582</v>
       </c>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C103" s="7" t="s">
+      <c r="A103" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="3">
+        <v>18.733215</v>
+      </c>
+      <c r="G103" s="3">
+        <v>105.660575</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C104" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D104" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E103" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F103" s="8">
+      <c r="E104" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="8">
         <v>19.116659</v>
       </c>
-      <c r="G103" s="8">
+      <c r="G104" s="8">
         <v>105.60582</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C104" s="2" t="s">
+    <row r="105" spans="1:7">
+      <c r="A105" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D105" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="3">
+      <c r="E105" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="3">
         <v>18.733215</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G105" s="3">
         <v>105.660575</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F105" s="8">
-        <v>19.116659</v>
-      </c>
-      <c r="G105" s="8">
-        <v>105.60582</v>
-      </c>
-    </row>
     <row r="106" spans="1:7">
-      <c r="A106" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="3">
-        <v>18.733215</v>
-      </c>
-      <c r="G106" s="3">
-        <v>105.660575</v>
+      <c r="A106" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="8">
+        <v>18.965371</v>
+      </c>
+      <c r="G106" s="8">
+        <v>105.442895</v>
       </c>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>237</v>
@@ -5009,10 +5023,10 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>237</v>
@@ -5032,56 +5046,56 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F109" s="8">
-        <v>18.965371</v>
+        <v>18.927597</v>
       </c>
       <c r="G109" s="8">
-        <v>105.442895</v>
+        <v>105.132691</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F110" s="8">
-        <v>18.927597</v>
+        <v>18.932649</v>
       </c>
       <c r="G110" s="8">
-        <v>105.132691</v>
+        <v>105.089679</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>248</v>
@@ -5100,181 +5114,181 @@
       </c>
     </row>
     <row r="112" spans="1:7">
-      <c r="A112" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D112" s="7" t="s">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D113" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="E112" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="8">
-        <v>18.932649</v>
-      </c>
-      <c r="G112" s="8">
-        <v>105.089679</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
+      <c r="E113" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="8">
+        <v>18.930418</v>
+      </c>
+      <c r="G113" s="8">
+        <v>105.089628</v>
+      </c>
     </row>
     <row r="114" spans="1:7">
-      <c r="A114" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F114" s="8">
-        <v>18.930418</v>
-      </c>
-      <c r="G114" s="8">
-        <v>105.089628</v>
+      <c r="A114" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="3">
+        <v>18.699539</v>
+      </c>
+      <c r="G114" s="3">
+        <v>105.659691</v>
       </c>
     </row>
     <row r="115" spans="1:7">
-      <c r="A115" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" s="3">
-        <v>18.699539</v>
-      </c>
-      <c r="G115" s="3">
-        <v>105.659691</v>
+      <c r="A115" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="8">
+        <v>19.262676</v>
+      </c>
+      <c r="G115" s="8">
+        <v>104.474548</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="7" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F116" s="8">
-        <v>19.262676</v>
+        <v>18.973552</v>
       </c>
       <c r="G116" s="8">
-        <v>104.474548</v>
+        <v>105.601033</v>
       </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F117" s="8">
-        <v>18.973552</v>
+        <v>19.142788</v>
       </c>
       <c r="G117" s="8">
-        <v>105.601033</v>
+        <v>105.27844</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>267</v>
+        <v>166</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>268</v>
+        <v>167</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F118" s="8">
-        <v>19.142788</v>
+        <v>19.350458</v>
       </c>
       <c r="G118" s="8">
-        <v>105.27844</v>
+        <v>105.290434</v>
       </c>
     </row>
     <row r="119" spans="1:7">
-      <c r="A119" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F119" s="8">
-        <v>19.350458</v>
-      </c>
-      <c r="G119" s="8">
-        <v>105.290434</v>
+      <c r="A119" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" s="3">
+        <v>18.701454</v>
+      </c>
+      <c r="G119" s="3">
+        <v>105.49574</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>273</v>
@@ -5293,34 +5307,34 @@
       </c>
     </row>
     <row r="121" spans="1:7">
-      <c r="A121" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F121" s="3">
-        <v>18.701454</v>
-      </c>
-      <c r="G121" s="3">
-        <v>105.49574</v>
+      <c r="A121" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" s="8">
+        <v>18.932085</v>
+      </c>
+      <c r="G121" s="8">
+        <v>105.08323</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>279</v>
@@ -5340,56 +5354,56 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>279</v>
+        <v>13</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F123" s="8">
-        <v>18.932085</v>
+        <v>18.934875</v>
       </c>
       <c r="G123" s="8">
-        <v>105.08323</v>
+        <v>105.07752</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>13</v>
+        <v>286</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F124" s="8">
-        <v>18.934875</v>
+        <v>19.052442</v>
       </c>
       <c r="G124" s="8">
-        <v>105.07752</v>
+        <v>104.87524</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="7" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C125" s="7" t="s">
         <v>286</v>
@@ -5409,82 +5423,82 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>286</v>
+        <v>119</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>287</v>
+        <v>58</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F126" s="8">
-        <v>19.052442</v>
+        <v>19.189569</v>
       </c>
       <c r="G126" s="8">
-        <v>104.87524</v>
+        <v>105.535439</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>119</v>
+        <v>294</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F127" s="8">
-        <v>19.189569</v>
+        <v>19.061333</v>
       </c>
       <c r="G127" s="8">
-        <v>105.535439</v>
+        <v>105.544518</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="7" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>38</v>
+        <v>249</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F128" s="8">
-        <v>19.061333</v>
+        <v>18.932217</v>
       </c>
       <c r="G128" s="8">
-        <v>105.544518</v>
+        <v>105.091201</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>249</v>
@@ -5493,18 +5507,18 @@
         <v>13</v>
       </c>
       <c r="F129" s="8">
-        <v>18.932217</v>
+        <v>18.931078</v>
       </c>
       <c r="G129" s="8">
-        <v>105.091201</v>
+        <v>105.092972</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="7" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>300</v>
@@ -5524,33 +5538,33 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="7" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F131" s="8">
-        <v>18.931078</v>
+        <v>18.985035</v>
       </c>
       <c r="G131" s="8">
-        <v>105.092972</v>
+        <v>105.260635</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>305</v>
@@ -5569,83 +5583,83 @@
       </c>
     </row>
     <row r="133" spans="1:7">
-      <c r="A133" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="D133" s="7" t="s">
+      <c r="A133" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="3">
+        <v>18.575621</v>
+      </c>
+      <c r="G133" s="3">
+        <v>105.54966</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="8">
+        <v>18.769751</v>
+      </c>
+      <c r="G134" s="8">
+        <v>105.279816</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D135" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E133" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" s="8">
-        <v>18.985035</v>
-      </c>
-      <c r="G133" s="8">
-        <v>105.260635</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" s="3">
-        <v>18.575621</v>
-      </c>
-      <c r="G134" s="3">
-        <v>105.54966</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E135" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F135" s="8">
-        <v>18.769751</v>
-      </c>
-      <c r="G135" s="8">
-        <v>105.279816</v>
+      <c r="E135" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F135" s="3">
+        <v>18.669737</v>
+      </c>
+      <c r="G135" s="3">
+        <v>105.576119</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>21</v>
@@ -5654,18 +5668,18 @@
         <v>13</v>
       </c>
       <c r="F136" s="3">
-        <v>18.669737</v>
+        <v>18.714606</v>
       </c>
       <c r="G136" s="3">
-        <v>105.576119</v>
+        <v>105.494578</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>320</v>
@@ -5684,60 +5698,60 @@
       </c>
     </row>
     <row r="138" spans="1:7">
-      <c r="A138" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D138" s="2" t="s">
+      <c r="A138" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F138" s="8">
+        <v>19.145151</v>
+      </c>
+      <c r="G138" s="8">
+        <v>105.706877</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D139" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E138" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F138" s="3">
-        <v>18.714606</v>
-      </c>
-      <c r="G138" s="3">
-        <v>105.494578</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F139" s="8">
-        <v>19.145151</v>
-      </c>
-      <c r="G139" s="8">
-        <v>105.706877</v>
+      <c r="E139" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F139" s="3">
+        <v>18.838349</v>
+      </c>
+      <c r="G139" s="3">
+        <v>105.490507</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>21</v>
@@ -5746,41 +5760,41 @@
         <v>13</v>
       </c>
       <c r="F140" s="3">
-        <v>18.838349</v>
+        <v>18.839026</v>
       </c>
       <c r="G140" s="3">
-        <v>105.490507</v>
+        <v>105.490171</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F141" s="3">
-        <v>18.839026</v>
+        <v>18.596846</v>
       </c>
       <c r="G141" s="3">
-        <v>105.490171</v>
+        <v>105.671324</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>334</v>
@@ -5800,33 +5814,33 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F143" s="3">
-        <v>18.596846</v>
+        <v>18.71012</v>
       </c>
       <c r="G143" s="3">
-        <v>105.671324</v>
+        <v>105.739593</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>339</v>
@@ -5846,10 +5860,10 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>339</v>
@@ -5868,112 +5882,112 @@
       </c>
     </row>
     <row r="146" spans="1:7">
-      <c r="A146" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F146" s="3">
-        <v>18.71012</v>
-      </c>
-      <c r="G146" s="3">
-        <v>105.739593</v>
-      </c>
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
     </row>
     <row r="147" spans="1:7">
-      <c r="A147" s="2"/>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
-      <c r="F147" s="3"/>
-      <c r="G147" s="3"/>
+      <c r="A147" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="3">
+        <v>18.768764</v>
+      </c>
+      <c r="G147" s="3">
+        <v>105.747355</v>
+      </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F148" s="3">
-        <v>18.768764</v>
+        <v>18.733342</v>
       </c>
       <c r="G148" s="3">
-        <v>105.747355</v>
+        <v>105.72223</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F149" s="3">
-        <v>18.733342</v>
+        <v>18.759751</v>
       </c>
       <c r="G149" s="3">
-        <v>105.72223</v>
+        <v>105.740274</v>
       </c>
     </row>
     <row r="150" spans="1:7">
-      <c r="A150" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F150" s="3">
-        <v>18.759751</v>
-      </c>
-      <c r="G150" s="3">
-        <v>105.740274</v>
+      <c r="A150" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="8">
+        <v>19.06702</v>
+      </c>
+      <c r="G150" s="8">
+        <v>104.85559</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="7" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C151" s="7" t="s">
         <v>355</v>
@@ -5993,10 +6007,10 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C152" s="7" t="s">
         <v>355</v>
@@ -6015,147 +6029,147 @@
       </c>
     </row>
     <row r="153" spans="1:7">
-      <c r="A153" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="C153" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F153" s="8">
-        <v>19.06702</v>
-      </c>
-      <c r="G153" s="8">
-        <v>104.85559</v>
+      <c r="A153" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" s="3">
+        <v>18.721224</v>
+      </c>
+      <c r="G153" s="3">
+        <v>105.714617</v>
       </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F154" s="3">
-        <v>18.721224</v>
+        <v>18.589903</v>
       </c>
       <c r="G154" s="3">
-        <v>105.714617</v>
+        <v>105.591138</v>
       </c>
     </row>
     <row r="155" spans="1:7">
-      <c r="A155" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D155" s="2" t="s">
+      <c r="A155" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" s="8">
+        <v>19.32553</v>
+      </c>
+      <c r="G155" s="8">
+        <v>105.35566</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="2"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D157" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E155" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F155" s="3">
-        <v>18.589903</v>
-      </c>
-      <c r="G155" s="3">
-        <v>105.591138</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C156" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="D156" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F156" s="8">
-        <v>19.32553</v>
-      </c>
-      <c r="G156" s="8">
-        <v>105.35566</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" s="2"/>
-      <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
-      <c r="E157" s="2"/>
-      <c r="F157" s="3"/>
-      <c r="G157" s="3"/>
+      <c r="E157" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="3">
+        <v>18.838349</v>
+      </c>
+      <c r="G157" s="3">
+        <v>105.490507</v>
+      </c>
     </row>
     <row r="158" spans="1:7">
-      <c r="A158" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F158" s="3">
-        <v>18.838349</v>
-      </c>
-      <c r="G158" s="3">
-        <v>105.490507</v>
-      </c>
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
     </row>
     <row r="159" spans="1:7">
-      <c r="A159" s="2"/>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
-      <c r="E159" s="2"/>
-      <c r="F159" s="3"/>
-      <c r="G159" s="3"/>
+      <c r="A159" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="8">
+        <v>19.06244</v>
+      </c>
+      <c r="G159" s="8">
+        <v>104.83698</v>
+      </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="7" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D160" s="7" t="s">
         <v>287</v>
@@ -6164,87 +6178,87 @@
         <v>13</v>
       </c>
       <c r="F160" s="8">
-        <v>19.06244</v>
+        <v>19.309889</v>
       </c>
       <c r="G160" s="8">
-        <v>104.83698</v>
+        <v>104.920486</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="7" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F161" s="8">
-        <v>19.309889</v>
+        <v>18.929893</v>
       </c>
       <c r="G161" s="8">
-        <v>104.920486</v>
+        <v>105.100319</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="7" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F162" s="8">
-        <v>18.929893</v>
+        <v>19.27491</v>
       </c>
       <c r="G162" s="8">
-        <v>105.100319</v>
+        <v>105.46816</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="7" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F163" s="8">
-        <v>19.27491</v>
+        <v>19.05122</v>
       </c>
       <c r="G163" s="8">
-        <v>105.46816</v>
+        <v>105.277893</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>386</v>
@@ -6264,13 +6278,13 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>386</v>
+        <v>13</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>21</v>
@@ -6279,73 +6293,73 @@
         <v>13</v>
       </c>
       <c r="F165" s="8">
-        <v>19.05122</v>
+        <v>18.893474</v>
       </c>
       <c r="G165" s="8">
-        <v>105.277893</v>
+        <v>105.30933</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>13</v>
+        <v>393</v>
       </c>
       <c r="D166" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" s="8">
+        <v>18.878584</v>
+      </c>
+      <c r="G166" s="8">
+        <v>105.375336</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D168" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E166" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F166" s="8">
-        <v>18.893474</v>
-      </c>
-      <c r="G166" s="8">
-        <v>105.30933</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="C167" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="E167" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F167" s="8">
-        <v>18.878584</v>
-      </c>
-      <c r="G167" s="8">
-        <v>105.375336</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" s="2"/>
-      <c r="B168" s="2"/>
-      <c r="C168" s="2"/>
-      <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
-      <c r="F168" s="3"/>
-      <c r="G168" s="3"/>
+      <c r="E168" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" s="3">
+        <v>18.723002</v>
+      </c>
+      <c r="G168" s="3">
+        <v>105.5019</v>
+      </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>397</v>
@@ -6365,13 +6379,13 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>21</v>
@@ -6380,18 +6394,18 @@
         <v>13</v>
       </c>
       <c r="F170" s="3">
-        <v>18.723002</v>
+        <v>18.725889</v>
       </c>
       <c r="G170" s="3">
-        <v>105.5019</v>
+        <v>105.484645</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>402</v>
@@ -6411,13 +6425,13 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>402</v>
+        <v>320</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>21</v>
@@ -6426,18 +6440,18 @@
         <v>13</v>
       </c>
       <c r="F172" s="3">
-        <v>18.725889</v>
+        <v>18.714606</v>
       </c>
       <c r="G172" s="3">
-        <v>105.484645</v>
+        <v>105.494578</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>320</v>
@@ -6456,149 +6470,149 @@
       </c>
     </row>
     <row r="174" spans="1:7">
-      <c r="A174" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D174" s="2" t="s">
+      <c r="A174" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" s="8">
+        <v>19.325236</v>
+      </c>
+      <c r="G174" s="8">
+        <v>105.414935</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" s="10">
+        <v>20.988386</v>
+      </c>
+      <c r="G175" s="10">
+        <v>105.941887</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D176" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E174" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F174" s="3">
-        <v>18.714606</v>
-      </c>
-      <c r="G174" s="3">
-        <v>105.494578</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
-      <c r="A175" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="D175" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="E175" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" s="8">
-        <v>19.325236</v>
-      </c>
-      <c r="G175" s="8">
-        <v>105.414935</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
-      <c r="A176" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="B176" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="C176" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="D176" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="E176" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F176" s="10">
-        <v>20.988386</v>
-      </c>
-      <c r="G176" s="10">
-        <v>105.941887</v>
+      <c r="E176" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" s="3">
+        <v>18.71012</v>
+      </c>
+      <c r="G176" s="3">
+        <v>105.739593</v>
       </c>
     </row>
     <row r="177" spans="1:7">
-      <c r="A177" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F177" s="3">
-        <v>18.71012</v>
-      </c>
-      <c r="G177" s="3">
-        <v>105.739593</v>
+      <c r="A177" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="8">
+        <v>18.93826</v>
+      </c>
+      <c r="G177" s="8">
+        <v>105.46077</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="7" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>421</v>
+        <v>54</v>
       </c>
       <c r="E178" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F178" s="8">
-        <v>18.93826</v>
+        <v>19.27376</v>
       </c>
       <c r="G178" s="8">
-        <v>105.46077</v>
+        <v>105.4658</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>54</v>
+        <v>194</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F179" s="8">
-        <v>19.27376</v>
+        <v>20.988386</v>
       </c>
       <c r="G179" s="8">
-        <v>105.4658</v>
+        <v>105.941887</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C180" s="7" t="s">
         <v>415</v>
@@ -6618,295 +6632,295 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>415</v>
+        <v>189</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F181" s="8">
-        <v>20.988386</v>
+        <v>19.028191</v>
       </c>
       <c r="G181" s="8">
-        <v>105.941887</v>
+        <v>104.96543</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>189</v>
+        <v>433</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>190</v>
+        <v>434</v>
       </c>
       <c r="E182" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F182" s="8">
-        <v>19.028191</v>
+        <v>18.927356</v>
       </c>
       <c r="G182" s="8">
-        <v>104.96543</v>
+        <v>105.476704</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="7" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>434</v>
+        <v>201</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F183" s="8">
-        <v>18.927356</v>
+        <v>19.02375</v>
       </c>
       <c r="G183" s="8">
-        <v>105.476704</v>
+        <v>105.563942</v>
       </c>
     </row>
     <row r="184" spans="1:7">
-      <c r="A184" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="C184" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="D184" s="7" t="s">
+      <c r="A184" s="2"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="D185" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="E184" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F184" s="8">
-        <v>19.02375</v>
-      </c>
-      <c r="G184" s="8">
-        <v>105.563942</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7">
-      <c r="A185" s="2"/>
-      <c r="B185" s="2"/>
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
-      <c r="F185" s="3"/>
-      <c r="G185" s="3"/>
+      <c r="E185" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185" s="8">
+        <v>18.97477</v>
+      </c>
+      <c r="G185" s="8">
+        <v>105.59412</v>
+      </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>201</v>
+        <v>249</v>
       </c>
       <c r="E186" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F186" s="8">
-        <v>18.97477</v>
+        <v>18.930553</v>
       </c>
       <c r="G186" s="8">
-        <v>105.59412</v>
+        <v>105.107413</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="7" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>249</v>
+        <v>45</v>
       </c>
       <c r="E187" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F187" s="8">
-        <v>18.930553</v>
+        <v>19.315672</v>
       </c>
       <c r="G187" s="8">
-        <v>105.107413</v>
+        <v>105.180941</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="7" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>45</v>
+        <v>369</v>
       </c>
       <c r="E188" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F188" s="8">
-        <v>19.315672</v>
+        <v>19.33047</v>
       </c>
       <c r="G188" s="8">
-        <v>105.180941</v>
+        <v>105.48551</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="7" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>369</v>
+        <v>91</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F189" s="8">
-        <v>19.33047</v>
+        <v>19.63582</v>
       </c>
       <c r="G189" s="8">
-        <v>105.48551</v>
+        <v>104.95265</v>
       </c>
     </row>
     <row r="190" spans="1:7">
-      <c r="A190" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="D190" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E190" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F190" s="8">
-        <v>19.63582</v>
-      </c>
-      <c r="G190" s="8">
-        <v>104.95265</v>
+      <c r="A190" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190" s="3">
+        <v>18.736863</v>
+      </c>
+      <c r="G190" s="3">
+        <v>105.705857</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>62</v>
+        <v>311</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F191" s="3">
-        <v>18.736863</v>
+        <v>18.691443</v>
       </c>
       <c r="G191" s="3">
-        <v>105.705857</v>
+        <v>105.688381</v>
       </c>
     </row>
     <row r="192" spans="1:7">
-      <c r="A192" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F192" s="3">
-        <v>18.691443</v>
-      </c>
-      <c r="G192" s="3">
-        <v>105.688381</v>
+      <c r="A192" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" s="8">
+        <v>19.137468</v>
+      </c>
+      <c r="G192" s="8">
+        <v>105.622632</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>223</v>
+        <v>294</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F193" s="8">
-        <v>19.137468</v>
+        <v>19.061333</v>
       </c>
       <c r="G193" s="8">
-        <v>105.622632</v>
+        <v>105.544518</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C194" s="7" t="s">
         <v>294</v>
@@ -6926,10 +6940,10 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C195" s="7" t="s">
         <v>294</v>
@@ -6949,171 +6963,171 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>294</v>
+        <v>469</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E196" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F196" s="8">
-        <v>19.061333</v>
+        <v>18.897457</v>
       </c>
       <c r="G196" s="8">
-        <v>105.544518</v>
+        <v>105.307968</v>
       </c>
     </row>
     <row r="197" spans="1:7">
-      <c r="A197" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="B197" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="C197" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="D197" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E197" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F197" s="8">
-        <v>18.897457</v>
-      </c>
-      <c r="G197" s="8">
-        <v>105.307968</v>
+      <c r="A197" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F197" s="3">
+        <v>18.73642</v>
+      </c>
+      <c r="G197" s="3">
+        <v>105.72461</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>62</v>
+        <v>194</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F198" s="3">
-        <v>18.73642</v>
+        <v>18.80565</v>
       </c>
       <c r="G198" s="3">
-        <v>105.72461</v>
+        <v>105.72235</v>
       </c>
     </row>
     <row r="199" spans="1:7">
-      <c r="A199" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F199" s="3">
-        <v>18.80565</v>
-      </c>
-      <c r="G199" s="3">
-        <v>105.72235</v>
+      <c r="A199" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F199" s="8">
+        <v>18.935631</v>
+      </c>
+      <c r="G199" s="8">
+        <v>105.427753</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="7" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>421</v>
+        <v>38</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F200" s="8">
-        <v>18.935631</v>
+        <v>18.993356</v>
       </c>
       <c r="G200" s="8">
-        <v>105.427753</v>
+        <v>105.45996</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="7" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>38</v>
+        <v>421</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F201" s="8">
-        <v>18.993356</v>
+        <v>18.935631</v>
       </c>
       <c r="G201" s="8">
-        <v>105.45996</v>
+        <v>105.427753</v>
       </c>
     </row>
     <row r="202" spans="1:7">
-      <c r="A202" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="B202" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="C202" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="D202" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="E202" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F202" s="8">
-        <v>18.935631</v>
-      </c>
-      <c r="G202" s="8">
-        <v>105.427753</v>
+      <c r="A202" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F202" s="3">
+        <v>18.744558</v>
+      </c>
+      <c r="G202" s="3">
+        <v>105.706764</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>486</v>
@@ -7133,79 +7147,79 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>486</v>
+        <v>170</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F204" s="3">
-        <v>18.744558</v>
+        <v>18.588904</v>
       </c>
       <c r="G204" s="3">
-        <v>105.706764</v>
+        <v>105.601941</v>
       </c>
     </row>
     <row r="205" spans="1:7">
-      <c r="A205" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F205" s="3">
-        <v>18.588904</v>
-      </c>
-      <c r="G205" s="3">
-        <v>105.601941</v>
+      <c r="A205" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E205" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F205" s="8">
+        <v>18.932217</v>
+      </c>
+      <c r="G205" s="8">
+        <v>105.091201</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>297</v>
+        <v>495</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>249</v>
+        <v>496</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F206" s="8">
-        <v>18.932217</v>
+        <v>19.110821</v>
       </c>
       <c r="G206" s="8">
-        <v>105.091201</v>
+        <v>105.339378</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="7" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C207" s="7" t="s">
         <v>495</v>
@@ -7225,10 +7239,10 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C208" s="7" t="s">
         <v>495</v>
@@ -7247,57 +7261,57 @@
       </c>
     </row>
     <row r="209" spans="1:7">
-      <c r="A209" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="B209" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="C209" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="D209" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="E209" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F209" s="8">
-        <v>19.110821</v>
-      </c>
-      <c r="G209" s="8">
-        <v>105.339378</v>
+      <c r="A209" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F209" s="3">
+        <v>18.714572</v>
+      </c>
+      <c r="G209" s="3">
+        <v>105.495535</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>503</v>
+        <v>310</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>29</v>
+        <v>311</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F210" s="3">
-        <v>18.714572</v>
+        <v>18.575621</v>
       </c>
       <c r="G210" s="3">
-        <v>105.495535</v>
+        <v>105.54966</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>310</v>
@@ -7317,10 +7331,10 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>310</v>
@@ -7339,257 +7353,243 @@
       </c>
     </row>
     <row r="213" spans="1:7">
-      <c r="A213" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F213" s="3">
-        <v>18.575621</v>
-      </c>
-      <c r="G213" s="3">
-        <v>105.54966</v>
+      <c r="A213" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="D213" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E213" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F213" s="8">
+        <v>18.931999</v>
+      </c>
+      <c r="G213" s="8">
+        <v>105.606003</v>
       </c>
     </row>
     <row r="214" spans="1:7">
-      <c r="A214" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="B214" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="C214" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="D214" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E214" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F214" s="8">
-        <v>18.931999</v>
-      </c>
-      <c r="G214" s="8">
-        <v>105.606003</v>
+      <c r="A214" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F214" s="3">
+        <v>18.766133</v>
+      </c>
+      <c r="G214" s="3">
+        <v>105.749508</v>
       </c>
     </row>
     <row r="215" spans="1:7">
-      <c r="A215" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F215" s="3">
-        <v>18.766133</v>
-      </c>
-      <c r="G215" s="3">
-        <v>105.749508</v>
+      <c r="A215" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="D215" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E215" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F215" s="8">
+        <v>19.264606</v>
+      </c>
+      <c r="G215" s="8">
+        <v>104.467537</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" s="7" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D216" s="7" t="s">
-        <v>261</v>
+        <v>71</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F216" s="8">
-        <v>19.264606</v>
+        <v>19.31698</v>
       </c>
       <c r="G216" s="8">
-        <v>104.467537</v>
+        <v>105.446236</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" s="7" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>71</v>
+        <v>167</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F217" s="8">
-        <v>19.31698</v>
+        <v>19.359901</v>
       </c>
       <c r="G217" s="8">
-        <v>105.446236</v>
+        <v>105.28122</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="7" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D218" s="7" t="s">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F218" s="8">
-        <v>19.359901</v>
+        <v>19.325681</v>
       </c>
       <c r="G218" s="8">
-        <v>105.28122</v>
+        <v>105.19001</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219" s="7" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>45</v>
+        <v>531</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F219" s="8">
-        <v>19.325681</v>
+        <v>19.252173</v>
       </c>
       <c r="G219" s="8">
-        <v>105.19001</v>
+        <v>105.71066</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" s="7" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D220" s="7" t="s">
-        <v>531</v>
+        <v>201</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F220" s="8">
-        <v>19.252173</v>
+        <v>19.092686</v>
       </c>
       <c r="G220" s="8">
-        <v>105.71066</v>
+        <v>105.592186</v>
       </c>
     </row>
     <row r="221" spans="1:7">
-      <c r="A221" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="B221" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="C221" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="D221" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E221" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F221" s="8">
-        <v>19.092686</v>
-      </c>
-      <c r="G221" s="8">
-        <v>105.592186</v>
+      <c r="A221" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F221" s="3">
+        <v>18.60098</v>
+      </c>
+      <c r="G221" s="3">
+        <v>105.62388</v>
       </c>
     </row>
     <row r="222" spans="1:7">
       <c r="A222" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>421</v>
+        <v>12</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F222" s="3">
-        <v>18.60098</v>
+        <v>18.596904</v>
       </c>
       <c r="G222" s="3">
-        <v>105.62388</v>
+        <v>105.671197</v>
       </c>
     </row>
     <row r="223" spans="1:7">
-      <c r="A223" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F223" s="3">
-        <v>18.596904</v>
-      </c>
-      <c r="G223" s="3">
-        <v>105.671197</v>
-      </c>
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+      <c r="F223" s="3"/>
+      <c r="G223" s="3"/>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="2"/>
@@ -7601,20 +7601,34 @@
       <c r="G224" s="3"/>
     </row>
     <row r="225" spans="1:7">
-      <c r="A225" s="2"/>
-      <c r="B225" s="2"/>
-      <c r="C225" s="2"/>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
-      <c r="F225" s="3"/>
-      <c r="G225" s="3"/>
+      <c r="A225" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F225" s="3">
+        <v>18.787268</v>
+      </c>
+      <c r="G225" s="3">
+        <v>105.697456</v>
+      </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>543</v>
@@ -7633,27 +7647,13 @@
       </c>
     </row>
     <row r="227" spans="1:7">
-      <c r="A227" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F227" s="3">
-        <v>18.787268</v>
-      </c>
-      <c r="G227" s="3">
-        <v>105.697456</v>
-      </c>
+      <c r="A227" s="2"/>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+      <c r="F227" s="3"/>
+      <c r="G227" s="3"/>
     </row>
     <row r="228" spans="1:7">
       <c r="A228" s="2"/>
@@ -7683,20 +7683,34 @@
       <c r="G230" s="3"/>
     </row>
     <row r="231" spans="1:7">
-      <c r="A231" s="2"/>
-      <c r="B231" s="2"/>
-      <c r="C231" s="2"/>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="3"/>
-      <c r="G231" s="3"/>
+      <c r="A231" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E231" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F231" s="8">
+        <v>19.05091</v>
+      </c>
+      <c r="G231" s="8">
+        <v>105.268989</v>
+      </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="7" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C232" s="7" t="s">
         <v>549</v>
@@ -7715,37 +7729,37 @@
       </c>
     </row>
     <row r="233" spans="1:7">
-      <c r="A233" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="B233" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="C233" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="D233" s="7" t="s">
+      <c r="A233" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D233" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E233" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F233" s="8">
-        <v>19.05091</v>
-      </c>
-      <c r="G233" s="8">
-        <v>105.268989</v>
+      <c r="E233" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F233" s="3">
+        <v>18.711835</v>
+      </c>
+      <c r="G233" s="3">
+        <v>105.67647</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>21</v>
@@ -7754,172 +7768,158 @@
         <v>13</v>
       </c>
       <c r="F234" s="3">
-        <v>18.711835</v>
+        <v>18.70531</v>
       </c>
       <c r="G234" s="3">
-        <v>105.67647</v>
+        <v>105.59045</v>
       </c>
     </row>
     <row r="235" spans="1:7">
-      <c r="A235" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="D235" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F235" s="3">
-        <v>18.70531</v>
-      </c>
-      <c r="G235" s="3">
-        <v>105.59045</v>
+      <c r="A235" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E235" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F235" s="8">
+        <v>19.189569</v>
+      </c>
+      <c r="G235" s="8">
+        <v>105.535439</v>
       </c>
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="7" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>119</v>
+        <v>562</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F236" s="8">
-        <v>19.189569</v>
+        <v>18.789995</v>
       </c>
       <c r="G236" s="8">
-        <v>105.535439</v>
+        <v>105.308037</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="7" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D237" s="7" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F237" s="8">
-        <v>18.789995</v>
+        <v>19.548935</v>
       </c>
       <c r="G237" s="8">
-        <v>105.308037</v>
+        <v>105.108788</v>
       </c>
     </row>
     <row r="238" spans="1:7">
-      <c r="A238" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="B238" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="C238" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="D238" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E238" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F238" s="8">
-        <v>19.548935</v>
-      </c>
-      <c r="G238" s="8">
-        <v>105.108788</v>
+      <c r="A238" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F238" s="3">
+        <v>18.766133</v>
+      </c>
+      <c r="G238" s="3">
+        <v>105.749508</v>
       </c>
     </row>
     <row r="239" spans="1:7">
-      <c r="A239" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F239" s="3">
-        <v>18.766133</v>
-      </c>
-      <c r="G239" s="3">
-        <v>105.749508</v>
+      <c r="A239" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="E239" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F239" s="8">
+        <v>19.252173</v>
+      </c>
+      <c r="G239" s="8">
+        <v>105.71066</v>
       </c>
     </row>
     <row r="240" spans="1:7">
-      <c r="A240" s="7" t="s">
-        <v>568</v>
-      </c>
-      <c r="B240" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="C240" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="D240" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="E240" s="7" t="s">
+      <c r="A240" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="B240" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="C240" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D240" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E240" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F240" s="8">
-        <v>19.252173</v>
+        <v>19.316675</v>
       </c>
       <c r="G240" s="8">
-        <v>105.71066</v>
+        <v>105.446007</v>
       </c>
     </row>
     <row r="241" spans="1:7">
-      <c r="A241" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="B241" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="C241" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D241" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E241" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F241" s="8">
-        <v>19.316675</v>
-      </c>
-      <c r="G241" s="8">
-        <v>105.446007</v>
-      </c>
+      <c r="A241" s="12"/>
+      <c r="B241" s="12"/>
+      <c r="C241" s="12"/>
+      <c r="D241" s="12"/>
+      <c r="E241" s="12"/>
+      <c r="F241" s="3"/>
+      <c r="G241" s="3"/>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="12"/>
@@ -7931,69 +7931,83 @@
       <c r="G242" s="3"/>
     </row>
     <row r="243" spans="1:7">
-      <c r="A243" s="12"/>
-      <c r="B243" s="12"/>
-      <c r="C243" s="12"/>
-      <c r="D243" s="12"/>
-      <c r="E243" s="12"/>
-      <c r="F243" s="3"/>
-      <c r="G243" s="3"/>
+      <c r="A243" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="B243" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="C243" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D243" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E243" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F243" s="8">
+        <v>19.322224</v>
+      </c>
+      <c r="G243" s="8">
+        <v>105.43194</v>
+      </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="11" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B244" s="11" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C244" s="11" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="E244" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F244" s="8">
-        <v>19.322224</v>
+        <v>18.926468</v>
       </c>
       <c r="G244" s="8">
-        <v>105.43194</v>
+        <v>108.480963</v>
       </c>
     </row>
     <row r="245" spans="1:7">
-      <c r="A245" s="11" t="s">
-        <v>574</v>
-      </c>
-      <c r="B245" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="C245" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D245" s="11" t="s">
+      <c r="A245" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="B245" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D245" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E245" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F245" s="8">
-        <v>18.926468</v>
-      </c>
-      <c r="G245" s="8">
-        <v>108.480963</v>
+      <c r="E245" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F245" s="3">
+        <v>18.7065</v>
+      </c>
+      <c r="G245" s="3">
+        <v>105.707897</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="12" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B246" s="12" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C246" s="12" t="s">
-        <v>41</v>
+        <v>580</v>
       </c>
       <c r="D246" s="12" t="s">
         <v>21</v>
@@ -8002,21 +8016,21 @@
         <v>13</v>
       </c>
       <c r="F246" s="3">
-        <v>18.7065</v>
+        <v>10.5002</v>
       </c>
       <c r="G246" s="3">
-        <v>105.707897</v>
+        <v>107.1741</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="12" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B247" s="12" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D247" s="12" t="s">
         <v>21</v>
@@ -8025,57 +8039,43 @@
         <v>13</v>
       </c>
       <c r="F247" s="3">
-        <v>10.5002</v>
+        <v>18.68167</v>
       </c>
       <c r="G247" s="3">
-        <v>107.1741</v>
+        <v>105.59248</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="12" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B248" s="12" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>583</v>
+        <v>13</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E248" s="12" t="s">
         <v>13</v>
       </c>
       <c r="F248" s="3">
-        <v>18.68167</v>
+        <v>18.70531</v>
       </c>
       <c r="G248" s="3">
-        <v>105.59248</v>
+        <v>105.59045</v>
       </c>
     </row>
     <row r="249" spans="1:7">
-      <c r="A249" s="12" t="s">
-        <v>584</v>
-      </c>
-      <c r="B249" s="12" t="s">
-        <v>585</v>
-      </c>
-      <c r="C249" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D249" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E249" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F249" s="3">
-        <v>18.70531</v>
-      </c>
-      <c r="G249" s="3">
-        <v>105.59045</v>
-      </c>
+      <c r="A249" s="13"/>
+      <c r="B249" s="14"/>
+      <c r="C249" s="15"/>
+      <c r="D249" s="14"/>
+      <c r="E249" s="14"/>
+      <c r="F249" s="14"/>
+      <c r="G249" s="14"/>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="13"/>
@@ -8438,7 +8438,7 @@
       <c r="G289" s="14"/>
     </row>
     <row r="290" spans="1:7">
-      <c r="A290" s="13"/>
+      <c r="A290" s="16"/>
       <c r="B290" s="14"/>
       <c r="C290" s="15"/>
       <c r="D290" s="14"/>
@@ -8546,7 +8546,7 @@
       <c r="G301" s="14"/>
     </row>
     <row r="302" spans="1:7">
-      <c r="A302" s="16"/>
+      <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="15"/>
       <c r="D302" s="14"/>
@@ -8834,7 +8834,7 @@
       <c r="G333" s="14"/>
     </row>
     <row r="334" spans="1:7">
-      <c r="A334" s="13"/>
+      <c r="A334" s="16"/>
       <c r="B334" s="14"/>
       <c r="C334" s="15"/>
       <c r="D334" s="14"/>
@@ -8852,7 +8852,7 @@
       <c r="G335" s="14"/>
     </row>
     <row r="336" spans="1:7">
-      <c r="A336" s="16"/>
+      <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="15"/>
       <c r="D336" s="14"/>
@@ -9050,7 +9050,7 @@
       <c r="G357" s="14"/>
     </row>
     <row r="358" spans="1:7">
-      <c r="A358" s="13"/>
+      <c r="A358" s="16"/>
       <c r="B358" s="14"/>
       <c r="C358" s="15"/>
       <c r="D358" s="14"/>
@@ -9059,13 +9059,13 @@
       <c r="G358" s="14"/>
     </row>
     <row r="359" spans="1:7">
-      <c r="A359" s="16"/>
-      <c r="B359" s="14"/>
-      <c r="C359" s="15"/>
-      <c r="D359" s="14"/>
-      <c r="E359" s="14"/>
-      <c r="F359" s="14"/>
-      <c r="G359" s="14"/>
+      <c r="A359" s="17"/>
+      <c r="B359" s="18"/>
+      <c r="C359" s="19"/>
+      <c r="D359" s="18"/>
+      <c r="E359" s="18"/>
+      <c r="F359" s="18"/>
+      <c r="G359" s="18"/>
     </row>
     <row r="360" spans="1:7">
       <c r="A360" s="17"/>
@@ -9077,7 +9077,7 @@
       <c r="G360" s="18"/>
     </row>
     <row r="361" spans="1:7">
-      <c r="A361" s="17"/>
+      <c r="A361" s="20"/>
       <c r="B361" s="18"/>
       <c r="C361" s="19"/>
       <c r="D361" s="18"/>
@@ -9347,7 +9347,7 @@
       <c r="G390" s="18"/>
     </row>
     <row r="391" spans="1:7">
-      <c r="A391" s="20"/>
+      <c r="A391" s="21"/>
       <c r="B391" s="18"/>
       <c r="C391" s="19"/>
       <c r="D391" s="18"/>
@@ -9454,17 +9454,8 @@
       <c r="F402" s="18"/>
       <c r="G402" s="18"/>
     </row>
-    <row r="403" spans="1:7">
-      <c r="A403" s="21"/>
-      <c r="B403" s="18"/>
-      <c r="C403" s="19"/>
-      <c r="D403" s="18"/>
-      <c r="E403" s="18"/>
-      <c r="F403" s="18"/>
-      <c r="G403" s="18"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A249">
+  <conditionalFormatting sqref="A2:A248">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/du_lieu_tram.xlsx
+++ b/du_lieu_tram.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
   <si>
     <t>ma_tram</t>
   </si>
@@ -71,9 +71,6 @@
     <t>NAN</t>
   </si>
   <si>
-    <t>18.836752 105.251633</t>
-  </si>
-  <si>
     <t>BSS-254641001137</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
   </si>
   <si>
     <t>Xã Nhân Hòa</t>
-  </si>
-  <si>
-    <t>19.028191 104.96543</t>
   </si>
   <si>
     <t>BSS-254641000137</t>
@@ -101,9 +95,6 @@
     <t>Xã Tương Dương</t>
   </si>
   <si>
-    <t>19.262676 104.474548</t>
-  </si>
-  <si>
     <t>BSS-254841000482</t>
   </si>
   <si>
@@ -114,9 +105,6 @@
   </si>
   <si>
     <t>Xã Anh Sơn</t>
-  </si>
-  <si>
-    <t>18.932085 105.08323</t>
   </si>
   <si>
     <t>BSS-254841000405</t>
@@ -134,9 +122,6 @@
     <t>Phường Thành Vinh</t>
   </si>
   <si>
-    <t>18.934875 105.07752</t>
-  </si>
-  <si>
     <t>BSS-254741000941</t>
   </si>
   <si>
@@ -147,9 +132,6 @@
   </si>
   <si>
     <t>Xã Con Cuông</t>
-  </si>
-  <si>
-    <t>19.052442 104.87524</t>
   </si>
   <si>
     <t>BSS-254741000977</t>
@@ -177,9 +159,6 @@
   </si>
   <si>
     <t>Xóm 5, Xã Hợp Minh, Quỳ Hợp, Tỉnh Nghệ An</t>
-  </si>
-  <si>
-    <t>18.897457 105.307968</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1267,7 @@
     <col min="3" max="3" width="31.6666666666667" customWidth="1"/>
     <col min="4" max="4" width="22.5555555555556" customWidth="1"/>
     <col min="5" max="5" width="20.7777777777778" customWidth="1"/>
-    <col min="6" max="6" width="16.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="27.6666666666667" customWidth="1"/>
     <col min="7" max="7" width="22.7777777777778" customWidth="1"/>
     <col min="8" max="8" width="29.5555555555556" customWidth="1"/>
   </cols>
@@ -1338,234 +1317,256 @@
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2"/>
+      <c r="F2" s="3">
+        <v>18.836752</v>
+      </c>
+      <c r="G2" s="2">
+        <v>105.251633</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="J2" s="4"/>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2"/>
+      <c r="F3" s="3">
+        <v>19.028191</v>
+      </c>
+      <c r="G3" s="2">
+        <v>104.96543</v>
+      </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="2"/>
+      <c r="F4" s="3">
+        <v>19.262676</v>
+      </c>
+      <c r="G4" s="2">
+        <v>104.474548</v>
+      </c>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="2"/>
+      <c r="F5" s="3">
+        <v>18.932085</v>
+      </c>
+      <c r="G5" s="2">
+        <v>105.08323</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="2"/>
+      <c r="F6" s="3">
+        <v>18.932085</v>
+      </c>
+      <c r="G6" s="2">
+        <v>105.08323</v>
+      </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="2"/>
+      <c r="F7" s="3">
+        <v>18.934875</v>
+      </c>
+      <c r="G7" s="2">
+        <v>105.07752</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="2"/>
+      <c r="F8" s="3">
+        <v>19.052442</v>
+      </c>
+      <c r="G8" s="2">
+        <v>104.87524</v>
+      </c>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="2"/>
+      <c r="F9" s="3">
+        <v>19.052442</v>
+      </c>
+      <c r="G9" s="2">
+        <v>104.87524</v>
+      </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="2"/>
+      <c r="F10" s="3">
+        <v>19.028191</v>
+      </c>
+      <c r="G10" s="2">
+        <v>104.96543</v>
+      </c>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="2"/>
+      <c r="F11" s="3">
+        <v>19.028191</v>
+      </c>
+      <c r="G11" s="2">
+        <v>104.96543</v>
+      </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="2"/>
+      <c r="F12" s="3">
+        <v>18.897457</v>
+      </c>
+      <c r="G12" s="2">
+        <v>105.307968</v>
+      </c>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:12">
